--- a/data/Output_Template_TKB_V8.xlsx
+++ b/data/Output_Template_TKB_V8.xlsx
@@ -6436,7 +6436,7 @@
       <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Kỹ năng sống
-Quản lý Trương</t>
+Giáo viên QL 1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -6788,7 +6788,7 @@
       <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Kỹ năng sống
-Quản lý Trương</t>
+Giáo viên QL 1</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -7730,7 +7730,7 @@
       <c r="G48" s="2" t="inlineStr">
         <is>
           <t>Kỹ năng sống
-Quản lý Trương</t>
+Giáo viên QL 1</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -8034,7 +8034,7 @@
       <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Kỹ năng sống
-Quản lý Trương</t>
+Giáo viên QL 1</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">

--- a/data/Output_Template_TKB_V8.xlsx
+++ b/data/Output_Template_TKB_V8.xlsx
@@ -465,8 +465,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5" customWidth="1" min="1" max="1"/>
-    <col width="8.1" customWidth="1" min="2" max="2"/>
-    <col width="6.9" customWidth="1" min="3" max="3"/>
+    <col width="12.1" customWidth="1" min="2" max="2"/>
+    <col width="10.9" customWidth="1" min="3" max="3"/>
     <col width="21.5" customWidth="1" min="4" max="4"/>
     <col width="21.5" customWidth="1" min="5" max="5"/>
     <col width="21.5" customWidth="1" min="6" max="6"/>
@@ -2370,8 +2370,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5" customWidth="1" min="1" max="1"/>
-    <col width="8.1" customWidth="1" min="2" max="2"/>
-    <col width="6.9" customWidth="1" min="3" max="3"/>
+    <col width="12.1" customWidth="1" min="2" max="2"/>
+    <col width="10.9" customWidth="1" min="3" max="3"/>
     <col width="21.5" customWidth="1" min="4" max="4"/>
     <col width="21.5" customWidth="1" min="5" max="5"/>
     <col width="21.5" customWidth="1" min="6" max="6"/>
@@ -4275,8 +4275,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5" customWidth="1" min="1" max="1"/>
-    <col width="8.1" customWidth="1" min="2" max="2"/>
-    <col width="6.9" customWidth="1" min="3" max="3"/>
+    <col width="12.1" customWidth="1" min="2" max="2"/>
+    <col width="10.9" customWidth="1" min="3" max="3"/>
     <col width="21.5" customWidth="1" min="4" max="4"/>
     <col width="21.5" customWidth="1" min="5" max="5"/>
     <col width="21.5" customWidth="1" min="6" max="6"/>
@@ -6180,8 +6180,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5" customWidth="1" min="1" max="1"/>
-    <col width="8.1" customWidth="1" min="2" max="2"/>
-    <col width="6.9" customWidth="1" min="3" max="3"/>
+    <col width="12.1" customWidth="1" min="2" max="2"/>
+    <col width="10.9" customWidth="1" min="3" max="3"/>
     <col width="21.5" customWidth="1" min="4" max="4"/>
     <col width="21.5" customWidth="1" min="5" max="5"/>
     <col width="21.5" customWidth="1" min="6" max="6"/>
@@ -8085,8 +8085,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5" customWidth="1" min="1" max="1"/>
-    <col width="8.1" customWidth="1" min="2" max="2"/>
-    <col width="6.9" customWidth="1" min="3" max="3"/>
+    <col width="12.1" customWidth="1" min="2" max="2"/>
+    <col width="10.9" customWidth="1" min="3" max="3"/>
     <col width="21.5" customWidth="1" min="4" max="4"/>
     <col width="21.5" customWidth="1" min="5" max="5"/>
     <col width="21.5" customWidth="1" min="6" max="6"/>

--- a/data/Output_Template_TKB_V8.xlsx
+++ b/data/Output_Template_TKB_V8.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 1</t>
         </is>
       </c>
@@ -569,32 +569,32 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 1</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 4</t>
-        </is>
-      </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Tiếng Việt
 Giáo viên CN 1</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 1</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
         </is>
       </c>
     </row>
@@ -606,14 +606,14 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên BM 3</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên BM 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 1</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 1</t>
         </is>
       </c>
@@ -643,26 +643,26 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên BM 3</t>
+          <t>TNXH
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 1</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -684,8 +684,8 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 1</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -696,14 +696,14 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Đạo đức
 Giáo viên CN 1</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên CN 1</t>
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -732,14 +732,14 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 4</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên CN 1</t>
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -756,26 +756,26 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 1</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Kỹ năng sống
-Giáo viên BM 2</t>
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -860,13 +860,13 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 2</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 2</t>
         </is>
       </c>
@@ -879,26 +879,26 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 2</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 2</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 2</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 2</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 2</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 5</t>
         </is>
       </c>
     </row>
@@ -953,8 +953,8 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Toán
+Giáo viên CN 2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 2</t>
         </is>
       </c>
@@ -994,14 +994,14 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1036,19 +1036,19 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 2</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 2</t>
-        </is>
-      </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 2</t>
         </is>
       </c>
@@ -1066,28 +1066,28 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 2</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>Đạo đức
 Giáo viên CN 2</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 2</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 5</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -1158,13 +1158,13 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 3</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 3</t>
         </is>
       </c>
@@ -1189,32 +1189,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 3</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên BM 2</t>
+Giáo viên CN 3</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 3</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 3</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên BM 2</t>
         </is>
       </c>
     </row>
@@ -1232,20 +1232,20 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 3</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 3</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên CN 3</t>
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1263,26 +1263,26 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>TNXH
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 3</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 3</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 3</t>
-        </is>
-      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1304,20 +1304,20 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 3</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 3</t>
-        </is>
-      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 5</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1346,20 +1346,20 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên BM 5</t>
+          <t>Tiếng Việt
+Giáo viên CN 3</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 3</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1376,26 +1376,26 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>Đạo đức
+Giáo viên CN 3</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>TNXH
-Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 3</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 3</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên BM 4</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 4</t>
         </is>
       </c>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 4</t>
         </is>
       </c>
@@ -1500,7 +1500,7 @@
       <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên BM 5</t>
+Giáo viên CN 4</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1512,7 +1512,7 @@
       <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên BM 5</t>
+Giáo viên CN 4</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -1523,8 +1523,8 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 4</t>
+          <t>Tiếng Việt
+Giáo viên BM 1</t>
         </is>
       </c>
     </row>
@@ -1542,26 +1542,26 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 4</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 5</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Tiếng Việt
+Giáo viên BM 1</t>
         </is>
       </c>
     </row>
@@ -1574,19 +1574,19 @@
       <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
-Giáo viên TA 4</t>
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 5</t>
+          <t>Toán
+Giáo viên CN 4</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Đạo đức
 Giáo viên CN 4</t>
         </is>
       </c>
@@ -1626,8 +1626,8 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 4</t>
+          <t>TNXH
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 4</t>
         </is>
       </c>
@@ -1662,14 +1662,14 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 4</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1686,26 +1686,26 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 4</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 4</t>
         </is>
       </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 1</t>
+        </is>
+      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1809,14 +1809,14 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên BM 2</t>
+          <t>Toán
+Giáo viên CN 5</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 5</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -1865,13 +1865,13 @@
       <c r="G44" s="2" t="inlineStr">
         <is>
           <t>TNXH
-Giáo viên BM 3</t>
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên BM 2</t>
+Giáo viên CN 5</t>
         </is>
       </c>
     </row>
@@ -1883,26 +1883,26 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 5</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 5</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Toán
+Giáo viên CN 5</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -1924,26 +1924,26 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Tiếng Việt
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 5</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 2</t>
-        </is>
-      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 5</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -1961,25 +1961,25 @@
       <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 5</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 5</t>
-        </is>
-      </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 5</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -1996,28 +1996,28 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
           <t>Đạo đức
 Giáo viên CN 5</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 5</t>
         </is>
       </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 6</t>
         </is>
       </c>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 6</t>
         </is>
       </c>
@@ -2119,32 +2119,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 6</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 6</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 3</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 6</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên CN 6</t>
+Giáo viên BM 2</t>
         </is>
       </c>
     </row>
@@ -2157,13 +2157,13 @@
       <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên BM 1</t>
+Giáo viên CN 6</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 6</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -2174,14 +2174,14 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 6</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên CN 6</t>
+Giáo viên BM 2</t>
         </is>
       </c>
     </row>
@@ -2194,12 +2194,12 @@
       <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên BM 1</t>
+Giáo viên CN 6</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 6</t>
         </is>
       </c>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 6</t>
         </is>
       </c>
@@ -2234,26 +2234,26 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 6</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 6</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 6</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2270,14 +2270,14 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Toán
 Giáo viên CN 6</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -2288,8 +2288,8 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 6</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -2306,26 +2306,26 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
+          <t>Kỹ năng sống
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Đạo đức
+Giáo viên CN 6</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 6</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2443,25 +2443,25 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 7</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 7</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 7</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 7</t>
         </is>
       </c>
@@ -2474,20 +2474,20 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 7</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 7</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 2</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -2511,31 +2511,31 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 7</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 7</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 7</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 7</t>
         </is>
       </c>
@@ -2548,26 +2548,26 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 7</t>
+          <t>Kỹ năng sống
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -2589,25 +2589,25 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên BM 5</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>TV tăng cường
 Giáo viên CN 7</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>TV tăng cường
-Giáo viên CN 7</t>
-        </is>
-      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Toán tăng cường
 Giáo viên BM 2</t>
         </is>
       </c>
@@ -2625,26 +2625,26 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>Toán tăng cường
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>TV tăng cường
+Giáo viên CN 7</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên BM 5</t>
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -2661,22 +2661,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Đạo đức
 Giáo viên CN 7</t>
         </is>
       </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>HĐTN
@@ -2771,7 +2771,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 8</t>
         </is>
       </c>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 8</t>
         </is>
       </c>
@@ -2796,8 +2796,8 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 8</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2827,26 +2827,26 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 8</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 8</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
         </is>
       </c>
     </row>
@@ -2858,14 +2858,14 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2905,20 +2905,20 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Toán
 Giáo viên CN 8</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2935,20 +2935,20 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>TV tăng cường
 Giáo viên CN 8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Toán tăng cường
 Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>TV tăng cường
-Giáo viên CN 8</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2971,20 +2971,20 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Đạo đức
+Giáo viên CN 8</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Kỹ năng sống
-Giáo viên BM 1</t>
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -3063,25 +3063,25 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 9</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 9</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 9</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 9</t>
         </is>
       </c>
@@ -3100,8 +3100,8 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 9</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -3118,8 +3118,8 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 9</t>
         </is>
       </c>
     </row>
@@ -3131,31 +3131,31 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 9</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 9</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 9</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 9</t>
         </is>
       </c>
@@ -3174,20 +3174,20 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>TNXH
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 9</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 9</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3209,25 +3209,25 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>Kỹ năng sống
 Giáo viên BM 2</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Toán tăng cường
-Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên BM 4</t>
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>TV tăng cường
 Giáo viên CN 9</t>
         </is>
       </c>
@@ -3245,20 +3245,20 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán tăng cường
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 9</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>TV tăng cường
-Giáo viên CN 9</t>
-        </is>
-      </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3299,8 +3299,8 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 10</t>
         </is>
       </c>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 10</t>
         </is>
       </c>
@@ -3404,26 +3404,26 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 10</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 10</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 10</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -3447,26 +3447,26 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 10</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 10</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 10</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 1</t>
         </is>
       </c>
     </row>
@@ -3478,13 +3478,13 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 10</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 10</t>
         </is>
       </c>
@@ -3496,8 +3496,8 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 10</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3519,8 +3519,8 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 10</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -3531,14 +3531,14 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 1</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>TV tăng cường
+Giáo viên CN 10</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3555,20 +3555,20 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>TV tăng cường
-Giáo viên CN 10</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -3591,26 +3591,26 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>Đạo đức
 Giáo viên CN 10</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 10</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 11</t>
         </is>
       </c>
@@ -3732,8 +3732,8 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 11</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3757,8 +3757,8 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -3769,14 +3769,14 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
           <t>Toán
 Giáo viên CN 11</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
         </is>
       </c>
     </row>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 11</t>
         </is>
       </c>
@@ -3800,8 +3800,8 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -3829,8 +3829,8 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Toán tăng cường
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -3841,14 +3841,14 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>TV tăng cường
-Giáo viên CN 11</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3865,26 +3865,26 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>TV tăng cường
+Giáo viên CN 11</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 11</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
-Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
 Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 11</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3901,25 +3901,25 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 11</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 11</t>
         </is>
       </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Kỹ năng sống
 Giáo viên BM 3</t>
         </is>
       </c>
@@ -3999,13 +3999,13 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 12</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 12</t>
         </is>
       </c>
@@ -4024,26 +4024,26 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 12</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 12</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 12</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 12</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4073,20 +4073,20 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 12</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 12</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Toán
+Giáo viên CN 12</t>
         </is>
       </c>
     </row>
@@ -4098,26 +4098,26 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 12</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 12</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>Toán
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 12</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4140,19 +4140,19 @@
       <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Thể dục
-Giáo viên TD 3</t>
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>TV tăng cường
 Giáo viên CN 12</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -4175,8 +4175,8 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 4</t>
+          <t>Toán tăng cường
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -4187,14 +4187,14 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên BM 3</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên BM 4</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4217,20 +4217,20 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 2</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 12</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4354,13 +4354,13 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 13</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 13</t>
         </is>
       </c>
@@ -4379,8 +4379,8 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 13</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -4397,14 +4397,14 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 13</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Công nghệ
-Giáo viên BM 1</t>
+Giáo viên BM 3</t>
         </is>
       </c>
     </row>
@@ -4416,32 +4416,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>Toán
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 13</t>
         </is>
       </c>
     </row>
@@ -4453,25 +4453,25 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>Toán
 Giáo viên CN 13</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Toán
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 13</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 13</t>
-        </is>
-      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 13</t>
         </is>
       </c>
@@ -4494,26 +4494,26 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên CN 13</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
 Giáo viên CN 13</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -4530,25 +4530,25 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>TV tăng cường
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 2</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>TV tăng cường
+          <t>Toán tăng cường
 Giáo viên CN 13</t>
         </is>
       </c>
@@ -4566,26 +4566,26 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
           <t>Kỹ năng sống
 Giáo viên CN 13</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 13</t>
         </is>
       </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 3</t>
+        </is>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 13</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -4689,8 +4689,8 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -4732,26 +4732,26 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>TV tăng cường
+Giáo viên CN 14</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 14</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>TNXH
-Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 14</t>
+Giáo viên BM 3</t>
         </is>
       </c>
     </row>
@@ -4770,19 +4770,19 @@
       <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
-Giáo viên TA 4</t>
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 14</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 14</t>
+          <t>Công nghệ
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -4804,26 +4804,26 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 3</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên CN 14</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Thể dục
 Giáo viên TD 2</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 14</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -4840,25 +4840,25 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>TNXH
-Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Toán tăng cường
-Giáo viên CN 14</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>TV tăng cường
 Giáo viên CN 14</t>
         </is>
       </c>
@@ -4882,22 +4882,22 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>HĐTN
 Giáo viên CN 14</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Kỹ năng sống
 Giáo viên CN 14</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -4980,13 +4980,13 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 15</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 15</t>
         </is>
       </c>
@@ -5000,25 +5000,25 @@
       <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
-Giáo viên TA 1</t>
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 15</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 15</t>
-        </is>
-      </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 15</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -5036,8 +5036,8 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -5048,19 +5048,19 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Công nghệ
-Giáo viên BM 4</t>
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 15</t>
         </is>
       </c>
@@ -5079,20 +5079,20 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 15</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 15</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 15</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên BM 4</t>
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -5114,26 +5114,26 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Toán tăng cường
 Giáo viên CN 15</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 15</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
-Giáo viên TA 1</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên BM 4</t>
+          <t>Đạo đức
+Giáo viên CN 15</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -5150,26 +5150,26 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>TV tăng cường
+Giáo viên CN 15</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên CN 15</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>TV tăng cường
-Giáo viên CN 15</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 15</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -5186,28 +5186,28 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Kỹ năng sống
 Giáo viên CN 15</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 15</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên CN 15</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -5278,19 +5278,19 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 16</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 16</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 16</t>
         </is>
       </c>
@@ -5309,8 +5309,8 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Toán
+Giáo viên CN 16</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>TV tăng cường
 Giáo viên CN 16</t>
         </is>
       </c>
@@ -5346,32 +5346,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 16</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 16</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 16</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
         </is>
       </c>
     </row>
@@ -5383,26 +5383,26 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>Toán
 Giáo viên CN 16</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên BM 4</t>
-        </is>
-      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 2</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -5424,26 +5424,26 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
           <t>Toán tăng cường
 Giáo viên CN 16</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 16</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -5460,8 +5460,8 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên CN 16</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -5472,8 +5472,8 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>TV tăng cường
-Giáo viên CN 16</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -5502,20 +5502,20 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>HĐTN
 Giáo viên CN 16</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 2</t>
-        </is>
-      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 1</t>
+          <t>Kỹ năng sống
+Giáo viên CN 16</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -5588,25 +5588,25 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 17</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 17</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 17</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 17</t>
         </is>
       </c>
@@ -5619,32 +5619,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 17</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 17</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 17</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 17</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 17</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 3</t>
         </is>
       </c>
     </row>
@@ -5656,32 +5656,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
           <t>Tin học
 Giáo viên TH 1</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 17</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 17</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 17</t>
-        </is>
-      </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 17</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
     </row>
@@ -5699,19 +5699,19 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 1</t>
+          <t>Toán
+Giáo viên CN 17</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 17</t>
         </is>
       </c>
@@ -5734,26 +5734,26 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
+          <t>Tiếng Việt
 Giáo viên CN 17</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Đạo đức
+Giáo viên CN 17</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Toán
+Giáo viên CN 17</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 17</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -5776,20 +5776,20 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Toán tăng cường
 Giáo viên CN 17</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Toán tăng cường
+Giáo viên CN 17</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>TNXH
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -5806,20 +5806,20 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên CN 17</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>TNXH
-Giáo viên CN 17</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên CN 17</t>
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5898,13 +5898,13 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 18</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 18</t>
         </is>
       </c>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 18</t>
         </is>
       </c>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 18</t>
         </is>
       </c>
@@ -5941,20 +5941,20 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 18</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 18</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Toán tăng cường
+Giáo viên CN 18</t>
         </is>
       </c>
     </row>
@@ -5966,32 +5966,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 18</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 18</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 18</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 18</t>
+Giáo viên TD 2</t>
         </is>
       </c>
     </row>
@@ -6003,26 +6003,26 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
           <t>Toán
 Giáo viên CN 18</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 18</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 18</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -6044,26 +6044,26 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 18</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
+          <t>Toán
 Giáo viên CN 18</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
           <t>TNXH
-Giáo viên BM 5</t>
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -6080,26 +6080,26 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
           <t>TV tăng cường
 Giáo viên CN 18</t>
         </is>
       </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 18</t>
+        </is>
+      </c>
       <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>Toán tăng cường
 Giáo viên CN 18</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -6116,25 +6116,25 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
 Giáo viên CN 18</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>HĐTN
-Giáo viên CN 18</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
 Giáo viên CN 18</t>
         </is>
       </c>
@@ -6253,19 +6253,19 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 19</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 19</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 19</t>
         </is>
       </c>
@@ -6284,32 +6284,32 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 19</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 19</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 19</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 19</t>
-        </is>
-      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 19</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
     </row>
@@ -6321,26 +6321,26 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Toán
+Giáo viên CN 19</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 19</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
-Giáo viên TA 1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 2</t>
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -6364,20 +6364,20 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Toán
+Giáo viên CN 19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>Toán
 Giáo viên CN 19</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -6399,25 +6399,25 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Toán tăng cường
+Giáo viên CN 19</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Khoa học
 Giáo viên CN 19</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
+          <t>Khoa học
 Giáo viên CN 19</t>
         </is>
       </c>
@@ -6441,20 +6441,20 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên BM 4</t>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 19</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Tin học
 Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -6483,16 +6483,16 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
           <t>HĐTN
 Giáo viên CN 19</t>
         </is>
       </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -6569,13 +6569,13 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
+          <t>Toán
 Giáo viên CN 20</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 20</t>
         </is>
       </c>
@@ -6601,24 +6601,24 @@
       <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
-Giáo viên TA 1</t>
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Khoa học
+Giáo viên CN 20</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 20</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 20</t>
         </is>
       </c>
@@ -6631,8 +6631,8 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 20</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -6643,20 +6643,20 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 20</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 20</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
     </row>
@@ -6668,25 +6668,25 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 20</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 20</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
-        </is>
-      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 20</t>
         </is>
       </c>
@@ -6709,26 +6709,26 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
 Giáo viên CN 20</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Toán tăng cường
 Giáo viên CN 20</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
-        </is>
-      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
-Giáo viên CN 20</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -6745,26 +6745,26 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
           <t>Âm nhạc
 Giáo viên ÂN 1</t>
         </is>
       </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
+          <t>Đạo đức
 Giáo viên CN 20</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Kỹ năng sống
+Giáo viên QL 1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -6781,28 +6781,28 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Lịch sử - Địa lý
 Giáo viên CN 20</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên QL 1</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 20</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 20</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -6873,7 +6873,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
+          <t>Tiếng Việt
 Giáo viên CN 21</t>
         </is>
       </c>
@@ -6904,32 +6904,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 21</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 21</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
           <t>Tin học
 Giáo viên TH 1</t>
         </is>
       </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 21</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 21</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 21</t>
         </is>
       </c>
     </row>
@@ -6941,32 +6941,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
+          <t>Toán
 Giáo viên CN 21</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 21</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 21</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 21</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 21</t>
         </is>
       </c>
@@ -6996,8 +6996,8 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 21</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -7019,20 +7019,20 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
 Giáo viên CN 21</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7055,26 +7055,26 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
 Giáo viên CN 21</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Khoa học
+Giáo viên CN 21</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -7091,26 +7091,26 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 1</t>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 21</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên QL 1</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 21</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 21</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -7220,26 +7220,26 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 22</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
           <t>Mỹ thuật
 Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 22</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
         </is>
       </c>
     </row>
@@ -7251,8 +7251,8 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 2</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -7269,8 +7269,8 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Toán tăng cường
+Giáo viên CN 22</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -7307,7 +7307,7 @@
       <c r="G35" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
-Giáo viên TA 1</t>
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -7329,14 +7329,14 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên BM 4</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7347,8 +7347,8 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -7365,25 +7365,25 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>Khoa học
+Giáo viên CN 22</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
-Giáo viên TA 1</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
+          <t>Lịch sử - Địa lý
 Giáo viên CN 22</t>
         </is>
       </c>
@@ -7407,22 +7407,22 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
+          <t>Đạo đức
+Giáo viên CN 22</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên QL 1</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
           <t>HĐTN
 Giáo viên CN 22</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 22</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 22</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -7499,19 +7499,19 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 23</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 23</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 23</t>
         </is>
       </c>
@@ -7524,8 +7524,8 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Toán
+Giáo viên CN 23</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -7542,14 +7542,14 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
+          <t>Tiếng Việt
 Giáo viên CN 23</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 23</t>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
         </is>
       </c>
     </row>
@@ -7561,32 +7561,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 23</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 23</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 23</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
           <t>Công nghệ
 Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 23</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 23</t>
         </is>
       </c>
     </row>
@@ -7598,25 +7598,25 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 23</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
-Giáo viên TA 2</t>
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 23</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 23</t>
         </is>
       </c>
@@ -7645,20 +7645,20 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Đạo đức
+Giáo viên CN 23</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
+Giáo viên CN 23</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>Tin học
 Giáo viên TH 1</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -7675,26 +7675,26 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 23</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>Toán tăng cường
 Giáo viên CN 23</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -7711,28 +7711,28 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
 Giáo viên CN 23</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 23</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 23</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 23</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên QL 1</t>
-        </is>
-      </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -7803,13 +7803,13 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 24</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 24</t>
         </is>
       </c>
@@ -7834,32 +7834,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 24</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 24</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 24</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 24</t>
+Giáo viên TA 4</t>
         </is>
       </c>
     </row>
@@ -7871,32 +7871,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 24</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 24</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 24</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 3</t>
         </is>
       </c>
     </row>
@@ -7908,19 +7908,19 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 24</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 24</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 24</t>
         </is>
       </c>
@@ -7949,25 +7949,25 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
           <t>Khoa học
 Giáo viên CN 24</t>
         </is>
       </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
           <t>Khoa học
-Giáo viên CN 24</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
 Giáo viên CN 24</t>
         </is>
       </c>
@@ -7985,26 +7985,26 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
           <t>Toán tăng cường
 Giáo viên CN 24</t>
         </is>
       </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Đạo đức
+Giáo viên CN 24</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -8021,25 +8021,25 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Âm nhạc
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
 Giáo viên CN 24</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 24</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên QL 1</t>
-        </is>
-      </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>HĐTN
+          <t>Lịch sử - Địa lý
 Giáo viên CN 24</t>
         </is>
       </c>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 25</t>
         </is>
       </c>
@@ -8189,8 +8189,8 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -8232,26 +8232,26 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 25</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 25</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 25</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+Giáo viên TA 4</t>
         </is>
       </c>
     </row>
@@ -8269,20 +8269,20 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 2</t>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Toán tăng cường
 Giáo viên CN 25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Âm nhạc
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -8304,20 +8304,20 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
           <t>Khoa học
 Giáo viên CN 25</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8340,26 +8340,26 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 25</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 25</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -8376,28 +8376,28 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 25</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 25</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Đạo đức
 Giáo viên CN 25</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 25</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -8480,7 +8480,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 26</t>
         </is>
       </c>
@@ -8499,7 +8499,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 26</t>
         </is>
       </c>
@@ -8511,20 +8511,20 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 26</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 26</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 26</t>
         </is>
       </c>
     </row>
@@ -8536,14 +8536,14 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 26</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 1</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -8554,14 +8554,14 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 26</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 26</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
     </row>
@@ -8573,8 +8573,8 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên BM 4</t>
+          <t>Toán tăng cường
+Giáo viên CN 26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -8585,14 +8585,14 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -8620,20 +8620,20 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Đạo đức
+Giáo viên CN 26</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 26</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Thể dục
 Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -8656,20 +8656,20 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
+          <t>Khoa học
 Giáo viên CN 26</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Âm nhạc
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 1</t>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -8686,8 +8686,8 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 26</t>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -8698,16 +8698,16 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 26</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>HĐTN
 Giáo viên CN 26</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 26</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 27</t>
         </is>
       </c>
@@ -8815,8 +8815,8 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 27</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -8827,8 +8827,8 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 27</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -8846,32 +8846,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 27</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 27</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 27</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
         </is>
       </c>
     </row>
@@ -8883,26 +8883,26 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 27</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 27</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 27</t>
+          <t>Âm nhạc
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 27</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -8924,25 +8924,25 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
-Giáo viên CN 27</t>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Toán tăng cường
 Giáo viên CN 27</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
+          <t>Đạo đức
 Giáo viên CN 27</t>
         </is>
       </c>
@@ -8960,26 +8960,26 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Khoa học
+Giáo viên CN 27</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 1</t>
+          <t>Khoa học
+Giáo viên CN 27</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -9002,16 +9002,16 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 27</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 27</t>
         </is>
       </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
+        </is>
+      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>HĐTN
@@ -9100,13 +9100,13 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 28</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 28</t>
         </is>
       </c>
@@ -9119,8 +9119,8 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Toán
+Giáo viên CN 28</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -9131,8 +9131,8 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 28</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -9143,8 +9143,8 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 28</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
     </row>
@@ -9156,31 +9156,31 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 28</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Kỹ năng sống
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 28</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 28</t>
         </is>
       </c>
@@ -9193,26 +9193,26 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>Âm nhạc
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 28</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
-Giáo viên TA 1</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 28</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 3</t>
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 28</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -9234,26 +9234,26 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Khoa học
 Giáo viên CN 28</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Công nghệ
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -9270,26 +9270,26 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>Toán tăng cường
+Giáo viên CN 28</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
           <t>Khoa học
 Giáo viên CN 28</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 1</t>
-        </is>
-      </c>
       <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên CN 28</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 28</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -9306,22 +9306,22 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 28</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>Đạo đức
 Giáo viên CN 28</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 28</t>
-        </is>
-      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
           <t>HĐTN
@@ -9404,7 +9404,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 29</t>
         </is>
       </c>
@@ -9436,25 +9436,25 @@
       <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
+Giáo viên CN 29</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 29</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 29</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
         </is>
       </c>
     </row>
@@ -9466,32 +9466,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 29</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 29</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ
 Giáo viên BM 5</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 1</t>
-        </is>
-      </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên CN 29</t>
+Giáo viên BM 5</t>
         </is>
       </c>
     </row>
@@ -9503,26 +9503,26 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 29</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 29</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -9544,26 +9544,26 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
-Giáo viên CN 29</t>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 29</t>
+          <t>Toán tăng cường
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 29</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên BM 1</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -9580,25 +9580,25 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Âm nhạc
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Khoa học
 Giáo viên CN 29</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 29</t>
-        </is>
-      </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Khoa học
 Giáo viên CN 29</t>
         </is>
       </c>
@@ -9616,8 +9616,8 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 2</t>
+          <t>Đạo đức
+Giáo viên CN 29</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -9628,14 +9628,14 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên BM 4</t>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 29</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 29</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">

--- a/data/Output_Template_TKB_V8.xlsx
+++ b/data/Output_Template_TKB_V8.xlsx
@@ -556,7 +556,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 1</t>
         </is>
       </c>
@@ -569,26 +569,26 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 1</t>
-        </is>
-      </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên CN 1</t>
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Kỹ năng sống
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -606,8 +606,8 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 1</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -619,18 +619,18 @@
       <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 1</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 1</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 1</t>
         </is>
       </c>
@@ -643,20 +643,20 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -684,26 +684,26 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 1</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 1</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 1</t>
-        </is>
-      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 1</t>
         </is>
       </c>
@@ -732,13 +732,13 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>TNXH
 Giáo viên BM 1</t>
         </is>
       </c>
@@ -756,16 +756,16 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
           <t>Thể dục
 Giáo viên TD 3</t>
         </is>
       </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
           <t>HĐTN
@@ -774,8 +774,8 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 1</t>
+          <t>Đạo đức
+Giáo viên CN 1</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -848,7 +848,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 2</t>
         </is>
       </c>
@@ -860,7 +860,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 2</t>
         </is>
       </c>
@@ -879,20 +879,20 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -916,26 +916,26 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 2</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 2</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Âm nhạc
 Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 2</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 2</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -959,20 +959,20 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên BM 1</t>
+Giáo viên CN 2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 2</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -995,25 +995,25 @@
       <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 2</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 2</t>
-        </is>
-      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 2</t>
+          <t>TNXH
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên CN 2</t>
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1048,8 +1048,8 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 2</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1066,28 +1066,28 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>Đạo đức
+Giáo viên CN 2</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 3</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 2</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 2</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 3</t>
         </is>
       </c>
@@ -1189,32 +1189,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 3</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 3</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 3</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 3</t>
         </is>
       </c>
     </row>
@@ -1238,20 +1238,20 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 3</t>
         </is>
       </c>
     </row>
@@ -1263,26 +1263,26 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 3</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 3</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 3</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 3</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1316,8 +1316,8 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>TNXH
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1376,28 +1376,28 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>Đạo đức
 Giáo viên CN 3</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 3</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>TNXH
 Giáo viên BM 1</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 3</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 4</t>
         </is>
       </c>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 4</t>
         </is>
       </c>
@@ -1517,14 +1517,14 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 4</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
     </row>
@@ -1542,26 +1542,26 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 4</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên BM 1</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 4</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
     </row>
@@ -1573,8 +1573,8 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 4</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1585,14 +1585,14 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>TNXH
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 4</t>
+          <t>Tiếng Việt
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1626,8 +1626,8 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 4</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1650,20 +1650,20 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 4</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 4</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -1686,28 +1686,28 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 4</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 1</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 4</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -1784,19 +1784,19 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 5</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 5</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 5</t>
         </is>
       </c>
@@ -1815,8 +1815,8 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -1853,24 +1853,24 @@
       <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 5</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 5</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 2</t>
-        </is>
-      </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 5</t>
         </is>
       </c>
@@ -1890,19 +1890,19 @@
       <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 5</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>TNXH
 Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 5</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -1924,26 +1924,26 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 5</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 5</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -1960,26 +1960,26 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 5</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 5</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -1996,26 +1996,26 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
           <t>Đạo đức
 Giáo viên CN 5</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 5</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2119,26 +2119,26 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 2</t>
+          <t>Toán
+Giáo viên CN 6</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 6</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Mỹ thuật
 Giáo viên MT 1</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 6</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -2199,20 +2199,20 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 6</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 6</t>
-        </is>
-      </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 6</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2234,14 +2234,14 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 6</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -2252,8 +2252,8 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 6</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2270,16 +2270,16 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 6</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
@@ -2288,8 +2288,8 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 6</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
+          <t>TNXH
 Giáo viên BM 2</t>
         </is>
       </c>
@@ -2318,14 +2318,14 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
           <t>HĐTN
 Giáo viên CN 6</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 7</t>
         </is>
       </c>
@@ -2474,14 +2474,14 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 7</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 7</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -2523,14 +2523,14 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 2</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 7</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -2548,26 +2548,26 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 7</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Toán
 Giáo viên CN 7</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -2589,26 +2589,26 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Toán tăng cường
 Giáo viên BM 2</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Đạo đức
+Giáo viên CN 7</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>TV tăng cường
 Giáo viên CN 7</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên BM 2</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -2625,26 +2625,26 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 7</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên BM 2</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>TV tăng cường
 Giáo viên CN 7</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -2661,20 +2661,20 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 7</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Kỹ năng sống
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Kỹ năng sống
 Giáo viên BM 2</t>
         </is>
       </c>
@@ -2821,26 +2821,26 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 8</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 8</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -2858,16 +2858,16 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 8</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
         </is>
       </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 8</t>
+        </is>
+      </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
@@ -2876,8 +2876,8 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 8</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2899,20 +2899,20 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 8</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>TV tăng cường
 Giáo viên CN 8</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 8</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2935,20 +2935,20 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 8</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>TV tăng cường
 Giáo viên CN 8</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên BM 2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2977,22 +2977,22 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
           <t>HĐTN
 Giáo viên CN 8</t>
         </is>
       </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 9</t>
         </is>
       </c>
@@ -3075,7 +3075,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 9</t>
         </is>
       </c>
@@ -3100,8 +3100,8 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 9</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -3131,26 +3131,26 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 9</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
         </is>
       </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 9</t>
+        </is>
+      </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Kỹ năng sống
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 9</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3168,16 +3168,16 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 9</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
           <t>TNXH
 Giáo viên BM 2</t>
         </is>
       </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 9</t>
+        </is>
+      </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Toán
@@ -3186,8 +3186,8 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Toán
+Giáo viên CN 9</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3209,20 +3209,20 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 9</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 2</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên BM 2</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,20 +3245,20 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 9</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên BM 2</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 9</t>
-        </is>
-      </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Toán tăng cường
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3293,16 +3293,16 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>HĐTN
 Giáo viên CN 9</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 2</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -3373,13 +3373,13 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 10</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 10</t>
         </is>
       </c>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 10</t>
         </is>
       </c>
@@ -3404,26 +3404,26 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 10</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 10</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>TNXH
 Giáo viên BM 3</t>
         </is>
       </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 10</t>
+        </is>
+      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 10</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -3447,25 +3447,25 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 10</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 10</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 10</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 10</t>
         </is>
       </c>
@@ -3478,26 +3478,26 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 10</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 10</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 10</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 10</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3519,26 +3519,26 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
           <t>Toán tăng cường
 Giáo viên BM 3</t>
         </is>
       </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên BM 3</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>TV tăng cường
+Giáo viên CN 10</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Thể dục
 Giáo viên TD 1</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>TV tăng cường
-Giáo viên CN 10</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3555,26 +3555,26 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>TV tăng cường
 Giáo viên CN 10</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3591,8 +3591,8 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -3603,16 +3603,16 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
           <t>HĐTN
 Giáo viên CN 10</t>
         </is>
       </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 2</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -3689,19 +3689,19 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 11</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 11</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 11</t>
         </is>
       </c>
@@ -3757,25 +3757,25 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 11</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
         </is>
       </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 11</t>
+        </is>
+      </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 11</t>
         </is>
       </c>
@@ -3800,14 +3800,14 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Toán
+Giáo viên CN 11</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
 Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 11</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3829,26 +3829,26 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>TV tăng cường
+Giáo viên CN 11</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>TV tăng cường
-Giáo viên CN 11</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3865,26 +3865,26 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>Toán tăng cường
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>TV tăng cường
+Giáo viên CN 11</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 1</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>TV tăng cường
-Giáo viên CN 11</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>Đạo đức
 Giáo viên CN 11</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên BM 3</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3901,26 +3901,26 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 11</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 3</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 12</t>
         </is>
       </c>
@@ -4005,13 +4005,13 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 12</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 12</t>
         </is>
       </c>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 12</t>
         </is>
       </c>
@@ -4036,14 +4036,14 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 12</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 12</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4067,25 +4067,25 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 12</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 12</t>
-        </is>
-      </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 12</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 12</t>
         </is>
       </c>
@@ -4098,25 +4098,25 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 12</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 3</t>
+          <t>Toán
+Giáo viên CN 12</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 12</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 12</t>
         </is>
       </c>
@@ -4139,26 +4139,26 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>TV tăng cường
+Giáo viên CN 12</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 1</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>TV tăng cường
-Giáo viên CN 12</t>
-        </is>
-      </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Kỹ năng sống
 Giáo viên BM 3</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên BM 3</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4175,26 +4175,26 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t>TV tăng cường
+Giáo viên CN 12</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên BM 3</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>TV tăng cường
-Giáo viên CN 12</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Toán tăng cường
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4211,26 +4211,26 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 12</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
           <t>Đạo đức
 Giáo viên CN 12</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>TNXH
 Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 12</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 13</t>
         </is>
       </c>
@@ -4379,32 +4379,32 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>Toán
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>TNXH
 Giáo viên BM 3</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 13</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 3</t>
         </is>
       </c>
     </row>
@@ -4416,16 +4416,16 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>TNXH
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>TV tăng cường
 Giáo viên CN 13</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
@@ -4440,8 +4440,8 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 13</t>
         </is>
       </c>
     </row>
@@ -4453,20 +4453,20 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 13</t>
-        </is>
-      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 13</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán tăng cường
 Giáo viên CN 13</t>
         </is>
       </c>
@@ -4506,14 +4506,14 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 13</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 13</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -4530,26 +4530,26 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>TV tăng cường
-Giáo viên CN 13</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
         </is>
       </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ
+Giáo viên BM 3</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Toán tăng cường
 Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -4566,28 +4566,28 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>Đạo đức
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>Kỹ năng sống
 Giáo viên CN 13</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 13</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -4664,13 +4664,13 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 14</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 14</t>
         </is>
       </c>
@@ -4689,32 +4689,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 14</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 14</t>
-        </is>
-      </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 14</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
     </row>
@@ -4726,32 +4726,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 14</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>TV tăng cường
-Giáo viên CN 14</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 14</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
         </is>
       </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 14</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 14</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 14</t>
+        </is>
+      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
     </row>
@@ -4763,26 +4763,26 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>TNXH
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 14</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
       <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Công nghệ
 Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -4804,26 +4804,26 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 14</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 14</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên CN 14</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 14</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -4840,20 +4840,20 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>TV tăng cường
+Giáo viên CN 14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Toán tăng cường
+Giáo viên CN 14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4876,26 +4876,26 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Kỹ năng sống
 Giáo viên CN 14</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 14</t>
         </is>
       </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên CN 14</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 15</t>
         </is>
       </c>
@@ -4980,13 +4980,13 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 15</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 15</t>
         </is>
       </c>
@@ -4999,14 +4999,14 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Toán
+Giáo viên CN 15</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 15</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5017,13 +5017,13 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 15</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán tăng cường
 Giáo viên CN 15</t>
         </is>
       </c>
@@ -5036,32 +5036,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
           <t>TNXH
 Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 15</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 15</t>
         </is>
       </c>
     </row>
@@ -5073,26 +5073,26 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>Toán
 Giáo viên CN 15</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 15</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>Toán
 Giáo viên CN 15</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -5114,26 +5114,26 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 15</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên CN 15</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 15</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 15</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -5150,20 +5150,20 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
           <t>TV tăng cường
 Giáo viên CN 15</t>
         </is>
       </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 15</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -5192,14 +5192,14 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Đạo đức
+Giáo viên CN 15</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -5290,13 +5290,13 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 16</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 16</t>
         </is>
       </c>
@@ -5309,26 +5309,26 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 16</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 16</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 16</t>
-        </is>
-      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>TV tăng cường
-Giáo viên CN 16</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -5352,25 +5352,25 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 2</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 16</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 16</t>
         </is>
       </c>
@@ -5383,26 +5383,26 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Toán
+Giáo viên CN 16</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 16</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 16</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>TNXH
 Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 16</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -5424,26 +5424,26 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 16</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên CN 16</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 16</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -5460,20 +5460,20 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>TV tăng cường
+Giáo viên CN 16</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên CN 16</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên CN 16</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -5496,28 +5496,28 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên CN 16</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 16</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
           <t>Đạo đức
 Giáo viên CN 16</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 16</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên CN 16</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -5588,19 +5588,19 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 17</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 17</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 17</t>
         </is>
       </c>
@@ -5619,8 +5619,8 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Toán
+Giáo viên CN 17</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -5631,8 +5631,8 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 17</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5656,32 +5656,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 17</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 17</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Tin học
 Giáo viên TH 1</t>
         </is>
       </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 17</t>
+        </is>
+      </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
     </row>
@@ -5693,26 +5693,26 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 17</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 17</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 17</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -5734,26 +5734,26 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
 Giáo viên CN 17</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 17</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 17</t>
-        </is>
-      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -5770,26 +5770,26 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>Toán tăng cường
+Giáo viên CN 17</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>TV tăng cường
 Giáo viên CN 17</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
 Giáo viên CN 17</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên CN 17</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 4</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -5812,14 +5812,14 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
 Giáo viên CN 17</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 4</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 18</t>
         </is>
       </c>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 18</t>
         </is>
       </c>
@@ -5929,32 +5929,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 18</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 18</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 18</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 18</t>
-        </is>
-      </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 18</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
     </row>
@@ -5966,32 +5966,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 18</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>TNXH
 Giáo viên BM 4</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 18</t>
-        </is>
-      </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
     </row>
@@ -6003,26 +6003,26 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Toán
+Giáo viên CN 18</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
           <t>Toán
 Giáo viên CN 18</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -6050,8 +6050,8 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -6062,8 +6062,8 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 4</t>
+          <t>Toán tăng cường
+Giáo viên CN 18</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -6086,8 +6086,8 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 18</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -6098,8 +6098,8 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -6116,25 +6116,25 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Đạo đức
+Giáo viên CN 18</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>HĐTN
+Giáo viên CN 18</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
           <t>Kỹ năng sống
-Giáo viên CN 18</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
 Giáo viên CN 18</t>
         </is>
       </c>
@@ -6265,13 +6265,13 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 19</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 19</t>
         </is>
       </c>
@@ -6284,32 +6284,32 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>Toán
+Giáo viên CN 19</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 19</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 19</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 19</t>
-        </is>
-      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
     </row>
@@ -6321,31 +6321,31 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 19</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 19</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Âm nhạc
 Giáo viên ÂN 1</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 19</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 19</t>
         </is>
       </c>
@@ -6358,25 +6358,25 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 19</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Toán
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 19</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 19</t>
         </is>
       </c>
@@ -6399,25 +6399,25 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 19</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
           <t>Thể dục
 Giáo viên TD 2</t>
         </is>
       </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
-Giáo viên CN 19</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
+          <t>Lịch sử - Địa lý
 Giáo viên CN 19</t>
         </is>
       </c>
@@ -6435,26 +6435,26 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>Toán tăng cường
+Giáo viên CN 19</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
+Giáo viên CN 19</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>Kỹ năng sống
 Giáo viên QL 1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
 Giáo viên CN 19</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -6477,20 +6477,20 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>Đạo đức
 Giáo viên CN 19</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 19</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -6594,26 +6594,26 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 20</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 20</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
           <t>Thể dục
 Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 20</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 20</t>
         </is>
       </c>
@@ -6643,8 +6643,8 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 20</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6655,8 +6655,8 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
     </row>
@@ -6668,26 +6668,26 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 20</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 20</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 20</t>
-        </is>
-      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 20</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -6709,26 +6709,26 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>Toán tăng cường
+Giáo viên CN 20</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 20</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 20</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên CN 20</t>
-        </is>
-      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -6745,26 +6745,26 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Khoa học
+Giáo viên CN 20</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
 Giáo viên CN 20</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên QL 1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -6781,26 +6781,26 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>Đạo đức
+Giáo viên CN 20</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 20</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 20</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 20</t>
-        </is>
-      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>HĐTN
-Giáo viên CN 20</t>
+          <t>Kỹ năng sống
+Giáo viên QL 1</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -6873,13 +6873,13 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 21</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 21</t>
         </is>
       </c>
@@ -6891,7 +6891,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 21</t>
         </is>
       </c>
@@ -6904,32 +6904,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>Toán
+Giáo viên CN 21</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>Tin học
 Giáo viên TH 1</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 21</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 21</t>
-        </is>
-      </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 21</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
     </row>
@@ -6941,20 +6941,20 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 21</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
         </is>
       </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 21</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6965,8 +6965,8 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Toán
+Giáo viên CN 21</t>
         </is>
       </c>
     </row>
@@ -6984,20 +6984,20 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 21</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 21</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 21</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -7019,26 +7019,26 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
           <t>Khoa học
 Giáo viên CN 21</t>
         </is>
       </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 21</t>
+        </is>
+      </c>
       <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên CN 21</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 21</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -7055,26 +7055,26 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
+Giáo viên CN 21</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên CN 21</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
-Giáo viên CN 21</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -7091,19 +7091,19 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 21</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
           <t>Kỹ năng sống
 Giáo viên QL 1</t>
         </is>
       </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 21</t>
+        </is>
+      </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>HĐTN
+          <t>Đạo đức
 Giáo viên CN 21</t>
         </is>
       </c>
@@ -7214,8 +7214,8 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 22</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -7226,8 +7226,8 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 22</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7238,8 +7238,8 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 22</t>
         </is>
       </c>
     </row>
@@ -7251,8 +7251,8 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 22</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -7269,14 +7269,14 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 22</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 22</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
     </row>
@@ -7288,7 +7288,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 22</t>
         </is>
       </c>
@@ -7299,15 +7299,15 @@
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 22</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -7329,26 +7329,26 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
         </is>
       </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên CN 22</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
 Giáo viên CN 22</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -7365,25 +7365,25 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
           <t>Khoa học
 Giáo viên CN 22</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
-        </is>
-      </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
+          <t>Khoa học
 Giáo viên CN 22</t>
         </is>
       </c>
@@ -7401,22 +7401,22 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>Đạo đức
+Giáo viên CN 22</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên QL 1</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 22</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 22</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên QL 1</t>
-        </is>
-      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
           <t>HĐTN
@@ -7493,7 +7493,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 23</t>
         </is>
       </c>
@@ -7511,7 +7511,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 23</t>
         </is>
       </c>
@@ -7536,20 +7536,20 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 23</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 23</t>
-        </is>
-      </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
     </row>
@@ -7561,31 +7561,31 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
+          <t>Kỹ năng sống
 Giáo viên BM 4</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 23</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Thể dục
 Giáo viên TD 2</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 23</t>
         </is>
       </c>
@@ -7604,14 +7604,14 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 23</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -7645,20 +7645,20 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 23</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
           <t>Đạo đức
 Giáo viên CN 23</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 23</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -7675,8 +7675,8 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Toán tăng cường
+Giáo viên CN 23</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
+          <t>Khoa học
 Giáo viên CN 23</t>
         </is>
       </c>
@@ -7711,8 +7711,8 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -7723,16 +7723,16 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 23</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
           <t>HĐTN
 Giáo viên CN 23</t>
         </is>
       </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -7809,7 +7809,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 24</t>
         </is>
       </c>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 24</t>
         </is>
       </c>
@@ -7846,14 +7846,14 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 24</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -7871,26 +7871,26 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
-        </is>
-      </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 24</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 24</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 24</t>
         </is>
       </c>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Toán tăng cường
 Giáo viên CN 24</t>
         </is>
       </c>
@@ -7949,20 +7949,20 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>Khoa học
 Giáo viên CN 24</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -7985,26 +7985,26 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 24</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Thể dục
 Giáo viên TD 3</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Đạo đức
 Giáo viên CN 24</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -8021,26 +8021,26 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 24</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 24</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 24</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
           <t>Âm nhạc
 Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 24</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 24</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 24</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -8164,7 +8164,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 25</t>
         </is>
       </c>
@@ -8189,32 +8189,32 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 25</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 25</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 25</t>
-        </is>
-      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 25</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 25</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
     </row>
@@ -8238,20 +8238,20 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 25</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
           <t>Kỹ năng sống
 Giáo viên BM 4</t>
         </is>
       </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 25</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Toán
+Giáo viên CN 25</t>
         </is>
       </c>
     </row>
@@ -8263,26 +8263,26 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 25</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
-        </is>
-      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
+          <t>Toán
 Giáo viên CN 25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên BM 5</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -8304,20 +8304,20 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>Âm nhạc
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>Khoa học
 Giáo viên CN 25</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8346,8 +8346,8 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Toán tăng cường
+Giáo viên CN 25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -8358,7 +8358,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
+          <t>Đạo đức
 Giáo viên CN 25</t>
         </is>
       </c>
@@ -8376,16 +8376,16 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 25</t>
         </is>
       </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
+        </is>
+      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
           <t>HĐTN
@@ -8394,7 +8394,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Lịch sử - Địa lý
 Giáo viên CN 25</t>
         </is>
       </c>
@@ -8474,7 +8474,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 26</t>
         </is>
       </c>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 26</t>
         </is>
       </c>
@@ -8499,20 +8499,20 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 26</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 26</t>
         </is>
       </c>
@@ -8536,7 +8536,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 26</t>
         </is>
       </c>
@@ -8548,8 +8548,8 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 26</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8573,19 +8573,19 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
+          <t>Tiếng Việt
 Giáo viên CN 26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 26</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 26</t>
         </is>
       </c>
@@ -8614,26 +8614,26 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>Khoa học
 Giáo viên CN 26</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
 Giáo viên CN 26</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Toán tăng cường
+Giáo viên CN 26</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -8650,26 +8650,26 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>Khoa học
+Giáo viên CN 26</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 26</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 26</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -8686,20 +8686,20 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
+          <t>Âm nhạc
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
+          <t>Đạo đức
 Giáo viên CN 26</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 26</t>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8778,7 +8778,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 27</t>
         </is>
       </c>
@@ -8796,7 +8796,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 27</t>
         </is>
       </c>
@@ -8809,31 +8809,31 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 27</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 27</t>
-        </is>
-      </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 27</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 27</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 27</t>
         </is>
       </c>
@@ -8846,32 +8846,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 27</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 27</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 27</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 27</t>
         </is>
       </c>
     </row>
@@ -8883,26 +8883,26 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 27</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Toán
+Giáo viên CN 27</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên BM 5</t>
+          <t>Tiếng Việt
+Giáo viên CN 27</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 27</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -8924,20 +8924,20 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 27</t>
+          <t>Âm nhạc
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8960,26 +8960,26 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
           <t>Khoa học
 Giáo viên CN 27</t>
         </is>
       </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
+        </is>
+      </c>
       <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên CN 27</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>Khoa học
 Giáo viên CN 27</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -8996,28 +8996,28 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 27</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 27</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 27</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 27</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 28</t>
         </is>
       </c>
@@ -9100,13 +9100,13 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 28</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Khoa học
 Giáo viên CN 28</t>
         </is>
       </c>
@@ -9119,32 +9119,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 28</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 28</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 28</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 28</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
         </is>
       </c>
     </row>
@@ -9156,26 +9156,26 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 28</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 5</t>
+          <t>Tiếng Việt
+Giáo viên CN 28</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 28</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Tin học
 Giáo viên TH 1</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 28</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -9193,26 +9193,26 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên BM 5</t>
+          <t>Tiếng Việt
+Giáo viên CN 28</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 28</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -9234,25 +9234,25 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>Toán tăng cường
+Giáo viên CN 28</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 28</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
+          <t>Mỹ thuật
 Giáo viên BM 5</t>
         </is>
       </c>
@@ -9270,26 +9270,26 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 28</t>
+          <t>Kỹ năng sống
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>Khoa học
 Giáo viên CN 28</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 28</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -9312,22 +9312,22 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
+          <t>HĐTN
+Giáo viên CN 28</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 28</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Đạo đức
 Giáo viên CN 28</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 28</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 29</t>
         </is>
       </c>
@@ -9429,26 +9429,26 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Kỹ năng sống
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 29</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 29</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -9472,19 +9472,19 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 29</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 29</t>
-        </is>
-      </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
+          <t>Âm nhạc
 Giáo viên BM 5</t>
         </is>
       </c>
@@ -9503,25 +9503,25 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 29</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 29</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 29</t>
         </is>
       </c>
@@ -9544,26 +9544,26 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
+          <t>Khoa học
+Giáo viên CN 29</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên BM 5</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
+Giáo viên CN 29</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -9580,26 +9580,26 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 29</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ
 Giáo viên BM 5</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
 Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 29</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 29</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -9616,7 +9616,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Lịch sử - Địa lý
 Giáo viên CN 29</t>
         </is>
       </c>
@@ -9634,8 +9634,8 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 29</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">

--- a/data/Output_Template_TKB_V8.xlsx
+++ b/data/Output_Template_TKB_V8.xlsx
@@ -569,25 +569,25 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
         </is>
       </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 1</t>
+        </is>
+      </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
+          <t>TNXH
 Giáo viên BM 1</t>
         </is>
       </c>
@@ -649,14 +649,14 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 1</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -684,8 +684,8 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Kỹ năng sống
 Giáo viên BM 1</t>
         </is>
       </c>
@@ -756,14 +756,14 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>TNXH
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 2</t>
         </is>
       </c>
@@ -897,8 +897,8 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 2</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 2</t>
         </is>
       </c>
@@ -971,8 +971,8 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Kỹ năng sống
 Giáo viên BM 1</t>
         </is>
       </c>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
+          <t>TNXH
 Giáo viên BM 1</t>
         </is>
       </c>
@@ -1189,8 +1189,8 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 3</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1238,8 +1238,8 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1263,14 +1263,14 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 3</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1304,8 +1304,8 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1340,20 +1340,20 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 3</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
 Giáo viên CN 3</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 1</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1376,22 +1376,22 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 3</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 3</t>
         </is>
       </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 1</t>
+        </is>
+      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>TNXH
@@ -1468,7 +1468,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 4</t>
         </is>
       </c>
@@ -1499,26 +1499,26 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>TNXH
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 4</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 4</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 4</t>
-        </is>
-      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1536,14 +1536,14 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 4</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -1573,20 +1573,20 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 4</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 4</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 1</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Tiếng Việt
 Giáo viên CN 4</t>
         </is>
       </c>
@@ -1650,8 +1650,8 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 4</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1686,8 +1686,8 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 1</t>
+          <t>Đạo đức
+Giáo viên CN 4</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1698,16 +1698,16 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
           <t>HĐTN
 Giáo viên CN 4</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 5</t>
         </is>
       </c>
@@ -1815,8 +1815,8 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 2</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -1858,8 +1858,8 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 5</t>
         </is>
       </c>
@@ -1924,8 +1924,8 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -1936,8 +1936,8 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -1960,8 +1960,8 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -1972,8 +1972,8 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Kỹ năng sống
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -1996,8 +1996,8 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2008,8 +2008,8 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 1</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -2119,20 +2119,20 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>TNXH
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 6</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 6</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -2156,8 +2156,8 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 6</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2193,26 +2193,26 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 6</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
+          <t>Tiếng Việt
+Giáo viên CN 6</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
 Giáo viên BM 2</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 6</t>
-        </is>
-      </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2234,8 +2234,8 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 6</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -2252,8 +2252,8 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 2</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2270,8 +2270,8 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 6</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -2306,20 +2306,20 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 2</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Đạo đức
 Giáo viên CN 6</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 7</t>
         </is>
       </c>
@@ -2517,14 +2517,14 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 7</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2554,8 +2554,8 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Toán
+Giáo viên CN 7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2589,20 +2589,20 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên BM 2</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 7</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên BM 2</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Toán tăng cường
 Giáo viên BM 2</t>
         </is>
       </c>
@@ -2661,28 +2661,28 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Kỹ năng sống
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 7</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 7</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>TNXH
 Giáo viên BM 2</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 7</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -2753,19 +2753,19 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 8</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 8</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 8</t>
         </is>
       </c>
@@ -2790,14 +2790,14 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 8</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2821,25 +2821,25 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 8</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>TNXH
 Giáo viên BM 2</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 8</t>
-        </is>
-      </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 8</t>
         </is>
       </c>
@@ -2864,20 +2864,20 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2905,20 +2905,20 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>TV tăng cường
+Giáo viên CN 8</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên BM 2</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>TV tăng cường
-Giáo viên CN 8</t>
-        </is>
-      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2941,14 +2941,14 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
           <t>TV tăng cường
 Giáo viên CN 8</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2977,16 +2977,16 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>HĐTN
 Giáo viên CN 8</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Mỹ thuật
@@ -3069,7 +3069,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 9</t>
         </is>
       </c>
@@ -3094,20 +3094,20 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 9</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 9</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 9</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3131,8 +3131,8 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 9</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3143,8 +3143,8 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 9</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3168,19 +3168,19 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>Toán
+Giáo viên CN 9</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>TNXH
 Giáo viên BM 2</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 9</t>
-        </is>
-      </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 9</t>
         </is>
       </c>
@@ -3209,20 +3209,20 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 9</t>
+          <t>Toán tăng cường
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,8 +3245,8 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 9</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3257,7 +3257,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
+          <t>Kỹ năng sống
 Giáo viên BM 2</t>
         </is>
       </c>
@@ -3281,22 +3281,22 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>Đạo đức
 Giáo viên CN 9</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>HĐTN
@@ -3373,7 +3373,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 10</t>
         </is>
       </c>
@@ -3391,7 +3391,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 10</t>
         </is>
       </c>
@@ -3410,8 +3410,8 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 10</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -3447,8 +3447,8 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 10</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 10</t>
         </is>
       </c>
@@ -3484,7 +3484,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 10</t>
         </is>
       </c>
@@ -3519,26 +3519,26 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
           <t>TV tăng cường
 Giáo viên CN 10</t>
         </is>
       </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 10</t>
+        </is>
+      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Kỹ năng sống
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3555,20 +3555,20 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
           <t>TV tăng cường
 Giáo viên CN 10</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -3591,26 +3591,26 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 10</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 10</t>
         </is>
       </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 2</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 11</t>
         </is>
       </c>
@@ -3763,8 +3763,8 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Toán
+Giáo viên CN 11</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 11</t>
         </is>
       </c>
@@ -3800,8 +3800,8 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 11</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -3829,20 +3829,20 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>TV tăng cường
 Giáo viên CN 11</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -3865,26 +3865,26 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
+          <t>TNXH
 Giáo viên BM 3</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>TV tăng cường
 Giáo viên CN 11</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 11</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3901,26 +3901,26 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 11</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>TNXH
 Giáo viên BM 3</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
 Giáo viên CN 11</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 12</t>
         </is>
       </c>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Kỹ năng sống
 Giáo viên BM 3</t>
         </is>
       </c>
@@ -4098,7 +4098,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 12</t>
         </is>
       </c>
@@ -4110,8 +4110,8 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -4139,20 +4139,20 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>Toán tăng cường
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
           <t>TV tăng cường
 Giáo viên CN 12</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 3</t>
+          <t>Đạo đức
+Giáo viên CN 12</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -4175,20 +4175,20 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
           <t>TV tăng cường
 Giáo viên CN 12</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên BM 3</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -4223,8 +4223,8 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 12</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 13</t>
         </is>
       </c>
@@ -4379,8 +4379,8 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 13</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -4422,25 +4422,25 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>TV tăng cường
-Giáo viên CN 13</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 13</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 13</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
 Giáo viên CN 13</t>
         </is>
       </c>
@@ -4453,14 +4453,14 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Toán
+Giáo viên CN 13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Công nghệ
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4506,8 +4506,8 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4536,8 +4536,8 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 3</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 14</t>
         </is>
       </c>
@@ -4689,8 +4689,8 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 14</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -4726,20 +4726,20 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>Toán
+Giáo viên CN 14</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 14</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 14</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 14</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4775,8 +4775,8 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 3</t>
+          <t>Toán
+Giáo viên CN 14</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4810,14 +4810,14 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 14</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Công nghệ
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4888,16 +4888,16 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
+          <t>Đạo đức
+Giáo viên CN 14</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 2</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -4968,13 +4968,13 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 15</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 15</t>
         </is>
       </c>
@@ -5011,8 +5011,8 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 15</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5042,14 +5042,14 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 15</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 15</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5079,13 +5079,13 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 15</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 15</t>
         </is>
       </c>
@@ -5120,14 +5120,14 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
           <t>Toán tăng cường
 Giáo viên CN 15</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -5156,14 +5156,14 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -5192,16 +5192,16 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>Đạo đức
 Giáo viên CN 15</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 3</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>HĐTN
@@ -5284,7 +5284,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 16</t>
         </is>
       </c>
@@ -5309,8 +5309,8 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -5321,8 +5321,8 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 16</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -5346,20 +5346,20 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
         </is>
       </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 16</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 16</t>
         </is>
       </c>
@@ -5430,14 +5430,14 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
           <t>TNXH
 Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -5472,8 +5472,8 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -5496,8 +5496,8 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 17</t>
         </is>
       </c>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 17</t>
         </is>
       </c>
@@ -5631,13 +5631,13 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 17</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>TV tăng cường
 Giáo viên CN 17</t>
         </is>
       </c>
@@ -5662,19 +5662,19 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 17</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 17</t>
         </is>
       </c>
@@ -5699,14 +5699,14 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Toán
+Giáo viên CN 17</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 4</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5740,13 +5740,13 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
-Giáo viên CN 17</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
 Giáo viên CN 17</t>
         </is>
       </c>
@@ -5782,8 +5782,8 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>TV tăng cường
-Giáo viên CN 17</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5806,22 +5806,22 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 17</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 2</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 17</t>
-        </is>
-      </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
           <t>HĐTN
@@ -5898,7 +5898,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 18</t>
         </is>
       </c>
@@ -5929,8 +5929,8 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -5966,16 +5966,16 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>Toán
+Giáo viên CN 18</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 2</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 18</t>
-        </is>
-      </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
@@ -5984,7 +5984,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Công nghệ
 Giáo viên BM 4</t>
         </is>
       </c>
@@ -6003,20 +6003,20 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
           <t>Toán
 Giáo viên CN 18</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Toán
+Giáo viên CN 18</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6050,14 +6050,14 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 18</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6086,19 +6086,19 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
           <t>Toán tăng cường
 Giáo viên CN 18</t>
         </is>
       </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
+          <t>TNXH
 Giáo viên BM 4</t>
         </is>
       </c>
@@ -6122,14 +6122,14 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
           <t>HĐTN
 Giáo viên CN 18</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 4</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6296,20 +6296,20 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Toán
+Giáo viên CN 19</t>
         </is>
       </c>
     </row>
@@ -6321,32 +6321,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 19</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 19</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Mỹ thuật
 Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 19</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 19</t>
         </is>
       </c>
     </row>
@@ -6358,14 +6358,14 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 19</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6399,20 +6399,20 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Kỹ năng sống
+Giáo viên QL 1</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Tin học
 Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
+Giáo viên CN 19</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6435,20 +6435,20 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên CN 19</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 19</t>
-        </is>
-      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên QL 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6477,16 +6477,16 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>Đạo đức
+Giáo viên CN 19</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>Công nghệ
 Giáo viên BM 4</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 19</t>
-        </is>
-      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>HĐTN
@@ -6563,7 +6563,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 20</t>
         </is>
       </c>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 20</t>
         </is>
       </c>
@@ -6594,20 +6594,20 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Toán
+Giáo viên CN 20</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 20</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 20</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6618,8 +6618,8 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 20</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
     </row>
@@ -6631,32 +6631,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 20</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 20</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 20</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 20</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
         </is>
       </c>
     </row>
@@ -6674,14 +6674,14 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>Toán
+Giáo viên CN 20</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 20</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6709,20 +6709,20 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 20</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 20</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
+Giáo viên CN 20</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6745,20 +6745,20 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Toán tăng cường
+Giáo viên CN 20</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
 Giáo viên CN 20</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6781,22 +6781,22 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 20</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 20</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>Đạo đức
 Giáo viên CN 20</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 20</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 20</t>
-        </is>
-      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Kỹ năng sống
@@ -6891,7 +6891,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 21</t>
         </is>
       </c>
@@ -6904,16 +6904,16 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 21</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
         </is>
       </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Tin học
@@ -6928,8 +6928,8 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
     </row>
@@ -6941,31 +6941,31 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Toán
+Giáo viên CN 21</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 21</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 21</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 21</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 21</t>
         </is>
       </c>
@@ -7019,19 +7019,19 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>Toán tăng cường
+Giáo viên CN 21</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>Khoa học
 Giáo viên CN 21</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 21</t>
-        </is>
-      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
+          <t>Khoa học
 Giáo viên CN 21</t>
         </is>
       </c>
@@ -7061,20 +7061,20 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
-Giáo viên CN 21</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
         </is>
       </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 21</t>
+        </is>
+      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 21</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -7091,26 +7091,26 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>Đạo đức
+Giáo viên CN 21</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>Kỹ năng sống
 Giáo viên QL 1</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 21</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 21</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 21</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -7214,20 +7214,20 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 22</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
           <t>Mỹ thuật
 Giáo viên MT 1</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 22</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 22</t>
         </is>
       </c>
@@ -7288,20 +7288,20 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 22</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 22</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -7341,8 +7341,8 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -7365,20 +7365,20 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Khoa học
 Giáo viên CN 22</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -7407,16 +7407,16 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 22</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>Kỹ năng sống
 Giáo viên QL 1</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 22</t>
-        </is>
-      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
           <t>HĐTN
@@ -7493,13 +7493,13 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 23</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 23</t>
         </is>
       </c>
@@ -7530,26 +7530,26 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 23</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 23</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Thể dục
 Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 23</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
         </is>
       </c>
     </row>
@@ -7561,20 +7561,20 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 23</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
           <t>Mỹ thuật
 Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 23</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -7604,13 +7604,13 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 23</t>
         </is>
       </c>
@@ -7639,20 +7639,20 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>Toán tăng cường
+Giáo viên CN 23</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
           <t>Khoa học
 Giáo viên CN 23</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 23</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -7675,20 +7675,20 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 23</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
           <t>Khoa học
 Giáo viên CN 23</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 23</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -7717,16 +7717,16 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
+          <t>HĐTN
+Giáo viên CN 23</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 23</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 23</t>
-        </is>
-      </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
           <t>Công nghệ
@@ -7803,13 +7803,13 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 24</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 24</t>
         </is>
       </c>
@@ -7834,25 +7834,25 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 24</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 24</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
+          <t>Âm nhạc
 Giáo viên BM 5</t>
         </is>
       </c>
@@ -7871,8 +7871,8 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 24</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -7883,8 +7883,8 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 24</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -7908,19 +7908,19 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 24</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 24</t>
-        </is>
-      </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
+          <t>Toán
 Giáo viên CN 24</t>
         </is>
       </c>
@@ -7949,19 +7949,19 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Khoa học
+Giáo viên CN 24</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
+          <t>Toán tăng cường
 Giáo viên CN 24</t>
         </is>
       </c>
@@ -7985,20 +7985,20 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 24</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Thể dục
 Giáo viên TD 3</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 24</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -8033,13 +8033,13 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
+          <t>Đạo đức
 Giáo viên CN 24</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
+          <t>Mỹ thuật
 Giáo viên BM 5</t>
         </is>
       </c>
@@ -8164,7 +8164,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 25</t>
         </is>
       </c>
@@ -8189,20 +8189,20 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 25</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
         </is>
       </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
+        </is>
+      </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 25</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -8213,8 +8213,8 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Toán
+Giáo viên CN 25</t>
         </is>
       </c>
     </row>
@@ -8238,20 +8238,20 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
+          <t>Tiếng Việt
+Giáo viên CN 25</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 25</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ
 Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 25</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 25</t>
         </is>
       </c>
     </row>
@@ -8263,8 +8263,8 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -8275,7 +8275,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 25</t>
         </is>
       </c>
@@ -8304,8 +8304,8 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên BM 5</t>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -8316,8 +8316,8 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Toán tăng cường
+Giáo viên CN 25</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8346,8 +8346,8 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 25</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -8382,7 +8382,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
+          <t>Âm nhạc
 Giáo viên BM 5</t>
         </is>
       </c>
@@ -8499,14 +8499,14 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 26</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -8548,20 +8548,20 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 26</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
           <t>Công nghệ
 Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 26</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
     </row>
@@ -8573,14 +8573,14 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 26</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -8614,20 +8614,20 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
+Giáo viên CN 26</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 26</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 26</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8650,20 +8650,20 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 26</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>Khoa học
 Giáo viên CN 26</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 26</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8686,22 +8686,22 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 26</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 26</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>Âm nhạc
 Giáo viên BM 5</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 26</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
-        </is>
-      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
           <t>HĐTN
@@ -8778,7 +8778,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 27</t>
         </is>
       </c>
@@ -8796,7 +8796,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 27</t>
         </is>
       </c>
@@ -8809,32 +8809,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Toán
+Giáo viên CN 27</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 27</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Thể dục
 Giáo viên TD 3</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 27</t>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
         </is>
       </c>
     </row>
@@ -8846,14 +8846,14 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 27</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -8870,8 +8870,8 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 27</t>
         </is>
       </c>
     </row>
@@ -8889,14 +8889,14 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 27</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 27</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8924,8 +8924,8 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Khoa học
+Giáo viên CN 27</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -8936,8 +8936,8 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên BM 5</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8960,20 +8960,20 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
+          <t>Toán tăng cường
 Giáo viên CN 27</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Mỹ thuật
 Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên CN 27</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9002,22 +9002,22 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 27</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>HĐTN
 Giáo viên CN 27</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 27</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 27</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 28</t>
         </is>
       </c>
@@ -9106,7 +9106,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
+          <t>Toán
 Giáo viên CN 28</t>
         </is>
       </c>
@@ -9119,8 +9119,8 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -9143,7 +9143,7 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 28</t>
         </is>
       </c>
@@ -9162,8 +9162,8 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 28</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -9180,8 +9180,8 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 28</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
     </row>
@@ -9199,8 +9199,8 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Toán
+Giáo viên CN 28</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -9234,8 +9234,8 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 28</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -9246,8 +9246,8 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Khoa học
+Giáo viên CN 28</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9276,14 +9276,14 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
           <t>Thể dục
 Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên CN 28</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9312,13 +9312,13 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 28</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>HĐTN
-Giáo viên CN 28</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
 Giáo viên CN 28</t>
         </is>
       </c>
@@ -9429,20 +9429,20 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
+          <t>Công nghệ
 Giáo viên BM 5</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
+          <t>Tiếng Việt
+Giáo viên CN 29</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 29</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -9472,8 +9472,8 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -9509,14 +9509,14 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 29</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 29</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -9556,8 +9556,8 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
-Giáo viên CN 29</t>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -9580,20 +9580,20 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 29</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Lịch sử - Địa lý
 Giáo viên CN 29</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 5</t>
+          <t>Khoa học
+Giáo viên CN 29</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -9616,19 +9616,19 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
+          <t>Kỹ năng sống
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
 Giáo viên CN 29</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>HĐTN
-Giáo viên CN 29</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
 Giáo viên CN 29</t>
         </is>
       </c>

--- a/data/Output_Template_TKB_V8.xlsx
+++ b/data/Output_Template_TKB_V8.xlsx
@@ -464,7 +464,7 @@
   <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10.5" customWidth="1" min="1" max="1"/>
+    <col width="5.7" customWidth="1" min="1" max="1"/>
     <col width="12.1" customWidth="1" min="2" max="2"/>
     <col width="10.9" customWidth="1" min="3" max="3"/>
     <col width="21.5" customWidth="1" min="4" max="4"/>
@@ -519,7 +519,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>LỚP 1/1</t>
+          <t>1/1</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
@@ -829,7 +829,7 @@
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>LỚP 1/2</t>
+          <t>1/2</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
@@ -1139,7 +1139,7 @@
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>LỚP 1/3</t>
+          <t>1/3</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
@@ -1449,7 +1449,7 @@
     <row r="32" ht="42" customHeight="1">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>LỚP 1/4</t>
+          <t>1/4</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
@@ -1759,7 +1759,7 @@
     <row r="42" ht="42" customHeight="1">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>LỚP 1/5</t>
+          <t>1/5</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
@@ -2069,7 +2069,7 @@
     <row r="52" ht="42" customHeight="1">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>LỚP 1/6</t>
+          <t>1/6</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
@@ -2369,7 +2369,7 @@
   <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10.5" customWidth="1" min="1" max="1"/>
+    <col width="5.7" customWidth="1" min="1" max="1"/>
     <col width="12.1" customWidth="1" min="2" max="2"/>
     <col width="10.9" customWidth="1" min="3" max="3"/>
     <col width="21.5" customWidth="1" min="4" max="4"/>
@@ -2424,7 +2424,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>LỚP 2/1</t>
+          <t>2/1</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
@@ -2734,7 +2734,7 @@
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>LỚP 2/2</t>
+          <t>2/2</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
@@ -3044,7 +3044,7 @@
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>LỚP 2/3</t>
+          <t>2/3</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
@@ -3354,7 +3354,7 @@
     <row r="32" ht="42" customHeight="1">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>LỚP 2/4</t>
+          <t>2/4</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
@@ -3664,7 +3664,7 @@
     <row r="42" ht="42" customHeight="1">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>LỚP 2/5</t>
+          <t>2/5</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
@@ -3974,7 +3974,7 @@
     <row r="52" ht="42" customHeight="1">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>LỚP 2/6</t>
+          <t>2/6</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
@@ -4274,7 +4274,7 @@
   <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10.5" customWidth="1" min="1" max="1"/>
+    <col width="5.7" customWidth="1" min="1" max="1"/>
     <col width="12.1" customWidth="1" min="2" max="2"/>
     <col width="10.9" customWidth="1" min="3" max="3"/>
     <col width="21.5" customWidth="1" min="4" max="4"/>
@@ -4329,7 +4329,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>LỚP 3/1</t>
+          <t>3/1</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
@@ -4639,7 +4639,7 @@
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>LỚP 3/2</t>
+          <t>3/2</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
@@ -4949,7 +4949,7 @@
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>LỚP 3/3</t>
+          <t>3/3</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
@@ -5259,7 +5259,7 @@
     <row r="32" ht="42" customHeight="1">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>LỚP 3/4</t>
+          <t>3/4</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
@@ -5569,7 +5569,7 @@
     <row r="42" ht="42" customHeight="1">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>LỚP 3/5</t>
+          <t>3/5</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
@@ -5879,7 +5879,7 @@
     <row r="52" ht="42" customHeight="1">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>LỚP 3/6</t>
+          <t>3/6</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
@@ -6179,7 +6179,7 @@
   <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10.5" customWidth="1" min="1" max="1"/>
+    <col width="5.7" customWidth="1" min="1" max="1"/>
     <col width="12.1" customWidth="1" min="2" max="2"/>
     <col width="10.9" customWidth="1" min="3" max="3"/>
     <col width="21.5" customWidth="1" min="4" max="4"/>
@@ -6234,7 +6234,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>LỚP 4/1</t>
+          <t>4/1</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
@@ -6544,7 +6544,7 @@
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>LỚP 4/2</t>
+          <t>4/2</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
@@ -6854,7 +6854,7 @@
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>LỚP 4/3</t>
+          <t>4/3</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
@@ -7164,7 +7164,7 @@
     <row r="32" ht="42" customHeight="1">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>LỚP 4/4</t>
+          <t>4/4</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
@@ -7474,7 +7474,7 @@
     <row r="42" ht="42" customHeight="1">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>LỚP 4/5</t>
+          <t>4/5</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
@@ -7784,7 +7784,7 @@
     <row r="52" ht="42" customHeight="1">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>LỚP 4/6</t>
+          <t>4/6</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
@@ -8084,7 +8084,7 @@
   <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10.5" customWidth="1" min="1" max="1"/>
+    <col width="5.7" customWidth="1" min="1" max="1"/>
     <col width="12.1" customWidth="1" min="2" max="2"/>
     <col width="10.9" customWidth="1" min="3" max="3"/>
     <col width="21.5" customWidth="1" min="4" max="4"/>
@@ -8139,7 +8139,7 @@
     <row r="2" ht="42" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>LỚP 5/1</t>
+          <t>5/1</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
@@ -8449,7 +8449,7 @@
     <row r="12" ht="42" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>LỚP 5/2</t>
+          <t>5/2</t>
         </is>
       </c>
       <c r="B12" s="1" t="inlineStr">
@@ -8759,7 +8759,7 @@
     <row r="22" ht="42" customHeight="1">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>LỚP 5/3</t>
+          <t>5/3</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
@@ -9069,7 +9069,7 @@
     <row r="32" ht="42" customHeight="1">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>LỚP 5/4</t>
+          <t>5/4</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
@@ -9379,7 +9379,7 @@
     <row r="42" ht="42" customHeight="1">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>LỚP 5/5</t>
+          <t>5/5</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">

--- a/data/Output_Template_TKB_V8.xlsx
+++ b/data/Output_Template_TKB_V8.xlsx
@@ -569,8 +569,8 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 1</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -580,15 +580,15 @@
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Âm nhạc
 Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 1</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -643,14 +643,14 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 1</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -702,8 +702,8 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -756,28 +756,28 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
           <t>Mỹ thuật
 Giáo viên MT 1</t>
         </is>
       </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 1</t>
+        </is>
+      </c>
       <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 1</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 1</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -854,7 +854,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 2</t>
         </is>
       </c>
@@ -879,32 +879,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 2</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 2</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
         </is>
       </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 2</t>
+        </is>
+      </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên CN 2</t>
+Giáo viên BM 1</t>
         </is>
       </c>
     </row>
@@ -916,19 +916,19 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 2</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Toán
+Giáo viên CN 2</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 2</t>
         </is>
       </c>
@@ -941,7 +941,7 @@
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên CN 2</t>
+Giáo viên BM 1</t>
         </is>
       </c>
     </row>
@@ -953,20 +953,20 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 2</t>
+          <t>TNXH
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 2</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 2</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -995,13 +995,13 @@
       <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên BM 1</t>
+Giáo viên CN 2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 1</t>
+          <t>Đạo đức
+Giáo viên CN 2</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1012,8 +1012,8 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 2</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên BM 1</t>
+Giáo viên CN 2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1048,8 +1048,8 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1066,20 +1066,20 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 2</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
           <t>Thể dục
 Giáo viên TD 3</t>
         </is>
       </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 1</t>
+        </is>
+      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1189,32 +1189,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 3</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 3</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 3</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 3</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1233,7 @@
       <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên CN 3</t>
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1251,7 +1251,7 @@
       <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên BM 1</t>
+Giáo viên CN 3</t>
         </is>
       </c>
     </row>
@@ -1263,14 +1263,14 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 3</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1304,8 +1304,8 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Kỹ năng sống
 Giáo viên BM 1</t>
         </is>
       </c>
@@ -1340,8 +1340,8 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1352,8 +1352,8 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 3</t>
+          <t>TNXH
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1376,20 +1376,20 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>Đạo đức
+Giáo viên CN 3</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 3</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 3</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 1</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1499,8 +1499,8 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 4</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -1523,8 +1523,8 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 4</t>
         </is>
       </c>
     </row>
@@ -1536,32 +1536,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
+          <t>Tiếng Việt
+Giáo viên CN 4</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 4</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 4</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên BM 1</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 4</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 4</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
         </is>
       </c>
     </row>
@@ -1585,8 +1585,8 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -1614,14 +1614,14 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 4</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 4</t>
+          <t>Kỹ năng sống
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -1650,14 +1650,14 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 4</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 4</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -1686,28 +1686,28 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 4</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
           <t>Đạo đức
 Giáo viên CN 4</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 4</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -1778,19 +1778,19 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 5</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 5</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 5</t>
         </is>
       </c>
@@ -1809,14 +1809,14 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 5</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 5</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -1852,20 +1852,20 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 5</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 5</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -1883,26 +1883,26 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 5</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
+          <t>Toán
+Giáo viên CN 5</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
           <t>Toán
 Giáo viên CN 5</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 2</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -1924,26 +1924,26 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Tiếng Việt
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 5</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 5</t>
+          <t>Kỹ năng sống
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -1960,26 +1960,26 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 5</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 5</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 5</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -1996,26 +1996,26 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 5</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Đạo đức
 Giáo viên CN 5</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>TNXH
 Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 5</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2119,20 +2119,20 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 6</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>TNXH
 Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 6</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -2156,8 +2156,8 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 6</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2205,14 +2205,14 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 6</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2234,26 +2234,26 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 6</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 6</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 6</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 6</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 6</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2270,26 +2270,26 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 6</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 6</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 6</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -2306,26 +2306,26 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Đạo đức
+Giáo viên CN 6</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 6</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Thể dục
 Giáo viên TD 1</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 6</t>
-        </is>
-      </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>HĐTN
-Giáo viên CN 6</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 7</t>
         </is>
       </c>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 7</t>
         </is>
       </c>
@@ -2511,26 +2511,26 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 7</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>TNXH
 Giáo viên BM 2</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -2548,14 +2548,14 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 7</t>
+          <t>Toán tăng cường
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 7</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2589,26 +2589,26 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 7</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>TV tăng cường
+Giáo viên CN 7</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>Âm nhạc
 Giáo viên ÂN 1</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>TV tăng cường
-Giáo viên CN 7</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -2625,26 +2625,26 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 7</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>TV tăng cường
+Giáo viên CN 7</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên BM 2</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>TV tăng cường
-Giáo viên CN 7</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -2661,28 +2661,28 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 7</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>Kỹ năng sống
 Giáo viên BM 2</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 7</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 7</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 2</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 8</t>
         </is>
       </c>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 8</t>
         </is>
       </c>
@@ -2784,14 +2784,14 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -2802,8 +2802,8 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 8</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -2821,8 +2821,8 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 8</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -2833,8 +2833,8 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 8</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 8</t>
         </is>
       </c>
@@ -2858,8 +2858,8 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Toán
+Giáo viên CN 8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2870,14 +2870,14 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Toán tăng cường
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 8</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2899,8 +2899,8 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 8</t>
+          <t>Kỹ năng sống
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2911,14 +2911,14 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
+          <t>TNXH
 Giáo viên BM 2</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2935,8 +2935,8 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 8</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2947,8 +2947,8 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2971,28 +2971,28 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>Đạo đức
 Giáo viên CN 8</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 8</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 9</t>
         </is>
       </c>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 9</t>
         </is>
       </c>
@@ -3106,8 +3106,8 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3137,25 +3137,25 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 9</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 9</t>
-        </is>
-      </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Kỹ năng sống
 Giáo viên BM 2</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 9</t>
         </is>
       </c>
@@ -3174,8 +3174,8 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 2</t>
+          <t>Toán
+Giáo viên CN 9</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3209,26 +3209,26 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>TV tăng cường
+Giáo viên CN 9</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>TV tăng cường
-Giáo viên CN 9</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3245,26 +3245,26 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
           <t>Toán tăng cường
 Giáo viên BM 2</t>
         </is>
       </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 9</t>
+        </is>
+      </c>
       <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>TV tăng cường
 Giáo viên CN 9</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3281,20 +3281,20 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Âm nhạc
 Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 9</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3422,8 +3422,8 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 10</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -3447,14 +3447,14 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 1</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 3</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -3496,8 +3496,8 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 10</t>
+          <t>Toán tăng cường
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3519,26 +3519,26 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
           <t>TV tăng cường
 Giáo viên CN 10</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 10</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 2</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3555,26 +3555,26 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
           <t>TV tăng cường
 Giáo viên CN 10</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3591,28 +3591,28 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>Đạo đức
+Giáo viên CN 10</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>TNXH
 Giáo viên BM 3</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 10</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -3689,19 +3689,19 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 11</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 11</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 11</t>
         </is>
       </c>
@@ -3738,8 +3738,8 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 11</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
     </row>
@@ -3757,26 +3757,26 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
+          <t>Toán
+Giáo viên CN 11</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 11</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 11</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 11</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 11</t>
         </is>
       </c>
     </row>
@@ -3794,20 +3794,20 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
           <t>Toán
 Giáo viên CN 11</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 3</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3829,8 +3829,8 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>TV tăng cường
+Giáo viên CN 11</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -3841,14 +3841,14 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>TV tăng cường
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 11</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên BM 3</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3865,26 +3865,26 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
           <t>TV tăng cường
 Giáo viên CN 11</t>
         </is>
       </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 11</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 11</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3901,28 +3901,28 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 11</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>TNXH
 Giáo viên BM 3</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 11</t>
-        </is>
-      </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -4005,13 +4005,13 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 12</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 12</t>
         </is>
       </c>
@@ -4042,8 +4042,8 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 12</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4067,25 +4067,25 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 12</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
         </is>
       </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 12</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 12</t>
+        </is>
+      </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 12</t>
         </is>
       </c>
@@ -4110,13 +4110,13 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 12</t>
         </is>
       </c>
@@ -4139,20 +4139,20 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>TV tăng cường
+Giáo viên CN 12</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>TV tăng cường
-Giáo viên CN 12</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 12</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -4175,14 +4175,14 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
           <t>TV tăng cường
 Giáo viên CN 12</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -4217,20 +4217,20 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 12</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
           <t>HĐTN
 Giáo viên CN 12</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 3</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4379,8 +4379,8 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -4397,14 +4397,14 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 13</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
     </row>
@@ -4428,20 +4428,20 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 13</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 13</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>TV tăng cường
-Giáo viên CN 13</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
     </row>
@@ -4465,8 +4465,8 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Toán
+Giáo viên CN 13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4494,26 +4494,26 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
+          <t>Tiếng Việt
 Giáo viên CN 13</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -4530,26 +4530,26 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>TV tăng cường
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Toán tăng cường
 Giáo viên CN 13</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -4566,28 +4566,28 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>Đạo đức
 Giáo viên CN 13</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên CN 13</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 13</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -4658,7 +4658,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 14</t>
         </is>
       </c>
@@ -4689,14 +4689,14 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Toán
+Giáo viên CN 14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -4707,8 +4707,8 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -4726,32 +4726,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 14</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>TV tăng cường
 Giáo viên CN 14</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 14</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
         </is>
       </c>
     </row>
@@ -4763,13 +4763,13 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 14</t>
         </is>
       </c>
@@ -4781,8 +4781,8 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 14</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán tăng cường
 Giáo viên CN 14</t>
         </is>
       </c>
@@ -4816,14 +4816,14 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>Công nghệ
 Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -4840,20 +4840,20 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>TV tăng cường
-Giáo viên CN 14</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 14</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4894,8 +4894,8 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 15</t>
         </is>
       </c>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 15</t>
         </is>
       </c>
@@ -5005,16 +5005,16 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 15</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
         </is>
       </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 15</t>
+        </is>
+      </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
@@ -5023,7 +5023,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
+          <t>Tiếng Việt
 Giáo viên CN 15</t>
         </is>
       </c>
@@ -5036,32 +5036,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 15</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 15</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>TNXH
 Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 15</t>
         </is>
       </c>
     </row>
@@ -5073,19 +5073,19 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 15</t>
         </is>
       </c>
@@ -5114,26 +5114,26 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 15</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
           <t>Toán tăng cường
 Giáo viên CN 15</t>
         </is>
       </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 15</t>
+        </is>
+      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Toán tăng cường
+Giáo viên CN 15</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -5150,26 +5150,26 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>Công nghệ
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>TV tăng cường
 Giáo viên CN 15</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
       <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 15</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>Thể dục
 Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -5192,22 +5192,22 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 15</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
           <t>HĐTN
 Giáo viên CN 15</t>
         </is>
       </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 16</t>
         </is>
       </c>
@@ -5309,8 +5309,8 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Toán
+Giáo viên CN 16</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -5321,14 +5321,14 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 16</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -5346,26 +5346,26 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 16</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -5383,26 +5383,26 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
           <t>Toán
 Giáo viên CN 16</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>Toán
 Giáo viên CN 16</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 16</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 4</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -5424,20 +5424,20 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 16</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 16</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -5460,26 +5460,26 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên CN 16</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>TV tăng cường
 Giáo viên CN 16</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên CN 16</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -5496,28 +5496,28 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Đạo đức
+Giáo viên CN 16</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 16</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Kỹ năng sống
 Giáo viên CN 16</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 16</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 16</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 17</t>
         </is>
       </c>
@@ -5600,7 +5600,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 17</t>
         </is>
       </c>
@@ -5619,25 +5619,25 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 17</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 17</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 17</t>
-        </is>
-      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>TV tăng cường
+          <t>Tiếng Việt
 Giáo viên CN 17</t>
         </is>
       </c>
@@ -5656,32 +5656,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 17</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 17</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 17</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
           <t>Thể dục
 Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 17</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 17</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 17</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
     </row>
@@ -5693,26 +5693,26 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 17</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 17</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -5734,26 +5734,26 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 17</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 17</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên CN 17</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -5770,25 +5770,25 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>TV tăng cường
+Giáo viên CN 17</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên CN 17</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
+          <t>Toán tăng cường
 Giáo viên CN 17</t>
         </is>
       </c>
@@ -5806,28 +5806,28 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Công nghệ
 Giáo viên BM 4</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Kỹ năng sống
 Giáo viên CN 17</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 17</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>Thể dục
 Giáo viên TD 2</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 17</t>
-        </is>
-      </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -5904,13 +5904,13 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 18</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 18</t>
         </is>
       </c>
@@ -5929,8 +5929,8 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Toán
+Giáo viên CN 18</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -5941,20 +5941,20 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 18</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
 Giáo viên CN 18</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
         </is>
       </c>
     </row>
@@ -5966,32 +5966,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 18</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>Công nghệ
 Giáo viên BM 4</t>
         </is>
       </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 18</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 18</t>
+        </is>
+      </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
       <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
-Giáo viên TA 3</t>
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -6015,14 +6015,14 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 18</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 18</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -6050,14 +6050,14 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Đạo đức
+Giáo viên CN 18</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>TNXH
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6086,20 +6086,20 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 18</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 4</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -6116,26 +6116,26 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
 Giáo viên CN 18</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 18</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>TNXH
 Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 18</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên CN 18</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -6271,7 +6271,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 19</t>
         </is>
       </c>
@@ -6284,8 +6284,8 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 19</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 19</t>
         </is>
       </c>
@@ -6321,32 +6321,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>Toán
+Giáo viên CN 19</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 19</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 19</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 19</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 19</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 19</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
         </is>
       </c>
     </row>
@@ -6358,14 +6358,14 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 19</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6399,26 +6399,26 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên QL 1</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
           <t>Khoa học
 Giáo viên CN 19</t>
         </is>
       </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 19</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -6435,20 +6435,20 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Toán tăng cường
 Giáo viên CN 19</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6471,26 +6471,26 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>Đạo đức
+Giáo viên CN 19</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 19</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 19</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 19</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
-        </is>
-      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>HĐTN
-Giáo viên CN 19</t>
+          <t>Kỹ năng sống
+Giáo viên QL 1</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -6594,32 +6594,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 20</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 20</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 20</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 20</t>
-        </is>
-      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
     </row>
@@ -6637,14 +6637,14 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Toán
+Giáo viên CN 20</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 20</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6668,14 +6668,14 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 20</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 20</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -6709,26 +6709,26 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 20</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
+Giáo viên CN 20</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên CN 20</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 20</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -6745,26 +6745,26 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 20</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 20</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
           <t>Khoa học
 Giáo viên CN 20</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -6781,28 +6781,28 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>Đạo đức
+Giáo viên CN 20</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên QL 1</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 20</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 20</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 20</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên QL 1</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -6885,13 +6885,13 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 21</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 21</t>
         </is>
       </c>
@@ -6904,26 +6904,26 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 21</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -6947,25 +6947,25 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 21</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 21</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 21</t>
         </is>
       </c>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 21</t>
         </is>
       </c>
@@ -7019,26 +7019,26 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
+Giáo viên CN 21</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
+Giáo viên CN 21</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên CN 21</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 21</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 21</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -7055,26 +7055,26 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
         </is>
       </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 21</t>
+        </is>
+      </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 21</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 21</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -7091,28 +7091,28 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Lịch sử - Địa lý
 Giáo viên CN 21</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 21</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Kỹ năng sống
 Giáo viên QL 1</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 21</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -7189,7 +7189,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 22</t>
         </is>
       </c>
@@ -7201,7 +7201,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 22</t>
         </is>
       </c>
@@ -7214,20 +7214,20 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 22</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 22</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -7238,8 +7238,8 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 22</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
     </row>
@@ -7251,32 +7251,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 22</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 22</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 22</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
         </is>
       </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 22</t>
+        </is>
+      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Toán
+Giáo viên CN 22</t>
         </is>
       </c>
     </row>
@@ -7288,26 +7288,26 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 22</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 22</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
           <t>Thể dục
 Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 22</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 22</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -7329,26 +7329,26 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên QL 1</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 22</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên CN 22</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên CN 22</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 22</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -7365,26 +7365,26 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
           <t>Khoa học
 Giáo viên CN 22</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Khoa học
 Giáo viên CN 22</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -7401,28 +7401,28 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 22</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 22</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
           <t>Đạo đức
 Giáo viên CN 22</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 22</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên QL 1</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 22</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -7493,7 +7493,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 23</t>
         </is>
       </c>
@@ -7505,13 +7505,13 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 23</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 23</t>
         </is>
       </c>
@@ -7524,14 +7524,14 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 23</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 23</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -7548,8 +7548,8 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 23</t>
         </is>
       </c>
     </row>
@@ -7561,32 +7561,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Toán
+Giáo viên CN 23</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 23</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 23</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
     </row>
@@ -7598,16 +7598,16 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 23</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Toán
@@ -7616,8 +7616,8 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 23</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -7639,25 +7639,25 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 23</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Khoa học
 Giáo viên CN 23</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Khoa học
 Giáo viên CN 23</t>
         </is>
       </c>
@@ -7675,26 +7675,26 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
 Giáo viên CN 23</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 23</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -7711,8 +7711,8 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 23</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -7723,16 +7723,16 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 23</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
           <t>Công nghệ
 Giáo viên BM 4</t>
         </is>
       </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 23</t>
+        </is>
+      </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -7809,13 +7809,13 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 24</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 24</t>
         </is>
       </c>
@@ -7834,14 +7834,14 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 24</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 24</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -7852,14 +7852,14 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên BM 5</t>
+          <t>Tiếng Việt
+Giáo viên CN 24</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 24</t>
         </is>
       </c>
     </row>
@@ -7871,32 +7871,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 24</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
       <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 24</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 24</t>
         </is>
       </c>
     </row>
@@ -7908,25 +7908,25 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>Toán
+Giáo viên CN 24</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 24</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 24</t>
-        </is>
-      </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 24</t>
         </is>
       </c>
@@ -7949,26 +7949,26 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
           <t>Khoa học
 Giáo viên CN 24</t>
         </is>
       </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
       <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên CN 24</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>Khoa học
 Giáo viên CN 24</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7985,26 +7985,26 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
+          <t>Âm nhạc
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
 Giáo viên CN 24</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Toán tăng cường
+Giáo viên CN 24</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -8021,26 +8021,26 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 24</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 24</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
 Giáo viên CN 24</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 25</t>
         </is>
       </c>
@@ -8170,7 +8170,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 25</t>
         </is>
       </c>
@@ -8195,20 +8195,20 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
+          <t>Tiếng Việt
+Giáo viên CN 25</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 25</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -8232,20 +8232,20 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 25</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 25</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 25</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -8269,20 +8269,20 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 25</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 25</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -8304,8 +8304,8 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -8316,14 +8316,14 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
+          <t>Lịch sử - Địa lý
 Giáo viên CN 25</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
-Giáo viên CN 25</t>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -8340,26 +8340,26 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>Toán tăng cường
+Giáo viên CN 25</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 3</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Khoa học
+Giáo viên CN 25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 25</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -8376,28 +8376,28 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>Đạo đức
+Giáo viên CN 25</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 25</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 25</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 25</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 25</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -8474,13 +8474,13 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 26</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 26</t>
         </is>
       </c>
@@ -8499,32 +8499,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 26</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
       <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 26</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Tin học
 Giáo viên TH 1</t>
         </is>
       </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 26</t>
+        </is>
+      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 26</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
     </row>
@@ -8542,26 +8542,26 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 26</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Âm nhạc
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 26</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
         </is>
       </c>
     </row>
@@ -8573,25 +8573,25 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 26</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>Kỹ năng sống
 Giáo viên BM 4</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 26</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 26</t>
-        </is>
-      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 26</t>
         </is>
       </c>
@@ -8614,8 +8614,8 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -8626,8 +8626,8 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8650,20 +8650,20 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>Khoa học
+Giáo viên CN 26</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 26</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 26</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8686,25 +8686,25 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 26</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 26</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 26</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên BM 5</t>
-        </is>
-      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>HĐTN
+          <t>Lịch sử - Địa lý
 Giáo viên CN 26</t>
         </is>
       </c>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 27</t>
         </is>
       </c>
@@ -8796,7 +8796,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 27</t>
         </is>
       </c>
@@ -8809,31 +8809,31 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 27</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 27</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 27</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
+          <t>Công nghệ
 Giáo viên BM 4</t>
         </is>
       </c>
@@ -8846,13 +8846,13 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
+          <t>Kỹ năng sống
 Giáo viên BM 4</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 27</t>
         </is>
       </c>
@@ -8864,13 +8864,13 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 27</t>
         </is>
       </c>
@@ -8883,20 +8883,20 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 27</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 27</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8924,25 +8924,25 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>Khoa học
 Giáo viên CN 27</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Khoa học
 Giáo viên CN 27</t>
         </is>
       </c>
@@ -8960,25 +8960,25 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên CN 27</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên BM 5</t>
-        </is>
-      </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
+          <t>Đạo đức
 Giáo viên CN 27</t>
         </is>
       </c>
@@ -8996,22 +8996,22 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 27</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 27</t>
         </is>
       </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên BM 5</t>
+        </is>
+      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Lịch sử - Địa lý
@@ -9088,19 +9088,19 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 28</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 28</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 28</t>
         </is>
       </c>
@@ -9119,32 +9119,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Toán
+Giáo viên CN 28</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 28</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 5</t>
-        </is>
-      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 28</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 28</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
     </row>
@@ -9156,32 +9156,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 28</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
         </is>
       </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 28</t>
+        </is>
+      </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 28</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 28</t>
         </is>
       </c>
     </row>
@@ -9193,19 +9193,19 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 28</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 28</t>
-        </is>
-      </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 28</t>
         </is>
       </c>
@@ -9234,8 +9234,8 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Toán tăng cường
+Giáo viên CN 28</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -9246,14 +9246,14 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
           <t>Khoa học
 Giáo viên CN 28</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -9270,25 +9270,25 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>Khoa học
+Giáo viên CN 28</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>Kỹ năng sống
 Giáo viên BM 5</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên CN 28</t>
-        </is>
-      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
+          <t>Đạo đức
 Giáo viên CN 28</t>
         </is>
       </c>
@@ -9312,20 +9312,20 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
+          <t>HĐTN
+Giáo viên CN 28</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 28</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 28</t>
-        </is>
-      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 28</t>
+          <t>Công nghệ
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 29</t>
         </is>
       </c>
@@ -9429,26 +9429,26 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 29</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
           <t>Công nghệ
 Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 29</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 29</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -9466,26 +9466,26 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Toán
+Giáo viên CN 29</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 29</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Tin học
 Giáo viên TH 1</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 29</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên BM 5</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -9503,16 +9503,16 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 29</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
         </is>
       </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
@@ -9521,7 +9521,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 29</t>
         </is>
       </c>
@@ -9544,20 +9544,20 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
+          <t>Toán tăng cường
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
 Giáo viên CN 29</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -9580,25 +9580,25 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 29</t>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 29</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Khoa học
 Giáo viên CN 29</t>
         </is>
       </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
+Giáo viên CN 29</t>
+        </is>
+      </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
+          <t>Kỹ năng sống
 Giáo viên BM 5</t>
         </is>
       </c>
@@ -9616,19 +9616,19 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
           <t>Đạo đức
 Giáo viên CN 29</t>
         </is>
       </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 29</t>
+        </is>
+      </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>HĐTN
+          <t>Lịch sử - Địa lý
 Giáo viên CN 29</t>
         </is>
       </c>

--- a/data/Output_Template_TKB_V8.xlsx
+++ b/data/Output_Template_TKB_V8.xlsx
@@ -538,13 +538,13 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 1</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 1</t>
         </is>
       </c>
@@ -581,14 +581,14 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 1</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -612,14 +612,14 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 1</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -643,20 +643,20 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Toán
+Giáo viên CN 1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 1</t>
+          <t>Toán
+Giáo viên CN 1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
+          <t>Toán
+Giáo viên CN 1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Đạo đức
 Giáo viên CN 1</t>
         </is>
       </c>
@@ -702,8 +702,8 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -720,25 +720,25 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>TNXH
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 1</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 1</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
+          <t>Tiếng Việt
 Giáo viên BM 1</t>
         </is>
       </c>
@@ -756,20 +756,20 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Kỹ năng sống
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 1</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>TNXH
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -854,13 +854,13 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 2</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 2</t>
         </is>
       </c>
@@ -879,8 +879,8 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Toán
+Giáo viên CN 2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -891,20 +891,20 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 2</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
-        </is>
-      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên BM 1</t>
+Giáo viên CN 2</t>
         </is>
       </c>
     </row>
@@ -916,32 +916,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 2</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>Toán
 Giáo viên CN 2</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Toán
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 2</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 2</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
         </is>
       </c>
     </row>
@@ -953,26 +953,26 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Tiếng Việt
+Giáo viên CN 2</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 2</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên BM 1</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 2</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -994,14 +994,14 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 2</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 2</t>
+          <t>TNXH
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1030,13 +1030,13 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 2</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Kỹ năng sống
 Giáo viên BM 1</t>
         </is>
       </c>
@@ -1066,28 +1066,28 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 2</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 2</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 3</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 2</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 3</t>
         </is>
       </c>
@@ -1189,8 +1189,8 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 3</t>
+          <t>TNXH
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 3</t>
         </is>
       </c>
@@ -1238,14 +1238,14 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 3</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1263,16 +1263,16 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 3</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
         </is>
       </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Toán
@@ -1281,8 +1281,8 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 3</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1304,8 +1304,8 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 3</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
+          <t>TNXH
 Giáo viên BM 1</t>
         </is>
       </c>
@@ -1340,8 +1340,8 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 3</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Kỹ năng sống
 Giáo viên BM 1</t>
         </is>
       </c>
@@ -1376,28 +1376,28 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>Đạo đức
 Giáo viên CN 3</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Thể dục
 Giáo viên TD 3</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 3</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 1</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -1474,13 +1474,13 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 4</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 4</t>
         </is>
       </c>
@@ -1499,14 +1499,14 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 4</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1517,14 +1517,14 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 4</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên CN 4</t>
+Giáo viên BM 1</t>
         </is>
       </c>
     </row>
@@ -1548,20 +1548,20 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 4</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 4</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 4</t>
         </is>
       </c>
@@ -1585,13 +1585,13 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Toán
+Giáo viên CN 4</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>TNXH
 Giáo viên BM 1</t>
         </is>
       </c>
@@ -1614,26 +1614,26 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 4</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 4</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 1</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 4</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 4</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1656,20 +1656,20 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 4</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 4</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 4</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 4</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1686,28 +1686,28 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>Đạo đức
+Giáo viên CN 4</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>TNXH
 Giáo viên BM 1</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 4</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 4</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 5</t>
         </is>
       </c>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 5</t>
         </is>
       </c>
@@ -1821,20 +1821,20 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 5</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên CN 5</t>
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 5</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
     </row>
@@ -1852,8 +1852,8 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 5</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -1864,14 +1864,14 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Tiếng Việt
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 5</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
     </row>
@@ -1889,20 +1889,20 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 5</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
           <t>Thể dục
 Giáo viên TD 1</t>
         </is>
       </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 5</t>
+        </is>
+      </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 5</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -1924,14 +1924,14 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 5</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -1942,8 +1942,8 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 5</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -1960,14 +1960,14 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 5</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -1978,8 +1978,8 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 5</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -1996,8 +1996,8 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Đạo đức
+Giáo viên CN 5</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2008,16 +2008,16 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 5</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
           <t>TNXH
 Giáo viên BM 2</t>
         </is>
       </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 1</t>
+        </is>
+      </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -2094,13 +2094,13 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 6</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 6</t>
         </is>
       </c>
@@ -2119,20 +2119,20 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 6</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>TNXH
 Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 6</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -2156,26 +2156,26 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 6</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 6</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 6</t>
-        </is>
-      </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 6</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2193,26 +2193,26 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>TNXH
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 6</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 6</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 6</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2234,26 +2234,26 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 6</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 6</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 6</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 6</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 6</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2270,14 +2270,14 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 6</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 6</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -2288,8 +2288,8 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 6</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -2306,26 +2306,26 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
           <t>Đạo đức
 Giáo viên CN 6</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 6</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2449,13 +2449,13 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 7</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 7</t>
         </is>
       </c>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 7</t>
         </is>
       </c>
@@ -2486,8 +2486,8 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 7</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -2511,8 +2511,8 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 7</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -2523,14 +2523,14 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 7</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 7</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -2548,26 +2548,26 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>Toán
+Giáo viên CN 7</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên BM 2</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 7</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>TNXH
 Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 7</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -2589,26 +2589,26 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 7</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
           <t>TV tăng cường
 Giáo viên CN 7</t>
         </is>
       </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Âm nhạc
 Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -2625,16 +2625,16 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 7</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
           <t>TV tăng cường
 Giáo viên CN 7</t>
         </is>
       </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Toán tăng cường
@@ -2643,8 +2643,8 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Đạo đức
+Giáo viên CN 7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -2661,28 +2661,28 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 7</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Kỹ năng sống
 Giáo viên BM 2</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 7</t>
         </is>
       </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 8</t>
         </is>
       </c>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 8</t>
         </is>
       </c>
@@ -2790,8 +2790,8 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -2802,8 +2802,8 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -2827,20 +2827,20 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 8</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 8</t>
-        </is>
-      </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 8</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -2864,19 +2864,19 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên BM 2</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 8</t>
         </is>
       </c>
@@ -2911,14 +2911,14 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Toán tăng cường
 Giáo viên BM 2</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Đạo đức
+Giáo viên CN 8</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2935,8 +2935,8 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2971,28 +2971,28 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 8</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>Âm nhạc
 Giáo viên ÂN 1</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 8</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 8</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 9</t>
         </is>
       </c>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 9</t>
         </is>
       </c>
@@ -3106,8 +3106,8 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 9</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3137,25 +3137,25 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 9</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 2</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 9</t>
         </is>
       </c>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 9</t>
         </is>
       </c>
@@ -3209,19 +3209,19 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>TV tăng cường
+Giáo viên CN 9</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>TV tăng cường
+          <t>Đạo đức
 Giáo viên CN 9</t>
         </is>
       </c>
@@ -3245,20 +3245,20 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>TV tăng cường
+Giáo viên CN 9</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên BM 2</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 9</t>
-        </is>
-      </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>TV tăng cường
-Giáo viên CN 9</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3281,26 +3281,26 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 9</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>TNXH
 Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 9</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 10</t>
         </is>
       </c>
@@ -3447,14 +3447,14 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
           <t>Thể dục
 Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 10</t>
         </is>
       </c>
@@ -3519,14 +3519,14 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Kỹ năng sống
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -3555,14 +3555,14 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -3597,22 +3597,22 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
           <t>TNXH
 Giáo viên BM 3</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 10</t>
         </is>
       </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 11</t>
         </is>
       </c>
@@ -3695,13 +3695,13 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 11</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 11</t>
         </is>
       </c>
@@ -3714,32 +3714,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 11</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 11</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 11</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 11</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 11</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 11</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 11</t>
         </is>
       </c>
     </row>
@@ -3757,7 +3757,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 11</t>
         </is>
       </c>
@@ -3769,14 +3769,14 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 11</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Toán
+Giáo viên CN 11</t>
         </is>
       </c>
     </row>
@@ -3788,26 +3788,26 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 11</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 11</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>Thể dục
 Giáo viên TD 1</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 11</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3829,26 +3829,26 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>Toán
+Giáo viên CN 11</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>TV tăng cường
 Giáo viên CN 11</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>Toán tăng cường
 Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 11</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3865,26 +3865,26 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>TV tăng cường
 Giáo viên CN 11</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 11</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 11</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3907,19 +3907,19 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
           <t>HĐTN
 Giáo viên CN 11</t>
         </is>
       </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 11</t>
+        </is>
+      </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Kỹ năng sống
 Giáo viên BM 3</t>
         </is>
       </c>
@@ -3993,7 +3993,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 12</t>
         </is>
       </c>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 12</t>
         </is>
       </c>
@@ -4042,8 +4042,8 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 12</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -4067,8 +4067,8 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 12</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -4079,8 +4079,8 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 12</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4104,19 +4104,19 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 12</t>
+          <t>Toán tăng cường
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 12</t>
         </is>
       </c>
@@ -4139,26 +4139,26 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>TV tăng cường
 Giáo viên CN 12</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên BM 3</t>
-        </is>
-      </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4175,25 +4175,25 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t>Toán tăng cường
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
           <t>TV tăng cường
 Giáo viên CN 12</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>Kỹ năng sống
-Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
 Giáo viên BM 3</t>
         </is>
       </c>
@@ -4217,19 +4217,19 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
+          <t>HĐTN
+Giáo viên CN 12</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
           <t>TNXH
 Giáo viên BM 3</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>Đạo đức
-Giáo viên CN 12</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
 Giáo viên CN 12</t>
         </is>
       </c>
@@ -4354,19 +4354,19 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 13</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 13</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 13</t>
         </is>
       </c>
@@ -4379,32 +4379,32 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Toán
+Giáo viên CN 13</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 13</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 13</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 13</t>
         </is>
       </c>
     </row>
@@ -4416,8 +4416,8 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -4428,20 +4428,20 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 13</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 13</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 3</t>
         </is>
       </c>
     </row>
@@ -4453,25 +4453,25 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 13</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
           <t>Công nghệ
 Giáo viên BM 3</t>
         </is>
       </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>TV tăng cường
+Giáo viên CN 13</t>
+        </is>
+      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 13</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 13</t>
         </is>
       </c>
@@ -4494,20 +4494,20 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 13</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4530,26 +4530,26 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>TV tăng cường
-Giáo viên CN 13</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
           <t>Toán tăng cường
 Giáo viên CN 13</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Toán tăng cường
 Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -4566,26 +4566,26 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>Đạo đức
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>Kỹ năng sống
 Giáo viên CN 13</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Thể dục
 Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 13</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 13</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -4707,8 +4707,8 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 14</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -4732,26 +4732,26 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
           <t>TNXH
 Giáo viên BM 3</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>TV tăng cường
-Giáo viên CN 14</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ
+Giáo viên BM 3</t>
         </is>
       </c>
     </row>
@@ -4781,8 +4781,8 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -4810,20 +4810,20 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
         </is>
       </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 14</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -4846,19 +4846,19 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Toán tăng cường
+Giáo viên CN 14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
+          <t>TV tăng cường
 Giáo viên CN 14</t>
         </is>
       </c>
@@ -4882,20 +4882,20 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>HĐTN
 Giáo viên CN 14</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Đạo đức
 Giáo viên CN 14</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -4999,14 +4999,14 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 15</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5036,20 +5036,20 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
           <t>TNXH
 Giáo viên BM 3</t>
         </is>
       </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5073,14 +5073,14 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
+          <t>Toán
+Giáo viên CN 15</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5114,20 +5114,20 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 15</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 15</t>
-        </is>
-      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Công nghệ
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -5150,8 +5150,8 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 3</t>
+          <t>Toán tăng cường
+Giáo viên CN 15</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -5162,14 +5162,14 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 15</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -5186,28 +5186,28 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 15</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 15</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>Kỹ năng sống
 Giáo viên CN 15</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 15</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 16</t>
         </is>
       </c>
@@ -5290,13 +5290,13 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 16</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 16</t>
         </is>
       </c>
@@ -5309,32 +5309,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 16</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 16</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
         </is>
       </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 16</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 16</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
     </row>
@@ -5346,32 +5346,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Toán
+Giáo viên CN 16</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 16</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 16</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 16</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 16</t>
         </is>
       </c>
     </row>
@@ -5383,25 +5383,25 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 16</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 16</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 16</t>
         </is>
       </c>
@@ -5424,20 +5424,20 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 16</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 16</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -5460,8 +5460,8 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 4</t>
+          <t>TV tăng cường
+Giáo viên CN 16</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -5472,14 +5472,14 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>TV tăng cường
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
 Giáo viên CN 16</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -5496,26 +5496,26 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Kỹ năng sống
 Giáo viên CN 16</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 16</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>TNXH
 Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 16</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên CN 16</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -5619,26 +5619,26 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Toán
+Giáo viên CN 17</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 17</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 17</t>
-        </is>
-      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 17</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -5680,8 +5680,8 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
     </row>
@@ -5693,16 +5693,16 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 17</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
         </is>
       </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 17</t>
+        </is>
+      </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
@@ -5711,8 +5711,8 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 17</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -5740,20 +5740,20 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Toán tăng cường
 Giáo viên CN 17</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>TNXH
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Toán tăng cường
+Giáo viên CN 17</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -5776,20 +5776,20 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
           <t>TNXH
 Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên CN 17</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên CN 17</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -5806,28 +5806,28 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Đạo đức
+Giáo viên CN 17</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 17</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>Kỹ năng sống
 Giáo viên CN 17</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 17</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 18</t>
         </is>
       </c>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 18</t>
         </is>
       </c>
@@ -5953,8 +5953,8 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 18</t>
+          <t>TNXH
+Giáo viên BM 4</t>
         </is>
       </c>
     </row>
@@ -5966,14 +5966,14 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>TV tăng cường
+Giáo viên CN 18</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -5984,8 +5984,8 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 18</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -6003,8 +6003,8 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Toán
+Giáo viên CN 18</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -6021,8 +6021,8 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Toán
+Giáo viên CN 18</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -6044,26 +6044,26 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 18</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 18</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>Toán tăng cường
 Giáo viên CN 18</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -6080,26 +6080,26 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>TV tăng cường
+          <t>Toán tăng cường
 Giáo viên CN 18</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>Thể dục
 Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -6116,26 +6116,26 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên CN 18</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 18</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 2</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên CN 18</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 18</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 4</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -6253,7 +6253,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 19</t>
         </is>
       </c>
@@ -6284,20 +6284,20 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 19</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 19</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>Âm nhạc
 Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 19</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -6321,32 +6321,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 19</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Toán
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 19</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 19</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 19</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
     </row>
@@ -6364,8 +6364,8 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6399,20 +6399,20 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>Toán
+Giáo viên CN 19</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>Khoa học
 Giáo viên CN 19</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Toán tăng cường
+Giáo viên CN 19</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6435,20 +6435,20 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 19</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
           <t>Tin học
 Giáo viên TH 1</t>
         </is>
       </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 19</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 19</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6471,22 +6471,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Lịch sử - Địa lý
 Giáo viên CN 19</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 19</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 19</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 19</t>
-        </is>
-      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Kỹ năng sống
@@ -6569,7 +6569,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 20</t>
         </is>
       </c>
@@ -6594,8 +6594,8 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Toán
+Giáo viên CN 20</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -6612,14 +6612,14 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 20</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
     </row>
@@ -6631,26 +6631,26 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 20</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 20</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 20</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 20</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -6668,14 +6668,14 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 20</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Toán
+Giáo viên CN 20</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -6686,8 +6686,8 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 20</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -6709,26 +6709,26 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
+          <t>Toán tăng cường
 Giáo viên CN 20</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Khoa học
 Giáo viên CN 20</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên CN 20</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -6745,26 +6745,26 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>Khoa học
 Giáo viên CN 20</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Đạo đức
+Giáo viên CN 20</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -6781,22 +6781,22 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Lịch sử - Địa lý
 Giáo viên CN 20</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 20</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Kỹ năng sống
 Giáo viên QL 1</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 20</t>
-        </is>
-      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
           <t>HĐTN
@@ -6885,7 +6885,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 21</t>
         </is>
       </c>
@@ -6904,32 +6904,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 21</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
           <t>Tin học
 Giáo viên TH 1</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
       <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Mỹ thuật
 Giáo viên MT 1</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 21</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
         </is>
       </c>
     </row>
@@ -6941,32 +6941,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 21</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 21</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Âm nhạc
 Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 21</t>
         </is>
       </c>
     </row>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 21</t>
         </is>
       </c>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 21</t>
         </is>
       </c>
@@ -7019,26 +7019,26 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên QL 1</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên CN 21</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 21</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 21</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 21</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên CN 21</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -7055,20 +7055,20 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>Khoa học
+Giáo viên CN 21</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
 Giáo viên CN 21</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7091,28 +7091,28 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 21</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 21</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 21</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên QL 1</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 21</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -7201,7 +7201,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 22</t>
         </is>
       </c>
@@ -7214,16 +7214,16 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 22</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
-        </is>
-      </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
@@ -7232,14 +7232,14 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 22</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
     </row>
@@ -7251,31 +7251,31 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 22</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 22</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 22</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 22</t>
         </is>
       </c>
@@ -7288,26 +7288,26 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 22</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 22</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Toán
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 22</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -7329,26 +7329,26 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên QL 1</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
+          <t>Khoa học
 Giáo viên CN 22</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
 Giáo viên CN 22</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -7365,13 +7365,13 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
-Giáo viên CN 22</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
+          <t>Toán tăng cường
 Giáo viên CN 22</t>
         </is>
       </c>
@@ -7383,8 +7383,8 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 22</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -7401,22 +7401,22 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 22</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên QL 1</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 22</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 22</t>
-        </is>
-      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Đạo đức
@@ -7493,25 +7493,25 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 23</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 23</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 23</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 23</t>
         </is>
       </c>
@@ -7524,32 +7524,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 23</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 23</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 23</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 23</t>
-        </is>
-      </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 23</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
     </row>
@@ -7561,32 +7561,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 23</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 23</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Toán
+Giáo viên CN 23</t>
         </is>
       </c>
     </row>
@@ -7598,26 +7598,26 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Toán
+Giáo viên CN 23</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 23</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 23</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Toán
+Giáo viên CN 23</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -7639,26 +7639,26 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 23</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 23</t>
-        </is>
-      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
-Giáo viên CN 23</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -7675,25 +7675,25 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 23</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Khoa học
+Giáo viên CN 23</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
+          <t>Khoa học
+Giáo viên CN 23</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
-Giáo viên CN 23</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
 Giáo viên CN 23</t>
         </is>
       </c>
@@ -7711,28 +7711,28 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 23</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 23</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 23</t>
-        </is>
-      </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -7809,13 +7809,13 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 24</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 24</t>
         </is>
       </c>
@@ -7834,14 +7834,14 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 24</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 24</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -7871,8 +7871,8 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -7882,21 +7882,21 @@
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 24</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Công nghệ
 Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
         </is>
       </c>
     </row>
@@ -7914,20 +7914,20 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 24</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 24</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 24</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -7949,26 +7949,26 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
+          <t>Đạo đức
 Giáo viên CN 24</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
 Giáo viên CN 24</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7985,26 +7985,26 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Khoa học
+Giáo viên CN 24</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên BM 5</t>
+          <t>Khoa học
+Giáo viên CN 24</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 24</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 24</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -8021,14 +8021,14 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 24</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -8164,19 +8164,19 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 25</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 25</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 25</t>
         </is>
       </c>
@@ -8189,32 +8189,32 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 25</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 25</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 25</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 25</t>
-        </is>
-      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 25</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
     </row>
@@ -8232,26 +8232,26 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 25</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 25</t>
         </is>
       </c>
     </row>
@@ -8269,20 +8269,20 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Toán
+Giáo viên CN 25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 25</t>
+          <t>Âm nhạc
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -8304,26 +8304,26 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Khoa học
 Giáo viên CN 25</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 25</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -8340,26 +8340,26 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>Khoa học
+Giáo viên CN 25</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên CN 25</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
 Giáo viên CN 25</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -8376,28 +8376,28 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>Đạo đức
 Giáo viên CN 25</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên BM 5</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 25</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 25</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 25</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 26</t>
         </is>
       </c>
@@ -8480,13 +8480,13 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 26</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 26</t>
         </is>
       </c>
@@ -8499,8 +8499,8 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
+          <t>Toán
+Giáo viên CN 26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -8511,8 +8511,8 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8523,8 +8523,8 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 26</t>
         </is>
       </c>
     </row>
@@ -8536,32 +8536,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 26</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 26</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 26</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 26</t>
         </is>
       </c>
     </row>
@@ -8573,26 +8573,26 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 26</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
-        </is>
-      </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 26</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 26</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -8614,26 +8614,26 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
+          <t>Âm nhạc
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
 Giáo viên CN 26</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Thể dục
 Giáo viên TD 3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên CN 26</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -8650,20 +8650,20 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>Toán tăng cường
+Giáo viên CN 26</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>Khoa học
 Giáo viên CN 26</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
 Giáo viên CN 26</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8686,28 +8686,28 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 26</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 26</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 26</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 26</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 26</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 27</t>
         </is>
       </c>
@@ -8790,13 +8790,13 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 27</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 27</t>
         </is>
       </c>
@@ -8827,14 +8827,14 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 27</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 27</t>
         </is>
       </c>
     </row>
@@ -8846,32 +8846,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 27</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 27</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Thể dục
 Giáo viên TD 3</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 27</t>
         </is>
       </c>
     </row>
@@ -8889,8 +8889,8 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -8901,8 +8901,8 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 27</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -8924,26 +8924,26 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>Khoa học
+Giáo viên CN 27</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
+Giáo viên CN 27</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 27</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 27</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -8960,25 +8960,25 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 27</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
-Giáo viên CN 27</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
 Giáo viên CN 27</t>
         </is>
       </c>
@@ -8996,25 +8996,25 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 27</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 27</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 27</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên BM 5</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
+          <t>Đạo đức
 Giáo viên CN 27</t>
         </is>
       </c>
@@ -9094,19 +9094,19 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 28</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 28</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 28</t>
         </is>
       </c>
@@ -9119,32 +9119,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 28</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 28</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 28</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 28</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Tin học
 Giáo viên TH 1</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 28</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 28</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
         </is>
       </c>
     </row>
@@ -9156,31 +9156,31 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>Toán
+Giáo viên CN 28</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 28</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 28</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 28</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 28</t>
         </is>
       </c>
@@ -9193,26 +9193,26 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 3</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 28</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 28</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -9234,26 +9234,26 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên CN 28</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
+Giáo viên CN 28</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Âm nhạc
 Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 28</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -9270,8 +9270,8 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
-Giáo viên CN 28</t>
+          <t>Công nghệ
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -9282,13 +9282,13 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 5</t>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 28</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Khoa học
 Giáo viên CN 28</t>
         </is>
       </c>
@@ -9318,13 +9318,13 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
+          <t>Đạo đức
 Giáo viên CN 28</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
+          <t>Mỹ thuật
 Giáo viên BM 5</t>
         </is>
       </c>
@@ -9404,7 +9404,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 29</t>
         </is>
       </c>
@@ -9429,26 +9429,26 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 29</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên BM 5</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 5</t>
+          <t>Tiếng Việt
+Giáo viên CN 29</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -9478,8 +9478,8 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Toán
+Giáo viên CN 29</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -9503,26 +9503,26 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>Công nghệ
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 29</t>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 29</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -9544,26 +9544,26 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên BM 5</t>
+          <t>Khoa học
+Giáo viên CN 29</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
+Giáo viên CN 29</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 29</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -9580,25 +9580,25 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
 Giáo viên BM 5</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 29</t>
-        </is>
-      </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
-Giáo viên CN 29</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
+          <t>Âm nhạc
 Giáo viên BM 5</t>
         </is>
       </c>
@@ -9622,20 +9622,20 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 29</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
           <t>HĐTN
 Giáo viên CN 29</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 29</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">

--- a/data/Output_Template_TKB_V8.xlsx
+++ b/data/Output_Template_TKB_V8.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Khối 1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Khối 2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Khối 3" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Khối 4" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Khối 5" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Khối 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Khối 2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Khối 3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Khối 4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Khối 5" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -32,10 +32,12 @@
     <font>
       <name val="Times New Roman"/>
       <b val="1"/>
+      <color rgb="FF000000"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Times New Roman"/>
+      <color rgb="FF000000"/>
       <sz val="14"/>
     </font>
   </fonts>
@@ -538,13 +540,13 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 1</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 1</t>
         </is>
       </c>
@@ -569,26 +571,26 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 1</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 1</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 1</t>
-        </is>
-      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -606,26 +608,26 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 1</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên CN 1</t>
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -643,26 +645,26 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>TNXH
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 1</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 1</t>
-        </is>
-      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên CN 1</t>
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -684,26 +686,26 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 1</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 1</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 1</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -720,14 +722,14 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -739,7 +741,7 @@
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên BM 1</t>
+Giáo viên CN 1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -756,14 +758,14 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 1</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Đạo đức
+Giáo viên CN 1</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -848,7 +850,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 2</t>
         </is>
       </c>
@@ -879,32 +881,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 2</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 2</t>
-        </is>
-      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 2</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
     </row>
@@ -922,26 +924,26 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 2</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 2</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 2</t>
         </is>
       </c>
     </row>
@@ -953,26 +955,26 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 2</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
-        </is>
-      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Toán
+Giáo viên CN 2</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -994,20 +996,20 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Tiếng Việt
+Giáo viên CN 2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
 Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 2</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1030,20 +1032,20 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
+          <t>Tiếng Việt
+Giáo viên CN 2</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
 Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1072,20 +1074,20 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>HĐTN
+Giáo viên CN 2</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>Đạo đức
 Giáo viên CN 2</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 2</t>
-        </is>
-      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>TNXH
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1158,13 +1160,13 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 3</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 3</t>
         </is>
       </c>
@@ -1189,26 +1191,26 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Tiếng Việt
+Giáo viên CN 3</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 3</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
 Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 3</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 3</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1226,20 +1228,20 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 3</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1263,26 +1265,26 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Toán
+Giáo viên CN 3</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Toán
+Giáo viên CN 3</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 3</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1304,26 +1306,26 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 3</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 3</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 1</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 3</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1340,26 +1342,26 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 3</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 3</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
 Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 3</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1376,28 +1378,28 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 3</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 3</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Đạo đức
 Giáo viên CN 3</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 3</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -1468,19 +1470,19 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 4</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 4</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 4</t>
         </is>
       </c>
@@ -1499,14 +1501,14 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 4</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 4</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1542,19 +1544,19 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 4</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
           <t>Thể dục
 Giáo viên TD 1</t>
         </is>
       </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 4</t>
+        </is>
+      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 4</t>
         </is>
       </c>
@@ -1573,26 +1575,26 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 4</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 4</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 4</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 1</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1614,7 +1616,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
+          <t>TNXH
 Giáo viên BM 1</t>
         </is>
       </c>
@@ -1632,8 +1634,8 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>TNXH
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1650,8 +1652,8 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1692,7 +1694,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Kỹ năng sống
 Giáo viên BM 1</t>
         </is>
       </c>
@@ -1784,7 +1786,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 5</t>
         </is>
       </c>
@@ -1821,20 +1823,20 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 5</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 5</t>
         </is>
       </c>
     </row>
@@ -1858,20 +1860,20 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 5</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
-        </is>
-      </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 5</t>
         </is>
       </c>
     </row>
@@ -1889,20 +1891,20 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 5</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 5</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -1924,20 +1926,20 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên CN 5</t>
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 5</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -1960,20 +1962,20 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 2</t>
+          <t>Kỹ năng sống
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên CN 5</t>
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 5</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -1996,26 +1998,26 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
           <t>Đạo đức
 Giáo viên CN 5</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 5</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 2</t>
-        </is>
-      </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 1</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2119,13 +2121,13 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 6</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Kỹ năng sống
 Giáo viên BM 2</t>
         </is>
       </c>
@@ -2156,8 +2158,8 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 6</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -2168,8 +2170,8 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 6</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -2193,8 +2195,8 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 6</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2205,8 +2207,8 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 2</t>
+          <t>Toán
+Giáo viên CN 6</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -2234,7 +2236,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 6</t>
         </is>
       </c>
@@ -2245,15 +2247,15 @@
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 6</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 6</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -2270,26 +2272,26 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 6</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 6</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 6</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -2306,26 +2308,26 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
           <t>Đạo đức
 Giáo viên CN 6</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Thể dục
 Giáo viên TD 1</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 6</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2443,25 +2445,25 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 7</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 7</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 7</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 7</t>
         </is>
       </c>
@@ -2474,7 +2476,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 7</t>
         </is>
       </c>
@@ -2486,8 +2488,8 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 7</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -2511,31 +2513,31 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 7</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 7</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 7</t>
+          <t>Kỹ năng sống
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 7</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 7</t>
         </is>
       </c>
@@ -2548,26 +2550,26 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 7</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
           <t>Toán tăng cường
 Giáo viên BM 2</t>
         </is>
       </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 7</t>
+        </is>
+      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 2</t>
+          <t>Toán
+Giáo viên CN 7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -2589,26 +2591,26 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 7</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>TV tăng cường
 Giáo viên CN 7</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -2625,26 +2627,26 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 7</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>TV tăng cường
 Giáo viên CN 7</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên BM 2</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 7</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -2661,26 +2663,26 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 7</t>
         </is>
       </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 2</t>
+        </is>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Đạo đức
+Giáo viên CN 7</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -2753,25 +2755,25 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 8</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 8</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 8</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 8</t>
         </is>
       </c>
@@ -2784,26 +2786,26 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 8</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 8</t>
-        </is>
-      </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 8</t>
+          <t>Kỹ năng sống
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -2821,31 +2823,31 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 8</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
           <t>TNXH
 Giáo viên BM 2</t>
         </is>
       </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 8</t>
+        </is>
+      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 8</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 8</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 8</t>
         </is>
       </c>
@@ -2858,25 +2860,25 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 8</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 8</t>
-        </is>
-      </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 8</t>
         </is>
       </c>
@@ -2899,8 +2901,8 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 8</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -2917,8 +2919,8 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 8</t>
+          <t>Toán tăng cường
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2935,8 +2937,8 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2947,14 +2949,14 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Đạo đức
+Giáo viên CN 8</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên BM 2</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2977,20 +2979,20 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 1</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 8</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -3137,20 +3139,20 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Toán
+Giáo viên CN 9</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>TNXH
 Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3174,8 +3176,8 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 9</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -3209,26 +3211,26 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>Toán tăng cường
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>TV tăng cường
 Giáo viên CN 9</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
-        </is>
-      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 9</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên BM 2</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3245,26 +3247,26 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>TV tăng cường
 Giáo viên CN 9</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>Toán tăng cường
 Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3281,26 +3283,26 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>Kỹ năng sống
 Giáo viên BM 2</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 9</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 2</t>
+          <t>Đạo đức
+Giáo viên CN 9</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -3373,25 +3375,25 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 10</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 10</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 10</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 10</t>
         </is>
       </c>
@@ -3404,20 +3406,20 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 10</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 10</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 10</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -3447,25 +3449,25 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 10</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 10</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 10</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 10</t>
         </is>
       </c>
@@ -3478,26 +3480,26 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 10</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 10</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 10</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên BM 3</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3519,8 +3521,8 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -3531,8 +3533,8 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Toán tăng cường
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -3555,20 +3557,20 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
           <t>Toán tăng cường
 Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -3597,16 +3599,16 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
           <t>HĐTN
 Giáo viên CN 10</t>
         </is>
       </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Thể dục
@@ -3695,7 +3697,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 11</t>
         </is>
       </c>
@@ -3714,20 +3716,20 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Toán
+Giáo viên CN 11</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 11</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -3769,8 +3771,8 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 11</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3794,8 +3796,8 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 11</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -3806,8 +3808,8 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Toán
+Giáo viên CN 11</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -3829,26 +3831,26 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 11</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Kỹ năng sống
 Giáo viên BM 3</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>TV tăng cường
 Giáo viên CN 11</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên BM 3</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3865,8 +3867,8 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -3877,14 +3879,14 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
+          <t>Toán tăng cường
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
           <t>TV tăng cường
 Giáo viên CN 11</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3907,19 +3909,19 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
+          <t>Đạo đức
+Giáo viên CN 11</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>HĐTN
 Giáo viên CN 11</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 11</t>
-        </is>
-      </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
+          <t>TNXH
 Giáo viên BM 3</t>
         </is>
       </c>
@@ -3993,13 +3995,13 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 12</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 12</t>
         </is>
       </c>
@@ -4024,7 +4026,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 12</t>
         </is>
       </c>
@@ -4067,14 +4069,14 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 12</t>
+          <t>Kỹ năng sống
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 12</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -4098,20 +4100,20 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 12</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên BM 3</t>
+          <t>Toán
+Giáo viên CN 12</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Toán
+Giáo viên CN 12</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -4139,14 +4141,14 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Toán tăng cường
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Đạo đức
+Giáo viên CN 12</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -4157,8 +4159,8 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Toán tăng cường
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4175,16 +4177,16 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
           <t>Thể dục
 Giáo viên TD 1</t>
         </is>
       </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
           <t>TV tăng cường
@@ -4193,8 +4195,8 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 3</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4217,8 +4219,8 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>HĐTN
-Giáo viên CN 12</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -4229,7 +4231,7 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>HĐTN
 Giáo viên CN 12</t>
         </is>
       </c>
@@ -4348,7 +4350,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 13</t>
         </is>
       </c>
@@ -4360,13 +4362,13 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 13</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 13</t>
         </is>
       </c>
@@ -4379,32 +4381,32 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>TNXH
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 13</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 13</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 13</t>
-        </is>
-      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 13</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
     </row>
@@ -4422,26 +4424,26 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 13</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 13</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 13</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
     </row>
@@ -4453,26 +4455,26 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>Toán
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>Công nghệ
 Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>TV tăng cường
-Giáo viên CN 13</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -4494,20 +4496,20 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 13</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên CN 13</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4530,26 +4532,26 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>TV tăng cường
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên CN 13</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 13</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -4566,28 +4568,28 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>Đạo đức
 Giáo viên CN 13</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 13</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên CN 13</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -4658,7 +4660,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 14</t>
         </is>
       </c>
@@ -4670,7 +4672,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 14</t>
         </is>
       </c>
@@ -4689,32 +4691,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 14</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 14</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 14</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
           <t>Thể dục
 Giáo viên TD 2</t>
         </is>
       </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>TV tăng cường
+Giáo viên CN 14</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 14</t>
+        </is>
+      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 14</t>
         </is>
       </c>
     </row>
@@ -4726,32 +4728,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 14</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
           <t>TNXH
 Giáo viên BM 3</t>
         </is>
       </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 14</t>
+        </is>
+      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Toán
+Giáo viên CN 14</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 14</t>
         </is>
       </c>
     </row>
@@ -4763,13 +4765,13 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 14</t>
         </is>
       </c>
@@ -4804,26 +4806,26 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên CN 14</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 14</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -4840,26 +4842,26 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>Toán tăng cường
+Giáo viên CN 14</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên CN 14</t>
-        </is>
-      </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>TV tăng cường
-Giáo viên CN 14</t>
+          <t>Công nghệ
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -4876,28 +4878,28 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>Đạo đức
+Giáo viên CN 14</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>Kỹ năng sống
 Giáo viên CN 14</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Thể dục
 Giáo viên TD 2</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 14</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 14</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -4974,7 +4976,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 15</t>
         </is>
       </c>
@@ -4986,7 +4988,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 15</t>
         </is>
       </c>
@@ -4999,32 +5001,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 15</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 15</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 15</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>TNXH
 Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 15</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 15</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 15</t>
         </is>
       </c>
     </row>
@@ -5036,32 +5038,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
+          <t>Toán
+Giáo viên CN 15</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 15</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 15</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Thể dục
 Giáo viên TD 2</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 15</t>
+          <t>Công nghệ
+Giáo viên BM 3</t>
         </is>
       </c>
     </row>
@@ -5073,20 +5075,20 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 15</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
         </is>
       </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 15</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -5114,26 +5116,26 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 15</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên CN 15</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 15</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 3</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 15</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -5150,26 +5152,26 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>TV tăng cường
+Giáo viên CN 15</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên CN 15</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>TV tăng cường
-Giáo viên CN 15</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -5186,26 +5188,26 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Đạo đức
+Giáo viên CN 15</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên CN 15</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 15</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 15</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên CN 15</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -5278,7 +5280,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 16</t>
         </is>
       </c>
@@ -5290,7 +5292,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 16</t>
         </is>
       </c>
@@ -5309,32 +5311,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Toán
+Giáo viên CN 16</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 16</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Thể dục
 Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 16</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
     </row>
@@ -5346,26 +5348,26 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 16</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 16</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 16</t>
+          <t>TNXH
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 16</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -5383,25 +5385,25 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 16</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 16</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 16</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 16</t>
         </is>
       </c>
@@ -5424,25 +5426,25 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán tăng cường
 Giáo viên CN 16</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Toán tăng cường
+Giáo viên CN 16</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 16</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
+          <t>Đạo đức
 Giáo viên CN 16</t>
         </is>
       </c>
@@ -5460,26 +5462,26 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>TV tăng cường
 Giáo viên CN 16</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên CN 16</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 16</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -5496,28 +5498,28 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>Kỹ năng sống
 Giáo viên CN 16</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 16</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 4</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -5588,13 +5590,13 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 17</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 17</t>
         </is>
       </c>
@@ -5619,16 +5621,16 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 17</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
         </is>
       </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 17</t>
+        </is>
+      </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
@@ -5637,14 +5639,14 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
+          <t>Tiếng Việt
+Giáo viên CN 17</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
 Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
         </is>
       </c>
     </row>
@@ -5662,14 +5664,14 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 17</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 17</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5693,26 +5695,26 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Toán
+Giáo viên CN 17</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 17</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Toán
+Giáo viên CN 17</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 17</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -5740,14 +5742,14 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên CN 17</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 4</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5776,20 +5778,20 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Đạo đức
+Giáo viên CN 17</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 4</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -5806,26 +5808,26 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Kỹ năng sống
 Giáo viên CN 17</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 17</t>
         </is>
       </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên CN 17</t>
+          <t>TNXH
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -5898,7 +5900,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 18</t>
         </is>
       </c>
@@ -5910,7 +5912,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 18</t>
         </is>
       </c>
@@ -5929,32 +5931,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 18</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 18</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 18</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 4</t>
         </is>
       </c>
     </row>
@@ -5966,14 +5968,14 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>TV tăng cường
+          <t>Toán
 Giáo viên CN 18</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 18</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -5984,14 +5986,14 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 18</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 18</t>
         </is>
       </c>
     </row>
@@ -6003,25 +6005,25 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>TV tăng cường
 Giáo viên CN 18</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Toán
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 18</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 18</t>
-        </is>
-      </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 18</t>
         </is>
       </c>
@@ -6044,26 +6046,26 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
+          <t>TNXH
 Giáo viên BM 4</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 18</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>TNXH
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -6080,26 +6082,26 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t>Đạo đức
+Giáo viên CN 18</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên CN 18</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 4</t>
-        </is>
-      </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Toán tăng cường
+Giáo viên CN 18</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -6122,20 +6124,20 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>HĐTN
 Giáo viên CN 18</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>Thể dục
 Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 18</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -6253,7 +6255,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 19</t>
         </is>
       </c>
@@ -6265,7 +6267,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 19</t>
         </is>
       </c>
@@ -6284,32 +6286,32 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 19</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 19</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
         </is>
       </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 19</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 19</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 19</t>
+        </is>
+      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 19</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
     </row>
@@ -6339,14 +6341,14 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 19</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
         </is>
       </c>
     </row>
@@ -6358,25 +6360,25 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Toán
+Giáo viên CN 19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Toán
+Giáo viên CN 19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 19</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 19</t>
         </is>
       </c>
@@ -6399,26 +6401,26 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 19</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
           <t>Khoa học
 Giáo viên CN 19</t>
         </is>
       </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
+          <t>Khoa học
 Giáo viên CN 19</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -6441,19 +6443,19 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Toán tăng cường
 Giáo viên CN 19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
+          <t>Lịch sử - Địa lý
 Giáo viên CN 19</t>
         </is>
       </c>
@@ -6477,22 +6479,22 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 19</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
           <t>HĐTN
 Giáo viên CN 19</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Kỹ năng sống
 Giáo viên QL 1</t>
         </is>
       </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 19</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -6563,13 +6565,13 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 20</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 20</t>
         </is>
       </c>
@@ -6600,26 +6602,26 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 20</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 20</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
     </row>
@@ -6631,26 +6633,26 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 20</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 20</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 20</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 20</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -6668,26 +6670,26 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán tăng cường
 Giáo viên CN 20</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 20</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 20</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -6709,25 +6711,25 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 20</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
           <t>Thể dục
 Giáo viên TD 2</t>
         </is>
       </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
+          <t>Lịch sử - Địa lý
 Giáo viên CN 20</t>
         </is>
       </c>
@@ -6751,20 +6753,20 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
           <t>Khoa học
 Giáo viên CN 20</t>
         </is>
       </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
+Giáo viên CN 20</t>
+        </is>
+      </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 20</t>
+          <t>Kỹ năng sống
+Giáo viên QL 1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -6781,22 +6783,22 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 20</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 20</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 20</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên QL 1</t>
-        </is>
-      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
           <t>HĐTN
@@ -6873,13 +6875,13 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 21</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 21</t>
         </is>
       </c>
@@ -6891,7 +6893,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 21</t>
         </is>
       </c>
@@ -6910,25 +6912,25 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 21</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 21</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 21</t>
         </is>
       </c>
@@ -6941,32 +6943,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 21</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 21</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 21</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
         </is>
       </c>
     </row>
@@ -6984,20 +6986,20 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 21</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 21</t>
-        </is>
-      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 21</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -7019,26 +7021,26 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên QL 1</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
           <t>Toán tăng cường
 Giáo viên CN 21</t>
         </is>
       </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
+Giáo viên CN 21</t>
+        </is>
+      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Khoa học
 Giáo viên CN 21</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 21</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -7055,26 +7057,26 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
-Giáo viên CN 21</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Kỹ năng sống
+Giáo viên QL 1</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
-Giáo viên CN 21</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -7091,25 +7093,25 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 21</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 21</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 21</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
+          <t>Đạo đức
 Giáo viên CN 21</t>
         </is>
       </c>
@@ -7195,7 +7197,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 22</t>
         </is>
       </c>
@@ -7214,8 +7216,8 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Toán
+Giáo viên CN 22</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -7232,14 +7234,14 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 22</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 22</t>
         </is>
       </c>
     </row>
@@ -7251,32 +7253,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 22</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 22</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 22</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
     </row>
@@ -7288,25 +7290,25 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 22</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 22</t>
-        </is>
-      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 22</t>
         </is>
       </c>
@@ -7329,26 +7331,26 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Toán tăng cường
+Giáo viên CN 22</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
-Giáo viên CN 22</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
-Giáo viên CN 22</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -7365,25 +7367,25 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>Khoa học
+Giáo viên CN 22</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 22</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 2</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên CN 22</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
+          <t>Khoa học
 Giáo viên CN 22</t>
         </is>
       </c>
@@ -7401,28 +7403,28 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên QL 1</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 22</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 22</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 22</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên QL 1</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 22</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 22</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -7493,7 +7495,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 23</t>
         </is>
       </c>
@@ -7505,13 +7507,13 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 23</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 23</t>
         </is>
       </c>
@@ -7524,20 +7526,20 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Toán
+Giáo viên CN 23</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 23</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 23</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -7548,8 +7550,8 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 23</t>
         </is>
       </c>
     </row>
@@ -7561,31 +7563,31 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 23</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
           <t>Tin học
 Giáo viên TH 1</t>
         </is>
       </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
       <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 23</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Thể dục
 Giáo viên TD 2</t>
         </is>
       </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 23</t>
         </is>
       </c>
@@ -7598,26 +7600,26 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 23</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 23</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 23</t>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 23</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -7639,26 +7641,26 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 23</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
+Giáo viên CN 23</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
+Giáo viên CN 23</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -7675,26 +7677,26 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 23</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
-Giáo viên CN 23</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 23</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>Toán tăng cường
 Giáo viên CN 23</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -7711,8 +7713,8 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Đạo đức
+Giáo viên CN 23</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -7723,16 +7725,16 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
           <t>HĐTN
 Giáo viên CN 23</t>
         </is>
       </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 23</t>
+        </is>
+      </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -7803,19 +7805,19 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 24</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 24</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 24</t>
         </is>
       </c>
@@ -7834,32 +7836,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 24</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 24</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 24</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 24</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 24</t>
+Giáo viên TA 3</t>
         </is>
       </c>
     </row>
@@ -7871,32 +7873,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 24</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 24</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
+          <t>Tiếng Việt
+Giáo viên CN 24</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 24</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
         </is>
       </c>
     </row>
@@ -7914,20 +7916,20 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 24</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 24</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -7949,26 +7951,26 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
 Giáo viên CN 24</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 24</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7985,16 +7987,16 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t>Toán tăng cường
+Giáo viên CN 24</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
           <t>Khoa học
 Giáo viên CN 24</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 24</t>
-        </is>
-      </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Thể dục
@@ -8003,8 +8005,8 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -8021,25 +8023,25 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
+          <t>Đạo đức
+Giáo viên CN 24</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 24</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên BM 5</t>
-        </is>
-      </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 24</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
           <t>HĐTN
-Giáo viên CN 24</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
 Giáo viên CN 24</t>
         </is>
       </c>
@@ -8189,8 +8191,8 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Toán
+Giáo viên CN 25</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -8213,8 +8215,8 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 25</t>
         </is>
       </c>
     </row>
@@ -8226,8 +8228,8 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 25</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -8238,20 +8240,20 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 25</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 25</t>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
         </is>
       </c>
     </row>
@@ -8281,8 +8283,8 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên BM 5</t>
+          <t>Tiếng Việt
+Giáo viên CN 25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -8304,20 +8306,20 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
         </is>
       </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
+Giáo viên CN 25</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8340,25 +8342,25 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
-Giáo viên CN 25</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
           <t>Toán tăng cường
 Giáo viên CN 25</t>
         </is>
       </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
+        </is>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
+          <t>Đạo đức
 Giáo viên CN 25</t>
         </is>
       </c>
@@ -8376,28 +8378,28 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 25</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 25</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 25</t>
         </is>
       </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 25</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -8468,7 +8470,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 26</t>
         </is>
       </c>
@@ -8480,7 +8482,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 26</t>
         </is>
       </c>
@@ -8499,20 +8501,20 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 26</t>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 26</t>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8536,32 +8538,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 26</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 26</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 26</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
     </row>
@@ -8573,20 +8575,20 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 26</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 26</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8614,26 +8616,26 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 26</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên BM 5</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
+          <t>Toán tăng cường
 Giáo viên CN 26</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -8650,8 +8652,8 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 26</t>
+          <t>Âm nhạc
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -8662,14 +8664,14 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>Khoa học
 Giáo viên CN 26</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -8686,28 +8688,28 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>Đạo đức
+Giáo viên CN 26</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 26</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 26</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 26</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 26</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -8790,7 +8792,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 27</t>
         </is>
       </c>
@@ -8809,20 +8811,20 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 27</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 27</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 27</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8846,32 +8848,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>Toán
+Giáo viên CN 27</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 27</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 27</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 27</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 27</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
         </is>
       </c>
     </row>
@@ -8883,25 +8885,25 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 27</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 27</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 27</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
+          <t>Kỹ năng sống
 Giáo viên BM 4</t>
         </is>
       </c>
@@ -8924,26 +8926,26 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
 Giáo viên CN 27</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
 Giáo viên CN 27</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -8960,26 +8962,26 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
+          <t>Khoa học
+Giáo viên CN 27</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
 Giáo viên CN 27</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên BM 5</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 27</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -8996,26 +8998,26 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 27</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 27</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 27</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 27</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 27</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -9094,7 +9096,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 28</t>
         </is>
       </c>
@@ -9106,7 +9108,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 28</t>
         </is>
       </c>
@@ -9131,7 +9133,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 28</t>
         </is>
       </c>
@@ -9143,8 +9145,8 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
     </row>
@@ -9156,31 +9158,31 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 28</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 28</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
         </is>
       </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Toán
+Giáo viên CN 28</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 28</t>
         </is>
       </c>
@@ -9193,26 +9195,26 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>Toán
+Giáo viên CN 28</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 28</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -9234,8 +9236,8 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 5</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -9252,8 +9254,8 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên BM 5</t>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 28</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -9270,14 +9272,14 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
           <t>Công nghệ
 Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -9306,8 +9308,8 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 28</t>
+          <t>Âm nhạc
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -9429,20 +9431,20 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Toán
+Giáo viên CN 29</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 29</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -9466,20 +9468,20 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 29</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 29</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 29</t>
+          <t>Âm nhạc
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -9503,26 +9505,26 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
+          <t>Toán tăng cường
 Giáo viên BM 5</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 29</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
+          <t>Toán
+Giáo viên CN 29</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
 Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -9544,7 +9546,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
+          <t>Đạo đức
 Giáo viên CN 29</t>
         </is>
       </c>
@@ -9556,14 +9558,14 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
-Giáo viên CN 29</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 29</t>
+          <t>Công nghệ
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -9580,26 +9582,26 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>Khoa học
+Giáo viên CN 29</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
+Giáo viên CN 29</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 29</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên BM 5</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -9616,26 +9618,26 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 29</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 29</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 29</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">

--- a/data/Output_Template_TKB_V8.xlsx
+++ b/data/Output_Template_TKB_V8.xlsx
@@ -546,7 +546,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 1</t>
         </is>
       </c>
@@ -577,8 +577,8 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Việt
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -589,8 +589,8 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 1</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -608,26 +608,26 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
+          <t>Tiếng Việt
+Giáo viên CN 1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên BM 1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -645,26 +645,26 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 1</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -686,16 +686,16 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 1</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
@@ -704,8 +704,8 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 1</t>
+          <t>TNXH
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -722,16 +722,16 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
@@ -740,7 +740,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Đạo đức
 Giáo viên CN 1</t>
         </is>
       </c>
@@ -758,28 +758,28 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 1</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 3</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 1</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 1</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -850,7 +850,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 2</t>
         </is>
       </c>
@@ -862,7 +862,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 2</t>
         </is>
       </c>
@@ -881,32 +881,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 2</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
 Giáo viên BM 1</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
       <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 2</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 2</t>
         </is>
       </c>
     </row>
@@ -918,32 +918,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 2</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 2</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 2</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 2</t>
         </is>
       </c>
     </row>
@@ -961,19 +961,19 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Toán
+Giáo viên CN 2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên CN 2</t>
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 2</t>
         </is>
       </c>
@@ -1008,14 +1008,14 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 2</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 2</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1044,14 +1044,14 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 2</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>TNXH
 Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1068,28 +1068,28 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 2</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Đạo đức
 Giáo viên CN 2</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 1</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -1160,7 +1160,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 3</t>
         </is>
       </c>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 3</t>
         </is>
       </c>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 3</t>
         </is>
       </c>
@@ -1203,20 +1203,20 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 3</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
+          <t>Tiếng Việt
+Giáo viên CN 3</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 3</t>
         </is>
       </c>
     </row>
@@ -1234,26 +1234,26 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 3</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
+Giáo viên CN 3</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 3</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 3</t>
         </is>
       </c>
     </row>
@@ -1265,25 +1265,25 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 3</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 3</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 3</t>
         </is>
       </c>
@@ -1306,26 +1306,26 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 3</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 3</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1342,26 +1342,26 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 3</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 3</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
           <t>TNXH
 Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 3</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 3</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1378,26 +1378,26 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 1</t>
+          <t>Đạo đức
+Giáo viên CN 3</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 3</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Thể dục
 Giáo viên TD 3</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 3</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 3</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 4</t>
         </is>
       </c>
@@ -1513,20 +1513,20 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 4</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 4</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
         </is>
       </c>
     </row>
@@ -1562,8 +1562,8 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
+          <t>Toán
+Giáo viên CN 4</t>
         </is>
       </c>
     </row>
@@ -1587,14 +1587,14 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 4</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 4</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1616,26 +1616,26 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 4</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên BM 1</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 4</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 4</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1652,8 +1652,8 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Đạo đức
+Giáo viên CN 4</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -1665,13 +1665,13 @@
       <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên CN 4</t>
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1688,28 +1688,28 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 4</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
+          <t>TNXH
 Giáo viên BM 1</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 4</t>
         </is>
       </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 1</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 5</t>
         </is>
       </c>
@@ -1811,32 +1811,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 5</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 5</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 5</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 5</t>
         </is>
       </c>
     </row>
@@ -1860,20 +1860,20 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 5</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên CN 5</t>
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 5</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
     </row>
@@ -1885,26 +1885,26 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 5</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 5</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 5</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên CN 5</t>
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -1926,20 +1926,20 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Kỹ năng sống
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên BM 1</t>
+Giáo viên CN 5</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 5</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -1962,20 +1962,20 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 1</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên BM 1</t>
+Giáo viên CN 5</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 5</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -1998,26 +1998,26 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>Đạo đức
+Giáo viên CN 5</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
           <t>TNXH
 Giáo viên BM 2</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 5</t>
-        </is>
-      </c>
       <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 5</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2121,14 +2121,14 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 2</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 6</t>
         </is>
       </c>
@@ -2169,15 +2169,15 @@
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 6</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>Mỹ thuật
 Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2195,20 +2195,20 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 6</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 6</t>
-        </is>
-      </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 6</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -2236,20 +2236,20 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 6</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 6</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -2272,20 +2272,20 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 6</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 6</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -2314,14 +2314,14 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
           <t>HĐTN
 Giáo viên CN 6</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 7</t>
         </is>
       </c>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 7</t>
         </is>
       </c>
@@ -2476,14 +2476,14 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 7</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 7</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -2513,31 +2513,31 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Kỹ năng sống
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 7</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>TNXH
 Giáo viên BM 2</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 2</t>
-        </is>
-      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 7</t>
         </is>
       </c>
@@ -2550,13 +2550,13 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên BM 2</t>
+          <t>Toán
+Giáo viên CN 7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 7</t>
         </is>
       </c>
@@ -2597,20 +2597,20 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
           <t>TV tăng cường
 Giáo viên CN 7</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -2633,20 +2633,20 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>TV tăng cường
+Giáo viên CN 7</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên BM 2</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>TV tăng cường
-Giáo viên CN 7</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Toán tăng cường
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -2663,28 +2663,28 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>Đạo đức
+Giáo viên CN 7</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 7</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>Âm nhạc
 Giáo viên ÂN 1</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 7</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 7</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -2761,19 +2761,19 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 8</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 8</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 8</t>
         </is>
       </c>
@@ -2786,26 +2786,26 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 8</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 8</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -2823,31 +2823,31 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Tiếng Việt
+Giáo viên CN 8</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 8</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 8</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
 Giáo viên BM 2</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 8</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 8</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 8</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 8</t>
         </is>
       </c>
@@ -2860,25 +2860,25 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Toán
+Giáo viên CN 8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>Toán tăng cường
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 8</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 2</t>
-        </is>
-      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 8</t>
         </is>
       </c>
@@ -2901,20 +2901,20 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 8</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>TV tăng cường
 Giáo viên CN 8</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên BM 2</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2937,26 +2937,26 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 8</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>TV tăng cường
 Giáo viên CN 8</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 8</t>
-        </is>
-      </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2973,22 +2973,22 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 8</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 1</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
           <t>HĐTN
@@ -3071,19 +3071,19 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 9</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 9</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 9</t>
         </is>
       </c>
@@ -3139,25 +3139,25 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Kỹ năng sống
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 9</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 9</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 9</t>
         </is>
       </c>
@@ -3176,20 +3176,20 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Toán
+Giáo viên CN 9</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 9</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 9</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3211,26 +3211,26 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên BM 2</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>TV tăng cường
 Giáo viên CN 9</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3247,26 +3247,26 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>TV tăng cường
 Giáo viên CN 9</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên BM 2</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3283,28 +3283,28 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 9</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Đạo đức
 Giáo viên CN 9</t>
         </is>
       </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -3375,19 +3375,19 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 10</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 10</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 10</t>
         </is>
       </c>
@@ -3412,14 +3412,14 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 10</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 10</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -3449,19 +3449,19 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 10</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 10</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 10</t>
         </is>
       </c>
@@ -3486,20 +3486,20 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 10</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 10</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Toán tăng cường
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -3527,14 +3527,14 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 2</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên BM 3</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -3557,20 +3557,20 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên BM 3</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -3593,26 +3593,26 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 10</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>Đạo đức
 Giáo viên CN 10</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 10</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 11</t>
         </is>
       </c>
@@ -3703,7 +3703,7 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 11</t>
         </is>
       </c>
@@ -3716,20 +3716,20 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 11</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 11</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 11</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -3765,19 +3765,19 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 11</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Kỹ năng sống
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 11</t>
         </is>
       </c>
@@ -3790,19 +3790,19 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 11</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 11</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 11</t>
         </is>
       </c>
@@ -3831,26 +3831,26 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Toán tăng cường
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>TV tăng cường
 Giáo viên CN 11</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3867,26 +3867,26 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>TV tăng cường
 Giáo viên CN 11</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3909,22 +3909,22 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 11</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
           <t>Đạo đức
 Giáo viên CN 11</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 11</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 3</t>
-        </is>
-      </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -3995,13 +3995,13 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 12</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 12</t>
         </is>
       </c>
@@ -4032,8 +4032,8 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 12</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -4069,20 +4069,20 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 12</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 12</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 3</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4106,14 +4106,14 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 12</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 12</t>
+          <t>Kỹ năng sống
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -4141,26 +4141,26 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên BM 3</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 12</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>TV tăng cường
 Giáo viên CN 12</t>
         </is>
       </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên BM 3</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4177,26 +4177,26 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>TV tăng cường
 Giáo viên CN 12</t>
         </is>
       </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên BM 3</t>
+        </is>
+      </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Toán tăng cường
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4213,25 +4213,25 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
           <t>Mỹ thuật
 Giáo viên MT 1</t>
         </is>
       </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
+          <t>HĐTN
+Giáo viên CN 12</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>HĐTN
+          <t>Đạo đức
 Giáo viên CN 12</t>
         </is>
       </c>
@@ -4350,19 +4350,19 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 13</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 13</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 13</t>
         </is>
       </c>
@@ -4381,32 +4381,32 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>TNXH
 Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 13</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 13</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
         </is>
       </c>
     </row>
@@ -4424,26 +4424,26 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 2</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 13</t>
-        </is>
-      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 13</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Công nghệ
+Giáo viên BM 3</t>
         </is>
       </c>
     </row>
@@ -4461,20 +4461,20 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 3</t>
+          <t>Toán
+Giáo viên CN 13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -4502,20 +4502,20 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Toán tăng cường
 Giáo viên CN 13</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -4544,14 +4544,14 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -4574,22 +4574,22 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
           <t>Đạo đức
 Giáo viên CN 13</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 13</t>
         </is>
       </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -4666,13 +4666,13 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 14</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 14</t>
         </is>
       </c>
@@ -4691,26 +4691,26 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>TV tăng cường
-Giáo viên CN 14</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 14</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Công nghệ
 Giáo viên BM 3</t>
         </is>
       </c>
@@ -4740,19 +4740,19 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 14</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 14</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>TV tăng cường
 Giáo viên CN 14</t>
         </is>
       </c>
@@ -4771,20 +4771,20 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 14</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 14</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 14</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -4806,26 +4806,26 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên CN 14</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên CN 14</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -4848,20 +4848,20 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 3</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -4884,22 +4884,22 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 14</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>Kỹ năng sống
 Giáo viên CN 14</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 14</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 15</t>
         </is>
       </c>
@@ -5001,8 +5001,8 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Toán
+Giáo viên CN 15</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -5025,8 +5025,8 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 15</t>
         </is>
       </c>
     </row>
@@ -5038,32 +5038,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 15</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>TV tăng cường
 Giáo viên CN 15</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 15</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 3</t>
         </is>
       </c>
     </row>
@@ -5075,20 +5075,20 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Công nghệ
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Toán
+Giáo viên CN 15</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -5116,26 +5116,26 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 15</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
           <t>Toán tăng cường
 Giáo viên CN 15</t>
         </is>
       </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Toán tăng cường
+Giáo viên CN 15</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -5152,26 +5152,26 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>TV tăng cường
-Giáo viên CN 15</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 15</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -5188,28 +5188,28 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên CN 15</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>Đạo đức
 Giáo viên CN 15</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên CN 15</t>
-        </is>
-      </c>
       <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 15</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 16</t>
         </is>
       </c>
@@ -5323,20 +5323,20 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 16</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 16</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
     </row>
@@ -5348,32 +5348,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 16</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 4</t>
-        </is>
-      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 16</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
     </row>
@@ -5385,25 +5385,25 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 16</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 16</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
         </is>
       </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 16</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 4</t>
+        </is>
+      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 16</t>
         </is>
       </c>
@@ -5426,26 +5426,26 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 16</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên CN 16</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên CN 16</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 16</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 16</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -5462,26 +5462,26 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
           <t>TV tăng cường
 Giáo viên CN 16</t>
         </is>
       </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên CN 16</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Đạo đức
+Giáo viên CN 16</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -5504,22 +5504,22 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 4</t>
+          <t>HĐTN
+Giáo viên CN 16</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Kỹ năng sống
 Giáo viên CN 16</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 16</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -5596,13 +5596,13 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 17</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 17</t>
         </is>
       </c>
@@ -5621,8 +5621,8 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Toán
+Giáo viên CN 17</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -5645,8 +5645,8 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 4</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
     </row>
@@ -5658,8 +5658,8 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>TNXH
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -5670,20 +5670,20 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 17</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 17</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 17</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
         </is>
       </c>
     </row>
@@ -5695,26 +5695,26 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 17</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 17</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 17</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
           <t>Âm nhạc
 Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 17</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -5742,20 +5742,20 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
+          <t>Toán tăng cường
+Giáo viên CN 17</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>Tin học
 Giáo viên TH 1</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên CN 17</t>
-        </is>
-      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 17</t>
+          <t>TNXH
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -5784,14 +5784,14 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
+          <t>Toán tăng cường
+Giáo viên CN 17</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
           <t>Đạo đức
 Giáo viên CN 17</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -5814,22 +5814,22 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>HĐTN
 Giáo viên CN 17</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>Công nghệ
 Giáo viên BM 4</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 4</t>
-        </is>
-      </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -5900,13 +5900,13 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 18</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 18</t>
         </is>
       </c>
@@ -5931,32 +5931,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 18</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 18</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 18</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
           <t>Âm nhạc
 Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 18</t>
         </is>
       </c>
     </row>
@@ -5974,26 +5974,26 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 18</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 18</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 18</t>
-        </is>
-      </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 18</t>
+          <t>TNXH
+Giáo viên BM 4</t>
         </is>
       </c>
     </row>
@@ -6011,20 +6011,20 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>TV tăng cường
+          <t>Toán
 Giáo viên CN 18</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 18</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 18</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -6046,26 +6046,26 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 18</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 4</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Kỹ năng sống
+Giáo viên CN 18</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 4</t>
+          <t>Toán tăng cường
+Giáo viên CN 18</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -6082,14 +6082,14 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>TV tăng cường
 Giáo viên CN 18</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -6100,8 +6100,8 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 18</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -6118,26 +6118,26 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
 Giáo viên CN 18</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 18</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 19</t>
         </is>
       </c>
@@ -6267,7 +6267,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 19</t>
         </is>
       </c>
@@ -6298,20 +6298,20 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 19</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 19</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
     </row>
@@ -6323,26 +6323,26 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 19</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 19</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>Mỹ thuật
 Giáo viên MT 1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 19</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -6366,19 +6366,19 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 19</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 19</t>
         </is>
       </c>
@@ -6401,26 +6401,26 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>Khoa học
 Giáo viên CN 19</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Thể dục
 Giáo viên TD 2</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
 Giáo viên CN 19</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -6437,25 +6437,25 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 19</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Toán tăng cường
 Giáo viên CN 19</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
+          <t>Khoa học
 Giáo viên CN 19</t>
         </is>
       </c>
@@ -6479,22 +6479,22 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>HĐTN
 Giáo viên CN 19</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>Kỹ năng sống
 Giáo viên QL 1</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 19</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 20</t>
         </is>
       </c>
@@ -6608,20 +6608,20 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 20</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 20</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
         </is>
       </c>
     </row>
@@ -6633,32 +6633,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 20</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 20</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 20</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 20</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 20</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
     </row>
@@ -6670,26 +6670,26 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
+          <t>Tiếng Việt
 Giáo viên CN 20</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 20</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 20</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 20</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -6711,25 +6711,25 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 20</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 2</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 20</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
+          <t>Đạo đức
 Giáo viên CN 20</t>
         </is>
       </c>
@@ -6747,26 +6747,26 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>Toán tăng cường
+Giáo viên CN 20</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
+Giáo viên CN 20</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Khoa học
 Giáo viên CN 20</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 20</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên QL 1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -6783,20 +6783,20 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 20</t>
+          <t>Kỹ năng sống
+Giáo viên QL 1</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 20</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 21</t>
         </is>
       </c>
@@ -6906,7 +6906,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 21</t>
         </is>
       </c>
@@ -6924,8 +6924,8 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 21</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -6943,26 +6943,26 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>Âm nhạc
 Giáo viên ÂN 1</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 21</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 21</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -6980,26 +6980,26 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 21</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 21</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
           <t>Mỹ thuật
 Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 21</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 21</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 21</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -7021,26 +7021,26 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
+          <t>Đạo đức
 Giáo viên CN 21</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
-Giáo viên CN 21</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
-Giáo viên CN 21</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 21</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -7057,26 +7057,26 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Khoa học
+Giáo viên CN 21</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên QL 1</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Công nghệ
 Giáo viên BM 4</t>
         </is>
       </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên CN 21</t>
+        </is>
+      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Khoa học
+Giáo viên CN 21</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -7099,19 +7099,19 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
           <t>HĐTN
 Giáo viên CN 21</t>
         </is>
       </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên QL 1</t>
+        </is>
+      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Lịch sử - Địa lý
 Giáo viên CN 21</t>
         </is>
       </c>
@@ -7191,13 +7191,13 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 22</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 22</t>
         </is>
       </c>
@@ -7222,20 +7222,20 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 22</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 22</t>
-        </is>
-      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 22</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -7253,8 +7253,8 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 22</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -7265,14 +7265,14 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 22</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -7290,14 +7290,14 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 22</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 22</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7308,8 +7308,8 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 22</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -7331,26 +7331,26 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên CN 22</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Đạo đức
+Giáo viên CN 22</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -7367,20 +7367,20 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>Khoa học
 Giáo viên CN 22</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 22</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Lịch sử - Địa lý
 Giáo viên CN 22</t>
         </is>
       </c>
@@ -7495,25 +7495,25 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 23</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 23</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 23</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 23</t>
         </is>
       </c>
@@ -7526,32 +7526,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 23</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 23</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 23</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 23</t>
-        </is>
-      </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 23</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
     </row>
@@ -7563,31 +7563,31 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 23</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Âm nhạc
 Giáo viên ÂN 1</t>
         </is>
       </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 23</t>
         </is>
       </c>
@@ -7600,26 +7600,26 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 23</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 23</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>Thể dục
 Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 23</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 23</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -7653,13 +7653,13 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Đạo đức
+Giáo viên CN 23</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
+          <t>Toán tăng cường
 Giáo viên CN 23</t>
         </is>
       </c>
@@ -7677,8 +7677,8 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -7689,7 +7689,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
+          <t>Khoa học
 Giáo viên CN 23</t>
         </is>
       </c>
@@ -7713,28 +7713,28 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 23</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 23</t>
         </is>
       </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 23</t>
+        </is>
+      </c>
       <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 23</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 23</t>
-        </is>
-      </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 24</t>
         </is>
       </c>
@@ -7823,7 +7823,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 24</t>
         </is>
       </c>
@@ -7836,32 +7836,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 24</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 24</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
           <t>Công nghệ
 Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 24</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 24</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
         </is>
       </c>
     </row>
@@ -7873,31 +7873,31 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 24</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>Toán
 Giáo viên CN 24</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 24</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 24</t>
         </is>
       </c>
@@ -7916,20 +7916,20 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 24</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 24</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>Tin học
 Giáo viên TH 1</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 24</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -7951,20 +7951,20 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
           <t>Khoa học
 Giáo viên CN 24</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -7999,14 +7999,14 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Đạo đức
+Giáo viên CN 24</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -8023,8 +8023,8 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 24</t>
+          <t>Âm nhạc
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 25</t>
         </is>
       </c>
@@ -8191,7 +8191,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 25</t>
         </is>
       </c>
@@ -8209,8 +8209,8 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 25</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -8228,14 +8228,14 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Toán
+Giáo viên CN 25</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -8246,14 +8246,14 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 25</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
     </row>
@@ -8265,26 +8265,26 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 25</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 25</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 25</t>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -8306,8 +8306,8 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Toán tăng cường
+Giáo viên CN 25</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -8318,13 +8318,13 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Khoa học
+Giáo viên CN 25</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
+          <t>Đạo đức
 Giáo viên CN 25</t>
         </is>
       </c>
@@ -8342,26 +8342,26 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 25</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
         </is>
       </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 25</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -8390,16 +8390,16 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 25</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>HĐTN
 Giáo viên CN 25</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 25</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -8482,13 +8482,13 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 26</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 26</t>
         </is>
       </c>
@@ -8501,31 +8501,31 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 26</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 26</t>
         </is>
       </c>
@@ -8538,32 +8538,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 26</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 26</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 26</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Thể dục
 Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 26</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
     </row>
@@ -8575,26 +8575,26 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 26</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 26</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 26</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 26</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -8622,13 +8622,13 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Khoa học
+Giáo viên CN 26</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
+          <t>Khoa học
 Giáo viên CN 26</t>
         </is>
       </c>
@@ -8652,25 +8652,25 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>Âm nhạc
 Giáo viên BM 5</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 26</t>
-        </is>
-      </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
+          <t>Toán tăng cường
 Giáo viên CN 26</t>
         </is>
       </c>
@@ -8694,20 +8694,20 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 26</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>HĐTN
 Giáo viên CN 26</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 26</t>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 27</t>
         </is>
       </c>
@@ -8817,26 +8817,26 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>Công nghệ
 Giáo viên BM 4</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 27</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 27</t>
-        </is>
-      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 27</t>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
         </is>
       </c>
     </row>
@@ -8848,32 +8848,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 27</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 27</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 27</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 27</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 27</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 27</t>
         </is>
       </c>
     </row>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 27</t>
         </is>
       </c>
@@ -8896,15 +8896,15 @@
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 27</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -8926,25 +8926,25 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
+          <t>Toán tăng cường
+Giáo viên CN 27</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Khoa học
 Giáo viên CN 27</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên BM 5</t>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
+          <t>Khoa học
 Giáo viên CN 27</t>
         </is>
       </c>
@@ -8962,8 +8962,8 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
-Giáo viên CN 27</t>
+          <t>Âm nhạc
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -8974,8 +8974,8 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
-Giáo viên CN 27</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9016,8 +9016,8 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Đạo đức
+Giáo viên CN 27</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 28</t>
         </is>
       </c>
@@ -9133,8 +9133,8 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 28</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -9158,26 +9158,26 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 28</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 28</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -9201,20 +9201,20 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 28</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 28</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -9236,25 +9236,25 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 28</t>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
+          <t>Công nghệ
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
           <t>Khoa học
-Giáo viên CN 28</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
 Giáo viên CN 28</t>
         </is>
       </c>
@@ -9272,26 +9272,26 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Toán tăng cường
+Giáo viên CN 28</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 28</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Khoa học
 Giáo viên CN 28</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -9308,8 +9308,8 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên BM 5</t>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 28</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -9320,16 +9320,16 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
           <t>Đạo đức
 Giáo viên CN 28</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -9406,7 +9406,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 29</t>
         </is>
       </c>
@@ -9431,32 +9431,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 29</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 29</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 29</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên BM 5</t>
         </is>
       </c>
     </row>
@@ -9468,31 +9468,31 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Toán
+Giáo viên CN 29</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 29</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
+          <t>Tiếng Việt
+Giáo viên CN 29</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên BM 5</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 29</t>
-        </is>
-      </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Công nghệ
 Giáo viên BM 5</t>
         </is>
       </c>
@@ -9505,8 +9505,8 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên BM 5</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -9517,13 +9517,13 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 29</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
+          <t>Tiếng Việt
 Giáo viên BM 5</t>
         </is>
       </c>
@@ -9546,8 +9546,8 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 29</t>
+          <t>Âm nhạc
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -9564,7 +9564,7 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
+          <t>Mỹ thuật
 Giáo viên BM 5</t>
         </is>
       </c>
@@ -9582,26 +9582,26 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 29</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
           <t>Khoa học
 Giáo viên CN 29</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>Khoa học
 Giáo viên CN 29</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 29</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -9618,26 +9618,26 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>Đạo đức
+Giáo viên CN 29</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 29</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 29</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 29</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">

--- a/data/Output_Template_TKB_V8.xlsx
+++ b/data/Output_Template_TKB_V8.xlsx
@@ -546,7 +546,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 1</t>
         </is>
       </c>
@@ -577,20 +577,20 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 1</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 1</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -615,19 +615,19 @@
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
+Giáo viên CN 1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 1</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -651,13 +651,13 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 1</t>
         </is>
       </c>
@@ -686,8 +686,8 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -698,14 +698,14 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 1</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 1</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -722,8 +722,8 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Kỹ năng sống
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -734,13 +734,13 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 1</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Tiếng Việt
 Giáo viên CN 1</t>
         </is>
       </c>
@@ -758,26 +758,26 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>Đạo đức
+Giáo viên CN 1</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>TNXH
 Giáo viên BM 1</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 1</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
 Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -850,13 +850,13 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 2</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 2</t>
         </is>
       </c>
@@ -881,20 +881,20 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 2</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -918,20 +918,20 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 2</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 2</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
+          <t>Toán
+Giáo viên CN 2</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -955,20 +955,20 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 2</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 2</t>
-        </is>
-      </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -996,26 +996,26 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 2</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 2</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 2</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1032,26 +1032,26 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 2</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 2</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1074,22 +1074,22 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>Đạo đức
+Giáo viên CN 2</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 2</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 3</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 2</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 2</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -1172,13 +1172,13 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 3</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 3</t>
         </is>
       </c>
@@ -1191,32 +1191,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 3</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 3</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 3</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 3</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
         </is>
       </c>
     </row>
@@ -1241,19 +1241,19 @@
       <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 3</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
+          <t>Toán
+Giáo viên CN 3</t>
         </is>
       </c>
     </row>
@@ -1265,26 +1265,26 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 3</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 3</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
-        </is>
-      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 3</t>
+          <t>Kỹ năng sống
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1306,26 +1306,26 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
+          <t>Tiếng Việt
+Giáo viên CN 3</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 3</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
 Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 3</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 3</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1342,14 +1342,14 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 1</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 3</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -1360,8 +1360,8 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 3</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1378,28 +1378,28 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 3</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>Đạo đức
 Giáo viên CN 3</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 3</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 4</t>
         </is>
       </c>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 4</t>
         </is>
       </c>
@@ -1501,26 +1501,26 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 4</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 4</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 1</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1538,26 +1538,26 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 4</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Thể dục
 Giáo viên TD 1</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 4</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 4</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1581,19 +1581,19 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 4</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 4</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 4</t>
         </is>
       </c>
@@ -1616,8 +1616,8 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 4</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1628,14 +1628,14 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 4</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Tiếng Việt
 Giáo viên CN 4</t>
         </is>
       </c>
@@ -1664,14 +1664,14 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 4</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1688,26 +1688,26 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Đạo đức
+Giáo viên CN 4</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 4</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>TNXH
 Giáo viên BM 1</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 4</t>
-        </is>
-      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 1</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 5</t>
         </is>
       </c>
@@ -1817,8 +1817,8 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 5</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -1829,14 +1829,14 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên BM 1</t>
         </is>
       </c>
     </row>
@@ -1854,26 +1854,26 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 5</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 5</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 5</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 5</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên BM 1</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 5</t>
         </is>
       </c>
@@ -1904,7 +1904,7 @@
       <c r="G45" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên BM 1</t>
+Giáo viên CN 5</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -1926,8 +1926,8 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -1944,8 +1944,8 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 5</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -1962,8 +1962,8 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -1980,8 +1980,8 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 5</t>
+          <t>Kỹ năng sống
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2004,14 +2004,14 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 2</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -2096,13 +2096,13 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 6</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 6</t>
         </is>
       </c>
@@ -2121,14 +2121,14 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 6</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 6</t>
         </is>
       </c>
@@ -2170,14 +2170,14 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 6</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 6</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2195,8 +2195,8 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Toán
+Giáo viên CN 6</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -2207,14 +2207,14 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 6</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2236,8 +2236,8 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 6</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -2272,14 +2272,14 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Đạo đức
 Giáo viên CN 6</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -2308,8 +2308,8 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 6</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2320,13 +2320,13 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 2</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Kỹ năng sống
 Giáo viên BM 2</t>
         </is>
       </c>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 7</t>
         </is>
       </c>
@@ -2476,32 +2476,32 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>Toán
+Giáo viên CN 7</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 7</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 7</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 7</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 7</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 7</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 7</t>
         </is>
       </c>
     </row>
@@ -2513,32 +2513,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 7</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>Kỹ năng sống
 Giáo viên BM 2</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 7</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 2</t>
-        </is>
-      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 7</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
     </row>
@@ -2550,13 +2550,13 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 7</t>
         </is>
       </c>
@@ -2591,8 +2591,8 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 7</t>
+          <t>Toán tăng cường
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -2603,14 +2603,14 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 7</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -2627,8 +2627,8 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 7</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -2639,8 +2639,8 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên BM 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 7</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2669,22 +2669,22 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 7</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 8</t>
         </is>
       </c>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 8</t>
         </is>
       </c>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 8</t>
         </is>
       </c>
@@ -2798,8 +2798,8 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2823,31 +2823,31 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 8</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 8</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 8</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
+          <t>TNXH
 Giáo viên BM 2</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 8</t>
         </is>
       </c>
@@ -2860,19 +2860,19 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 8</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
           <t>Toán tăng cường
 Giáo viên BM 2</t>
         </is>
       </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 2</t>
+        </is>
+      </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 8</t>
         </is>
       </c>
@@ -2901,13 +2901,13 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 8</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Toán tăng cường
 Giáo viên BM 2</t>
         </is>
       </c>
@@ -2919,8 +2919,8 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên BM 2</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2937,26 +2937,26 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>TV tăng cường
+Giáo viên CN 8</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>TV tăng cường
-Giáo viên CN 8</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2985,8 +2985,8 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Kỹ năng sống
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -3071,19 +3071,19 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 9</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 9</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 9</t>
         </is>
       </c>
@@ -3139,25 +3139,25 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
+          <t>TNXH
 Giáo viên BM 2</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 9</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 9</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 9</t>
         </is>
       </c>
@@ -3182,14 +3182,14 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Toán
+Giáo viên CN 9</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 2</t>
+          <t>Toán
+Giáo viên CN 9</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3211,14 +3211,14 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3247,8 +3247,8 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3259,8 +3259,8 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Kỹ năng sống
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3289,16 +3289,16 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
+          <t>Đạo đức
+Giáo viên CN 9</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>HĐTN
 Giáo viên CN 9</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 9</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>Thể dục
@@ -3393,7 +3393,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 10</t>
         </is>
       </c>
@@ -3406,8 +3406,8 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 10</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -3449,8 +3449,8 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 10</t>
         </is>
       </c>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 10</t>
         </is>
       </c>
@@ -3521,20 +3521,20 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Toán
+Giáo viên CN 10</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Thể dục
 Giáo viên TD 1</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -3569,8 +3569,8 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -3599,16 +3599,16 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
+          <t>Đạo đức
+Giáo viên CN 10</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>HĐTN
 Giáo viên CN 10</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 10</t>
-        </is>
-      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
           <t>TNXH
@@ -3685,7 +3685,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 11</t>
         </is>
       </c>
@@ -3697,13 +3697,13 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 11</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 11</t>
         </is>
       </c>
@@ -3734,8 +3734,8 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 11</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3759,25 +3759,25 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 11</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 3</t>
-        </is>
-      </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 11</t>
         </is>
       </c>
@@ -3796,8 +3796,8 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Toán
+Giáo viên CN 11</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 11</t>
         </is>
       </c>
@@ -3831,26 +3831,26 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>TV tăng cường
+Giáo viên CN 11</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên BM 3</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>TV tăng cường
-Giáo viên CN 11</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên BM 3</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3867,8 +3867,8 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -3879,14 +3879,14 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Toán tăng cường
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -3903,13 +3903,13 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Kỹ năng sống
 Giáo viên BM 3</t>
         </is>
       </c>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 12</t>
         </is>
       </c>
@@ -4026,20 +4026,20 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 12</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 12</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 12</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -4081,13 +4081,13 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 12</t>
         </is>
       </c>
@@ -4100,20 +4100,20 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 12</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 12</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Kỹ năng sống
 Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 12</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -4147,20 +4147,20 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>TV tăng cường
 Giáo viên CN 12</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Toán tăng cường
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4177,26 +4177,26 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Toán tăng cường
 Giáo viên BM 3</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>TV tăng cường
 Giáo viên CN 12</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên BM 3</t>
-        </is>
-      </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên BM 3</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4213,20 +4213,20 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 12</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 13</t>
         </is>
       </c>
@@ -4381,20 +4381,20 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
         </is>
       </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 13</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -4418,32 +4418,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>Toán
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 13</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 3</t>
         </is>
       </c>
     </row>
@@ -4455,19 +4455,19 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>TNXH
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 13</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 13</t>
-        </is>
-      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 13</t>
         </is>
       </c>
@@ -4502,20 +4502,20 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
           <t>Toán tăng cường
 Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -4538,8 +4538,8 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 13</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -4550,8 +4550,8 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -4574,22 +4574,22 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>Đạo đức
 Giáo viên CN 13</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 13</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -4666,7 +4666,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 14</t>
         </is>
       </c>
@@ -4691,32 +4691,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>Toán
+Giáo viên CN 14</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 14</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 14</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 14</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 14</t>
         </is>
       </c>
     </row>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
+          <t>TNXH
 Giáo viên BM 3</t>
         </is>
       </c>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 14</t>
         </is>
       </c>
@@ -4752,8 +4752,8 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>TV tăng cường
-Giáo viên CN 14</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
     </row>
@@ -4765,26 +4765,26 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 14</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 14</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -4806,26 +4806,26 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 14</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Toán tăng cường
 Giáo viên CN 14</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -4842,26 +4842,26 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>TV tăng cường
+Giáo viên CN 14</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên CN 14</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Công nghệ
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Kỹ năng sống
+Giáo viên CN 14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -4878,16 +4878,16 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>Đạo đức
 Giáo viên CN 14</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
           <t>HĐTN
@@ -4896,8 +4896,8 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên CN 14</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 15</t>
         </is>
       </c>
@@ -4988,7 +4988,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 15</t>
         </is>
       </c>
@@ -5001,20 +5001,20 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>TNXH
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 15</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 15</t>
-        </is>
-      </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 15</t>
+          <t>Công nghệ
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5044,25 +5044,25 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 15</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 15</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>TV tăng cường
+          <t>Toán
 Giáo viên CN 15</t>
         </is>
       </c>
@@ -5075,20 +5075,20 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 3</t>
+          <t>Toán
+Giáo viên CN 15</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 15</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -5116,26 +5116,26 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
+          <t>Tiếng Việt
 Giáo viên CN 15</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 15</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>Mỹ thuật
 Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên CN 15</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -5152,26 +5152,26 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>TV tăng cường
+Giáo viên CN 15</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Toán tăng cường
+Giáo viên CN 15</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Toán tăng cường
+Giáo viên CN 15</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -5188,22 +5188,22 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>Kỹ năng sống
 Giáo viên CN 15</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 15</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 3</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
           <t>HĐTN
@@ -5280,13 +5280,13 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 16</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 16</t>
         </is>
       </c>
@@ -5317,26 +5317,26 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 16</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 16</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 16</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
     </row>
@@ -5354,14 +5354,14 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 16</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>Công nghệ
 Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 16</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -5391,14 +5391,14 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 16</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 4</t>
+          <t>Toán
+Giáo viên CN 16</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -5432,8 +5432,8 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 4</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -5444,8 +5444,8 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Toán tăng cường
+Giáo viên CN 16</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -5468,20 +5468,20 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 16</t>
+          <t>TNXH
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 16</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -5498,26 +5498,26 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Đạo đức
+Giáo viên CN 16</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên CN 16</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 16</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên CN 16</t>
+          <t>TNXH
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -5590,13 +5590,13 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 17</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 17</t>
         </is>
       </c>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>TV tăng cường
 Giáo viên CN 17</t>
         </is>
       </c>
@@ -5658,32 +5658,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 17</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 17</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
           <t>TNXH
 Giáo viên BM 4</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 17</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 17</t>
-        </is>
-      </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
     </row>
@@ -5695,26 +5695,26 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 17</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>Toán
 Giáo viên CN 17</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Toán
+Giáo viên CN 17</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -5736,26 +5736,26 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 17</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
           <t>Toán tăng cường
 Giáo viên CN 17</t>
         </is>
       </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 4</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -5772,14 +5772,14 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>TV tăng cường
-Giáo viên CN 17</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -5790,8 +5790,8 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 17</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -5808,16 +5808,16 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
           <t>Kỹ năng sống
 Giáo viên CN 17</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
           <t>HĐTN
@@ -5826,8 +5826,8 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Đạo đức
+Giáo viên CN 17</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 18</t>
         </is>
       </c>
@@ -5931,8 +5931,8 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 4</t>
+          <t>Toán
+Giáo viên CN 18</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -5942,21 +5942,21 @@
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 18</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 18</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>Âm nhạc
 Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 18</t>
         </is>
       </c>
     </row>
@@ -5968,22 +5968,22 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 18</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
         </is>
       </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 18</t>
+        </is>
+      </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
@@ -5992,8 +5992,8 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 18</t>
         </is>
       </c>
     </row>
@@ -6005,8 +6005,8 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -6017,14 +6017,14 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 18</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>TV tăng cường
+Giáo viên CN 18</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -6046,26 +6046,26 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 18</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
           <t>Kỹ năng sống
 Giáo viên CN 18</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Toán tăng cường
 Giáo viên CN 18</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -6082,14 +6082,14 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>TV tăng cường
-Giáo viên CN 18</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -6100,8 +6100,8 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>TNXH
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -6118,20 +6118,20 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
+          <t>Đạo đức
+Giáo viên CN 18</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
           <t>Công nghệ
 Giáo viên BM 4</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 18</t>
-        </is>
-      </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>TNXH
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 19</t>
         </is>
       </c>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 19</t>
         </is>
       </c>
@@ -6298,20 +6298,20 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 19</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 19</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 19</t>
         </is>
       </c>
     </row>
@@ -6323,31 +6323,31 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 19</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 19</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 19</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 19</t>
         </is>
       </c>
@@ -6366,20 +6366,20 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>Toán
+Giáo viên CN 19</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 19</t>
-        </is>
-      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 19</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -6401,8 +6401,8 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Kỹ năng sống
+Giáo viên QL 1</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -6413,13 +6413,13 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
+          <t>Khoa học
 Giáo viên CN 19</t>
         </is>
       </c>
@@ -6437,26 +6437,26 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>Toán tăng cường
+Giáo viên CN 19</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 2</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 19</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên CN 19</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
-Giáo viên CN 19</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -6479,22 +6479,22 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Đạo đức
+Giáo viên CN 19</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 19</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 19</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên QL 1</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -6565,13 +6565,13 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 20</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 20</t>
         </is>
       </c>
@@ -6602,8 +6602,8 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 20</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -6614,14 +6614,14 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 20</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 20</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
     </row>
@@ -6633,32 +6633,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>Tin học
 Giáo viên TH 1</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 20</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
-        </is>
-      </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 20</t>
         </is>
       </c>
     </row>
@@ -6676,20 +6676,20 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 20</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 20</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 20</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -6711,25 +6711,25 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 20</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
           <t>Thể dục
 Giáo viên TD 2</t>
         </is>
       </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 20</t>
+          <t>Kỹ năng sống
+Giáo viên QL 1</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Khoa học
 Giáo viên CN 20</t>
         </is>
       </c>
@@ -6765,7 +6765,7 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
+          <t>Đạo đức
 Giáo viên CN 20</t>
         </is>
       </c>
@@ -6783,28 +6783,28 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 20</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên QL 1</t>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 20</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 20</t>
         </is>
       </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -6875,7 +6875,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 21</t>
         </is>
       </c>
@@ -6906,8 +6906,8 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 21</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -6943,14 +6943,14 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Toán
+Giáo viên CN 21</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -6961,8 +6961,8 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Toán
+Giáo viên CN 21</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -6980,26 +6980,26 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 21</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>Toán
 Giáo viên CN 21</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 21</t>
-        </is>
-      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 21</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -7021,26 +7021,26 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 21</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên QL 1</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Tin học
 Giáo viên TH 1</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 21</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -7057,19 +7057,19 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>Toán tăng cường
+Giáo viên CN 21</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>Khoa học
 Giáo viên CN 21</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
-        </is>
-      </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
+          <t>Đạo đức
 Giáo viên CN 21</t>
         </is>
       </c>
@@ -7105,14 +7105,14 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên QL 1</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 21</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 22</t>
         </is>
       </c>
@@ -7222,20 +7222,20 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 22</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 22</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -7253,32 +7253,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 22</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 22</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 22</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
     </row>
@@ -7302,14 +7302,14 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
           <t>Thể dục
 Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 22</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -7331,14 +7331,14 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Lịch sử - Địa lý
 Giáo viên CN 22</t>
         </is>
       </c>
@@ -7373,20 +7373,20 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
           <t>Khoa học
 Giáo viên CN 22</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Khoa học
 Giáo viên CN 22</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -7403,28 +7403,28 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>Đạo đức
+Giáo viên CN 22</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 22</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 22</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
           <t>Kỹ năng sống
 Giáo viên QL 1</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 22</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 22</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 22</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -7495,25 +7495,25 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 23</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 23</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 23</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 23</t>
         </is>
       </c>
@@ -7526,8 +7526,8 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 23</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -7538,14 +7538,14 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 23</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 23</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -7563,31 +7563,31 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 23</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 23</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 23</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 23</t>
         </is>
       </c>
@@ -7600,26 +7600,26 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
           <t>Toán
 Giáo viên CN 23</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 23</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>Thể dục
 Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 23</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 23</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -7641,26 +7641,26 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>Toán tăng cường
+Giáo viên CN 23</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
+Giáo viên CN 23</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 23</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 23</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên CN 23</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -7689,14 +7689,14 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
           <t>Khoa học
 Giáo viên CN 23</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -7725,16 +7725,16 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
           <t>HĐTN
 Giáo viên CN 23</t>
         </is>
       </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 23</t>
+        </is>
+      </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 24</t>
         </is>
       </c>
@@ -7817,13 +7817,13 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 24</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 24</t>
         </is>
       </c>
@@ -7836,32 +7836,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 24</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
+          <t>Toán
+Giáo viên CN 24</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 24</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+Giáo viên TA 3</t>
         </is>
       </c>
     </row>
@@ -7873,31 +7873,31 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 24</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 24</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
-        </is>
-      </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 24</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 24</t>
         </is>
       </c>
@@ -7910,26 +7910,26 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 24</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 24</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 24</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
           <t>Tin học
 Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 24</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 24</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -7951,26 +7951,26 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên CN 24</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>Khoa học
 Giáo viên CN 24</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7987,7 +7987,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
+          <t>Đạo đức
 Giáo viên CN 24</t>
         </is>
       </c>
@@ -7999,14 +7999,14 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
 Giáo viên CN 24</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -8023,20 +8023,20 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 24</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
           <t>Âm nhạc
 Giáo viên BM 5</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 24</t>
-        </is>
-      </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 24</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 25</t>
         </is>
       </c>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 25</t>
         </is>
       </c>
@@ -8197,25 +8197,25 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 25</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 25</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 25</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 25</t>
         </is>
       </c>
@@ -8228,22 +8228,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 25</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
         </is>
       </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 25</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 25</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
@@ -8252,8 +8252,8 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
         </is>
       </c>
     </row>
@@ -8271,20 +8271,20 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 25</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Tin học
 Giáo viên TH 1</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -8306,26 +8306,26 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
 Giáo viên CN 25</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 25</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
-Giáo viên CN 25</t>
+          <t>Âm nhạc
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 25</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -8342,26 +8342,26 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Khoa học
+Giáo viên CN 25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Toán tăng cường
+Giáo viên CN 25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Khoa học
+Giáo viên CN 25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -8384,22 +8384,22 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên BM 5</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 25</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 25</t>
         </is>
       </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 25</t>
+        </is>
+      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -8470,7 +8470,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 26</t>
         </is>
       </c>
@@ -8488,7 +8488,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 26</t>
         </is>
       </c>
@@ -8507,8 +8507,8 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -8519,13 +8519,13 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 26</t>
         </is>
       </c>
@@ -8538,32 +8538,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 26</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 26</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 26</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
         </is>
       </c>
     </row>
@@ -8575,26 +8575,26 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 26</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 26</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
         </is>
       </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 26</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
+        </is>
+      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 26</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -8616,16 +8616,16 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 26</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
           <t>Khoa học
 Giáo viên CN 26</t>
         </is>
       </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Khoa học
@@ -8634,8 +8634,8 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Toán tăng cường
+Giáo viên CN 26</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -8652,26 +8652,26 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
+          <t>Công nghệ
 Giáo viên BM 4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 26</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Âm nhạc
 Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên CN 26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Lịch sử - Địa lý
 Giáo viên CN 26</t>
         </is>
       </c>
@@ -8817,16 +8817,16 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 27</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>Tin học
 Giáo viên TH 1</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
-        </is>
-      </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
@@ -8835,8 +8835,8 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
+          <t>Tiếng Việt
+Giáo viên CN 27</t>
         </is>
       </c>
     </row>
@@ -8848,32 +8848,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 27</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 27</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 27</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 27</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 27</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 27</t>
         </is>
       </c>
     </row>
@@ -8885,26 +8885,26 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 27</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 27</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 27</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -8926,26 +8926,26 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 27</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
           <t>Khoa học
 Giáo viên CN 27</t>
         </is>
       </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ
 Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 27</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -8968,20 +8968,20 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Toán tăng cường
+Giáo viên CN 27</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Khoa học
+Giáo viên CN 27</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Đạo đức
+Giáo viên CN 27</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -9010,16 +9010,16 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>HĐTN
 Giáo viên CN 27</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 27</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -9090,13 +9090,13 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 28</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 28</t>
         </is>
       </c>
@@ -9121,20 +9121,20 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 28</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 28</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
           <t>Thể dục
 Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 28</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 28</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -9158,26 +9158,26 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>Toán
+Giáo viên CN 28</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 3</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Tin học
 Giáo viên TH 1</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 28</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -9195,20 +9195,20 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 28</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 28</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 28</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9236,20 +9236,20 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Toán tăng cường
+Giáo viên CN 28</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
+          <t>Kỹ năng sống
 Giáo viên BM 5</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 5</t>
+          <t>Đạo đức
+Giáo viên CN 28</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9272,16 +9272,16 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 28</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 28</t>
         </is>
       </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Khoa học
@@ -9290,8 +9290,8 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên BM 5</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -9308,25 +9308,25 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 28</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>HĐTN
-Giáo viên CN 28</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
 Giáo viên CN 28</t>
         </is>
       </c>
@@ -9431,32 +9431,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 29</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 29</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Kỹ năng sống
 Giáo viên BM 5</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Công nghệ
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên CN 29</t>
+Giáo viên BM 5</t>
         </is>
       </c>
     </row>
@@ -9468,31 +9468,31 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 29</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 29</t>
-        </is>
-      </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 29</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên BM 5</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
+          <t>Tiếng Việt
 Giáo viên BM 5</t>
         </is>
       </c>
@@ -9505,26 +9505,26 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>Toán
+Giáo viên CN 29</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 29</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 29</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên BM 5</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -9546,25 +9546,25 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
+          <t>Toán tăng cường
 Giáo viên BM 5</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
+Giáo viên CN 29</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Thể dục
 Giáo viên TD 3</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
+          <t>Âm nhạc
 Giáo viên BM 5</t>
         </is>
       </c>
@@ -9582,20 +9582,20 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 29</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
-Giáo viên CN 29</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên BM 5</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -9618,14 +9618,14 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Lịch sử - Địa lý
 Giáo viên CN 29</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 29</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
+          <t>Đạo đức
 Giáo viên CN 29</t>
         </is>
       </c>

--- a/data/Output_Template_TKB_V8.xlsx
+++ b/data/Output_Template_TKB_V8.xlsx
@@ -571,7 +571,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 1</t>
         </is>
       </c>
@@ -583,13 +583,13 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>TNXH
 Giáo viên BM 1</t>
         </is>
       </c>
@@ -621,13 +621,13 @@
       <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -645,7 +645,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 1</t>
         </is>
       </c>
@@ -658,13 +658,13 @@
       <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 1</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -698,14 +698,14 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 1</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 1</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -722,8 +722,8 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 1</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -734,14 +734,14 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 1</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -758,26 +758,26 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>Đạo đức
 Giáo viên CN 1</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 1</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 1</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -881,14 +881,14 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 2</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -930,14 +930,14 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 2</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên CN 2</t>
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -955,26 +955,26 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 2</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 2</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên CN 2</t>
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -996,20 +996,20 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Toán
+Giáo viên CN 2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
 Giáo viên BM 1</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 1</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên BM 1</t>
+Giáo viên CN 2</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1032,20 +1032,20 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>TNXH
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 2</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 1</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1080,16 +1080,16 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>HĐTN
 Giáo viên CN 2</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -1166,13 +1166,13 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 3</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 3</t>
         </is>
       </c>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 3</t>
         </is>
       </c>
@@ -1204,7 +1204,7 @@
       <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
-Giáo viên BM 1</t>
+Giáo viên CN 3</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1240,14 +1240,14 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 3</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 3</t>
         </is>
       </c>
@@ -1277,14 +1277,14 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Toán
+Giáo viên CN 3</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 1</t>
+          <t>Toán
+Giáo viên CN 3</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1306,8 +1306,8 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>TNXH
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1318,13 +1318,13 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Đạo đức
 Giáo viên CN 3</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Tiếng Việt
 Giáo viên BM 1</t>
         </is>
       </c>
@@ -1354,14 +1354,14 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 3</t>
+          <t>TNXH
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Tiếng Việt
+Giáo viên BM 1</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1378,28 +1378,28 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>TNXH
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
 Giáo viên BM 1</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 3</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 3</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -1476,13 +1476,13 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 4</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 4</t>
         </is>
       </c>
@@ -1507,8 +1507,8 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên BM 1</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1550,14 +1550,14 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 4</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -1581,20 +1581,20 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 4</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 4</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1628,13 +1628,13 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 4</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Đạo đức
 Giáo viên CN 4</t>
         </is>
       </c>
@@ -1664,14 +1664,14 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 4</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 4</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -1688,8 +1688,8 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 4</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1700,16 +1700,16 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
           <t>TNXH
 Giáo viên BM 1</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 5</t>
         </is>
       </c>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 5</t>
         </is>
       </c>
@@ -1823,14 +1823,14 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 5</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 5</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -1860,8 +1860,8 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 5</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 5</t>
         </is>
       </c>
@@ -1897,14 +1897,14 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 5</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 5</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -1926,26 +1926,26 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 5</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 5</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
           <t>Âm nhạc
 Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 5</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 1</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 5</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -1962,8 +1962,8 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Đạo đức
+Giáo viên CN 5</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -1974,14 +1974,14 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 5</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 1</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -1998,8 +1998,8 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 5</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2010,16 +2010,16 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
+          <t>HĐTN
+Giáo viên CN 5</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 1</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 5</t>
-        </is>
-      </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 6</t>
         </is>
       </c>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 6</t>
         </is>
       </c>
@@ -2121,14 +2121,14 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 6</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 6</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -2158,26 +2158,26 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>TNXH
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 6</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 6</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 6</t>
-        </is>
-      </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 6</t>
+          <t>Kỹ năng sống
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2195,26 +2195,26 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
           <t>Toán
 Giáo viên CN 6</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 6</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 2</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -2236,8 +2236,8 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 6</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -2272,14 +2272,14 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
+          <t>Tiếng Việt
 Giáo viên CN 6</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -2308,8 +2308,8 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Đạo đức
+Giáo viên CN 6</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -2320,14 +2320,14 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
           <t>Mỹ thuật
 Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 2</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -2445,19 +2445,19 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 7</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 7</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 7</t>
         </is>
       </c>
@@ -2488,8 +2488,8 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 7</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -2519,20 +2519,20 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 7</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 7</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 7</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -2556,20 +2556,20 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 7</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 7</t>
-        </is>
-      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 7</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -2591,26 +2591,26 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>TV tăng cường
+Giáo viên CN 7</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên BM 2</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>TV tăng cường
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 7</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 7</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 2</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -2627,8 +2627,8 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Toán tăng cường
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -2639,14 +2639,14 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 7</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên BM 2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -2669,22 +2669,22 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 7</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>TNXH
 Giáo viên BM 2</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 7</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -2755,13 +2755,13 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 8</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 8</t>
         </is>
       </c>
@@ -2798,8 +2798,8 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 8</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -2823,26 +2823,26 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 8</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 8</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 2</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -2860,19 +2860,19 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên BM 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 2</t>
+          <t>Toán
+Giáo viên CN 8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 8</t>
         </is>
       </c>
@@ -2901,26 +2901,26 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 8</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
           <t>Toán tăng cường
 Giáo viên BM 2</t>
         </is>
       </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên BM 2</t>
+        </is>
+      </c>
       <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>TV tăng cường
 Giáo viên CN 8</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2937,26 +2937,26 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 8</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Thể dục
 Giáo viên TD 1</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>TV tăng cường
 Giáo viên CN 8</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2973,28 +2973,28 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 8</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 8</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>Âm nhạc
 Giáo viên ÂN 1</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 8</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 8</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -3065,7 +3065,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 9</t>
         </is>
       </c>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 9</t>
         </is>
       </c>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 9</t>
         </is>
       </c>
@@ -3114,8 +3114,8 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 9</t>
+          <t>TNXH
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -3133,14 +3133,14 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 9</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 2</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -3151,8 +3151,8 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 9</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3170,25 +3170,25 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>Toán tăng cường
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên BM 2</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
           <t>Toán
 Giáo viên CN 9</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 9</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 9</t>
-        </is>
-      </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 9</t>
         </is>
       </c>
@@ -3211,26 +3211,26 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 9</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>TV tăng cường
 Giáo viên CN 9</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 2</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3247,26 +3247,26 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 9</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
+          <t>TNXH
 Giáo viên BM 2</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>TV tăng cường
 Giáo viên CN 9</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3283,28 +3283,28 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
           <t>Đạo đức
 Giáo viên CN 9</t>
         </is>
       </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
       <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 9</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 10</t>
         </is>
       </c>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 10</t>
         </is>
       </c>
@@ -3406,14 +3406,14 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Toán
+Giáo viên CN 10</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 10</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -3449,8 +3449,8 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 10</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -3467,7 +3467,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 10</t>
         </is>
       </c>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 10</t>
         </is>
       </c>
@@ -3521,26 +3521,26 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Toán tăng cường
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>TV tăng cường
 Giáo viên CN 10</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 1</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>TV tăng cường
-Giáo viên CN 10</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -3557,26 +3557,26 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>TV tăng cường
+Giáo viên CN 10</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
           <t>Kỹ năng sống
 Giáo viên BM 2</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>TV tăng cường
-Giáo viên CN 10</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3593,28 +3593,28 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 10</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 1</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>Đạo đức
 Giáo viên CN 10</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 10</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 3</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 11</t>
         </is>
       </c>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 11</t>
         </is>
       </c>
@@ -3734,8 +3734,8 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 11</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -3759,20 +3759,20 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Toán
+Giáo viên CN 11</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 11</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 11</t>
         </is>
       </c>
@@ -3802,13 +3802,13 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 11</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 11</t>
         </is>
       </c>
@@ -3831,8 +3831,8 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -3849,8 +3849,8 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Thể dục
+Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -3879,8 +3879,8 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
+          <t>Đạo đức
+Giáo viên CN 11</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -3903,8 +3903,8 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -3915,16 +3915,16 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
           <t>HĐTN
 Giáo viên CN 11</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 11</t>
-        </is>
-      </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 12</t>
         </is>
       </c>
@@ -4038,8 +4038,8 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 12</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -4075,14 +4075,14 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 12</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
           <t>Âm nhạc
 Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 1</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4106,13 +4106,13 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
+          <t>Toán tăng cường
 Giáo viên BM 3</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 12</t>
         </is>
       </c>
@@ -4141,8 +4141,8 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -4153,14 +4153,14 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 1</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
           <t>TV tăng cường
 Giáo viên CN 12</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên BM 3</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4177,26 +4177,26 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên BM 3</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>TV tăng cường
 Giáo viên CN 12</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 1</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4213,26 +4213,26 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 12</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>HĐTN
+Giáo viên CN 12</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
           <t>TNXH
 Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 12</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 12</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4356,13 +4356,13 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 13</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 13</t>
         </is>
       </c>
@@ -4381,32 +4381,32 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 13</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 3</t>
         </is>
       </c>
     </row>
@@ -4430,20 +4430,20 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 13</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
     </row>
@@ -4455,8 +4455,8 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -4467,13 +4467,13 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 13</t>
         </is>
       </c>
@@ -4502,20 +4502,20 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 13</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 13</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Công nghệ
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -4538,20 +4538,20 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>Toán tăng cường
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên CN 13</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>Âm nhạc
 Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -4574,22 +4574,22 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Đạo đức
+Giáo viên CN 13</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 13</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 13</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 14</t>
         </is>
       </c>
@@ -4691,32 +4691,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 14</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 14</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 14</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 14</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 14</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
     </row>
@@ -4728,32 +4728,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>Công nghệ
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 14</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 14</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>TNXH
 Giáo viên BM 3</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 14</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Toán
-Giáo viên CN 14</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 14</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
     </row>
@@ -4765,8 +4765,8 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Toán
+Giáo viên CN 14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -4776,15 +4776,15 @@
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Toán
+Giáo viên CN 14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -4812,14 +4812,14 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Toán tăng cường
+Giáo viên CN 14</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4848,20 +4848,20 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 14</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 3</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên CN 14</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -4890,16 +4890,16 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên CN 14</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>HĐTN
 Giáo viên CN 14</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 15</t>
         </is>
       </c>
@@ -4982,13 +4982,13 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 15</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 15</t>
         </is>
       </c>
@@ -5001,8 +5001,8 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 3</t>
+          <t>Toán
+Giáo viên CN 15</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -5013,14 +5013,14 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 15</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 15</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -5044,14 +5044,14 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 15</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5062,7 +5062,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 15</t>
         </is>
       </c>
@@ -5075,26 +5075,26 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>Công nghệ
+Giáo viên BM 3</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>Toán
 Giáo viên CN 15</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>TNXH
+Giáo viên BM 3</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 15</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -5116,26 +5116,26 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 15</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 3</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 15</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -5152,26 +5152,26 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>Toán tăng cường
+Giáo viên CN 15</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên CN 15</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
           <t>TV tăng cường
 Giáo viên CN 15</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên CN 15</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên CN 15</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -5188,8 +5188,8 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Kỹ năng sống
+Giáo viên CN 15</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -5200,16 +5200,16 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên CN 15</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
           <t>HĐTN
 Giáo viên CN 15</t>
         </is>
       </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
+Giáo viên CN 15</t>
+        </is>
+      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -5280,7 +5280,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 16</t>
         </is>
       </c>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 16</t>
         </is>
       </c>
@@ -5311,14 +5311,14 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 16</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 16</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -5329,8 +5329,8 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 16</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -5348,26 +5348,26 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>TV tăng cường
+Giáo viên CN 16</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>Mỹ thuật
 Giáo viên MT 1</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 16</t>
-        </is>
-      </c>
       <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Công nghệ
 Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 16</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -5385,13 +5385,13 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Toán
+Giáo viên CN 16</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 16</t>
         </is>
       </c>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 16</t>
         </is>
       </c>
@@ -5426,16 +5426,16 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 16</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
           <t>Tin học
 Giáo viên TH 1</t>
         </is>
       </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 4</t>
+        </is>
+      </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Toán tăng cường
@@ -5444,8 +5444,8 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 16</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -5462,26 +5462,26 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>TV tăng cường
-Giáo viên CN 16</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
         </is>
       </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
+        </is>
+      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Toán tăng cường
+Giáo viên CN 16</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -5498,28 +5498,28 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên CN 16</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>Đạo đức
 Giáo viên CN 16</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên CN 16</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 16</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>TNXH
-Giáo viên BM 4</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -5596,13 +5596,13 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 17</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 17</t>
         </is>
       </c>
@@ -5621,25 +5621,25 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 17</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 17</t>
-        </is>
-      </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 17</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>TV tăng cường
+          <t>Tiếng Việt
 Giáo viên CN 17</t>
         </is>
       </c>
@@ -5658,26 +5658,26 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 17</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 17</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
         </is>
       </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 17</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 17</t>
+        </is>
+      </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 17</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -5695,26 +5695,26 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 17</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 17</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 17</t>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -5736,26 +5736,26 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 17</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên CN 17</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Toán tăng cường
+Giáo viên CN 17</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -5772,26 +5772,26 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>TV tăng cường
+Giáo viên CN 17</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên CN 17</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>Âm nhạc
 Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>TNXH
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -5808,28 +5808,28 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>Đạo đức
+Giáo viên CN 17</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên CN 17</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>TNXH
 Giáo viên BM 4</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên CN 17</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 17</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 17</t>
-        </is>
-      </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -5912,7 +5912,7 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 18</t>
         </is>
       </c>
@@ -5943,14 +5943,14 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Tiếng Việt
+Giáo viên CN 18</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>TV tăng cường
+Giáo viên CN 18</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -5968,16 +5968,16 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 2</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 2</t>
-        </is>
-      </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
@@ -5986,7 +5986,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 18</t>
         </is>
       </c>
@@ -6005,8 +6005,8 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -6017,14 +6017,14 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 18</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>TV tăng cường
-Giáo viên CN 18</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -6058,14 +6058,14 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Toán tăng cường
+Giáo viên CN 18</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -6082,26 +6082,26 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t>TNXH
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 2</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
       <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên CN 18</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>TNXH
 Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 2</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -6130,14 +6130,14 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>TNXH
-Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
           <t>HĐTN
 Giáo viên CN 18</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 19</t>
         </is>
       </c>
@@ -6286,20 +6286,20 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 19</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 19</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 19</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -6335,7 +6335,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán tăng cường
 Giáo viên CN 19</t>
         </is>
       </c>
@@ -6372,14 +6372,14 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Toán
+Giáo viên CN 19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -6401,26 +6401,26 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên QL 1</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
           <t>Khoa học
 Giáo viên CN 19</t>
         </is>
       </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
+Giáo viên CN 19</t>
+        </is>
+      </c>
       <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Công nghệ
 Giáo viên BM 4</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 19</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -6437,8 +6437,8 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 19</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -6449,14 +6449,14 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
           <t>Mỹ thuật
 Giáo viên MT 1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên QL 1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -6485,13 +6485,13 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>HĐTN
+Giáo viên CN 19</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>Lịch sử - Địa lý
-Giáo viên CN 19</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
 Giáo viên CN 19</t>
         </is>
       </c>
@@ -6596,20 +6596,20 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
 Giáo viên CN 20</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 20</t>
-        </is>
-      </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 20</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6633,8 +6633,8 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 20</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -6651,8 +6651,8 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 20</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 20</t>
         </is>
       </c>
@@ -6681,15 +6681,15 @@
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Âm nhạc
 Giáo viên ÂN 1</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -6711,26 +6711,26 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên QL 1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
+Giáo viên CN 20</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên QL 1</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 20</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -6759,14 +6759,14 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 20</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
-Giáo viên CN 20</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -6783,26 +6783,26 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>Đạo đức
+Giáo viên CN 20</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 20</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 20</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 20</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -6906,8 +6906,8 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 21</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -6949,14 +6949,14 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
           <t>Âm nhạc
 Giáo viên ÂN 1</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6980,8 +6980,8 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 21</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -6998,8 +6998,8 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -7021,26 +7021,26 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Kỹ năng sống
+Giáo viên QL 1</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên QL 1</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 21</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -7069,14 +7069,14 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 21</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
           <t>Khoa học
 Giáo viên CN 21</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -7105,14 +7105,14 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 21</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Đạo đức
+Giáo viên CN 21</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 22</t>
         </is>
       </c>
@@ -7228,14 +7228,14 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 22</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên MT 1</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -7253,8 +7253,8 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 22</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -7265,14 +7265,14 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 22</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 22</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -7290,20 +7290,20 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>Công nghệ
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Việt
 Giáo viên CN 22</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 22</t>
-        </is>
-      </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Mỹ thuật
+Giáo viên MT 1</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -7331,26 +7331,26 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 2</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 22</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
           <t>Tin học
 Giáo viên TH 1</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
-Giáo viên CN 22</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 22</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -7367,26 +7367,26 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>Toán tăng cường
+Giáo viên CN 22</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
+Giáo viên CN 22</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 3</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>Khoa học
 Giáo viên CN 22</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 22</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -7415,14 +7415,14 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên QL 1</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
           <t>HĐTN
 Giáo viên CN 22</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên QL 1</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 23</t>
         </is>
       </c>
@@ -7538,14 +7538,14 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Âm nhạc
+Giáo viên ÂN 1</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -7563,8 +7563,8 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 23</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -7575,8 +7575,8 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 23</t>
+          <t>Tiếng Anh
+Giáo viên TA 3</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -7600,8 +7600,8 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 23</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -7618,8 +7618,8 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 2</t>
+          <t>Tiếng Việt
+Giáo viên CN 23</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -7641,20 +7641,20 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 23</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
           <t>Khoa học
 Giáo viên CN 23</t>
         </is>
       </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
+Giáo viên CN 23</t>
+        </is>
+      </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên ÂN 1</t>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -7677,8 +7677,8 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Thể dục
+Giáo viên TD 2</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -7689,13 +7689,13 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
+          <t>Toán tăng cường
+Giáo viên CN 23</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
+          <t>Đạo đức
 Giáo viên CN 23</t>
         </is>
       </c>
@@ -7731,8 +7731,8 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 23</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -7854,8 +7854,8 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 24</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
@@ -7873,8 +7873,8 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 24</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -7910,16 +7910,16 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 24</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
           <t>Tin học
 Giáo viên TH 1</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
-        </is>
-      </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
@@ -7928,8 +7928,8 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 24</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -7951,26 +7951,26 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Toán tăng cường
+Giáo viên CN 24</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>Toán tăng cường
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
 Giáo viên CN 24</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 24</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -7987,26 +7987,26 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Đạo đức
-Giáo viên CN 24</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
           <t>Khoa học
 Giáo viên CN 24</t>
         </is>
       </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
+Giáo viên CN 24</t>
+        </is>
+      </c>
       <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 24</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>Mỹ thuật
 Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 24</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -8035,14 +8035,14 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
+          <t>HĐTN
+Giáo viên CN 24</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 24</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -8172,7 +8172,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 25</t>
         </is>
       </c>
@@ -8191,26 +8191,26 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 25</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 25</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 25</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -8228,8 +8228,8 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Âm nhạc
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -8240,14 +8240,14 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 25</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 25</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -8265,7 +8265,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 25</t>
         </is>
       </c>
@@ -8277,14 +8277,14 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 25</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -8306,26 +8306,26 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Toán tăng cường
+Giáo viên CN 25</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
 Giáo viên CN 25</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên BM 5</t>
-        </is>
-      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Khoa học
+Giáo viên CN 25</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -8342,26 +8342,26 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
-Giáo viên CN 25</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 25</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
-Giáo viên CN 25</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -8384,19 +8384,19 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 25</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>Đạo đức
+Giáo viên CN 25</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>HĐTN
-Giáo viên CN 25</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
 Giáo viên CN 25</t>
         </is>
       </c>
@@ -8501,8 +8501,8 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 26</t>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -8513,14 +8513,14 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 26</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 26</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 26</t>
         </is>
       </c>
@@ -8550,14 +8550,14 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Việt
+Giáo viên CN 26</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
-Giáo viên CN 26</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -8575,8 +8575,8 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -8587,14 +8587,14 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Tiếng Việt
+Giáo viên CN 26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -8616,8 +8616,8 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
-Giáo viên CN 26</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -8628,14 +8628,14 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Khoa học
-Giáo viên CN 26</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
           <t>Toán tăng cường
 Giáo viên CN 26</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -8652,8 +8652,8 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Khoa học
+Giáo viên CN 26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -8664,14 +8664,14 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên BM 5</t>
+          <t>Khoa học
+Giáo viên CN 26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -8700,16 +8700,16 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
+          <t>Âm nhạc
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>HĐTN
 Giáo viên CN 26</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -8780,7 +8780,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 27</t>
         </is>
       </c>
@@ -8811,8 +8811,8 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Toán
+Giáo viên CN 27</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -8823,8 +8823,8 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>Tin học
-Giáo viên TH 1</t>
+          <t>Công nghệ
+Giáo viên BM 4</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8848,26 +8848,26 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên BM 4</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>Toán
 Giáo viên CN 27</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Tiếng Việt
 Giáo viên CN 27</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Việt
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 27</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -8885,8 +8885,8 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Kỹ năng sống
-Giáo viên BM 4</t>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -8903,8 +8903,8 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 27</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -8938,14 +8938,14 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Đạo đức
+Giáo viên CN 27</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
-Giáo viên BM 4</t>
+          <t>Âm nhạc
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -8962,8 +8962,8 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên BM 5</t>
+          <t>Tin học
+Giáo viên TH 1</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -8974,13 +8974,13 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
           <t>Khoa học
-Giáo viên CN 27</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
 Giáo viên CN 27</t>
         </is>
       </c>
@@ -9010,16 +9010,16 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
+          <t>HĐTN
+Giáo viên CN 27</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>Thể dục
 Giáo viên TD 3</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>HĐTN
-Giáo viên CN 27</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -9090,19 +9090,19 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 28</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 28</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 28</t>
         </is>
       </c>
@@ -9121,8 +9121,8 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -9133,14 +9133,14 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 28</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 28</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -9164,20 +9164,20 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
+          <t>Tiếng Việt
+Giáo viên CN 28</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Công nghệ
+          <t>Tiếng Việt
+Giáo viên CN 28</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
 Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Tin học
-Giáo viên TH 1</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -9201,19 +9201,19 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 28</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
         </is>
       </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Tin học
+Giáo viên TH 1</t>
+        </is>
+      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 28</t>
         </is>
       </c>
@@ -9236,20 +9236,20 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Toán tăng cường
-Giáo viên CN 28</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
           <t>Đạo đức
 Giáo viên CN 28</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 28</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9272,14 +9272,14 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Lịch sử - Địa lý
-Giáo viên CN 28</t>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Kỹ năng sống
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -9290,8 +9290,8 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Toán tăng cường
+Giáo viên CN 28</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -9308,28 +9308,28 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 28</t>
         </is>
       </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
+        </is>
+      </c>
       <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Âm nhạc
-Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>HĐTN
 Giáo viên CN 28</t>
         </is>
       </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Công nghệ
+Giáo viên BM 5</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Nghỉ</t>
@@ -9406,13 +9406,13 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 29</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Toán
+          <t>Tiếng Việt
 Giáo viên CN 29</t>
         </is>
       </c>
@@ -9431,26 +9431,26 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 29</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Âm nhạc
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Toán
 Giáo viên CN 29</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>Kỹ năng sống
-Giáo viên BM 5</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Công nghệ
-Giáo viên BM 5</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -9468,8 +9468,8 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Mỹ thuật
-Giáo viên BM 5</t>
+          <t>Tiếng Việt
+Giáo viên CN 29</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -9479,15 +9479,15 @@
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Tin học
 Giáo viên TH 1</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
@@ -9505,26 +9505,26 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Toán
-Giáo viên CN 29</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
           <t>Tiếng Anh
 Giáo viên TA 4</t>
         </is>
       </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Tiếng Việt
+Giáo viên CN 29</t>
+        </is>
+      </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
+          <t>Toán
 Giáo viên CN 29</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Việt
-Giáo viên CN 29</t>
+          <t>Mỹ thuật
+Giáo viên BM 5</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -9546,26 +9546,26 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>Kỹ năng sống
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Khoa học
+Giáo viên CN 29</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
           <t>Toán tăng cường
 Giáo viên BM 5</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Khoa học
-Giáo viên CN 29</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Thể dục
-Giáo viên TD 3</t>
-        </is>
-      </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Âm nhạc
-Giáo viên BM 5</t>
+          <t>Tiếng Anh
+Giáo viên TA 4</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -9582,8 +9582,8 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
+          <t>Lịch sử - Địa lý
+Giáo viên CN 29</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -9594,14 +9594,14 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Tiếng Anh
-Giáo viên TA 4</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
           <t>Khoa học
 Giáo viên CN 29</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Thể dục
+Giáo viên TD 3</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -9618,25 +9618,25 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>Công nghệ
+Giáo viên BM 5</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
           <t>Lịch sử - Địa lý
 Giáo viên CN 29</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>Lịch sử - Địa lý
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Đạo đức
 Giáo viên CN 29</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>HĐTN
-Giáo viên CN 29</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>Đạo đức
 Giáo viên CN 29</t>
         </is>
       </c>
